--- a/research/traditional_assets/database/data/ireland/ireland_packaging_container.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_packaging_container.xlsx
@@ -644,7 +644,7 @@
         <v>0.0340788148742739</v>
       </c>
       <c r="X2">
-        <v>0.09163273798481084</v>
+        <v>0.09161133364430954</v>
       </c>
       <c r="Z2">
         <v>47.38246122281682</v>
@@ -653,10 +653,10 @@
         <v>2.063953913442233</v>
       </c>
       <c r="AB2">
-        <v>0.07950097434166192</v>
+        <v>0.07948681063812128</v>
       </c>
       <c r="AC2">
-        <v>1.984452939100571</v>
+        <v>1.984467102804111</v>
       </c>
       <c r="AD2">
         <v>13919</v>
@@ -772,7 +772,7 @@
         <v>0.0340788148742739</v>
       </c>
       <c r="X3">
-        <v>0.09163273798481084</v>
+        <v>0.09161133364430954</v>
       </c>
       <c r="Z3">
         <v>47.38246122281682</v>
@@ -781,10 +781,10 @@
         <v>2.063953913442233</v>
       </c>
       <c r="AB3">
-        <v>0.07950097434166192</v>
+        <v>0.07948681063812128</v>
       </c>
       <c r="AC3">
-        <v>1.984452939100571</v>
+        <v>1.984467102804111</v>
       </c>
       <c r="AD3">
         <v>13919</v>
@@ -1121,49 +1121,49 @@
         <v>4.11049723756906</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>9.2717920643112</v>
       </c>
       <c r="G2">
         <v>5.68358365995929</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1.17610304743221</v>
       </c>
       <c r="I2">
         <v>0.338278909374293</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K2">
         <v>27905.9</v>
       </c>
       <c r="L2">
-        <v>44818.5459000077</v>
+        <v>41921.9596713246</v>
       </c>
       <c r="M2">
         <v>41220.6949864978</v>
       </c>
       <c r="N2">
-        <v>43867.5459000077</v>
+        <v>43922.9783203795</v>
       </c>
       <c r="O2">
         <v>14265.7949864978</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2952.01864905485</v>
       </c>
       <c r="Q2">
-        <v>0.0795009743416619</v>
+        <v>0.0794868106381213</v>
       </c>
       <c r="R2">
-        <v>0.0774675472854567</v>
+        <v>0.0774142893647452</v>
       </c>
       <c r="S2">
         <v>0.0557695395797173</v>
       </c>
       <c r="T2">
-        <v>0.0504320395797173</v>
+        <v>0.0492070395797173</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1176,16 +1176,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.09163273798481079</v>
+        <v>0.0916113336443095</v>
       </c>
       <c r="X2">
-        <v>0.0774675472854567</v>
+        <v>0.07953741569265051</v>
       </c>
       <c r="Y2">
         <v>0.892948161318065</v>
       </c>
       <c r="Z2">
-        <v>0.616971173124606</v>
+        <v>0.657605027268565</v>
       </c>
       <c r="AA2">
         <v>13919</v>
@@ -1218,7 +1218,7 @@
         <v>27905.9</v>
       </c>
       <c r="AK2">
-        <v>0.05132743418963755</v>
+        <v>0.05130346377183671</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1406,13 +1406,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.07746754728545668</v>
+        <v>0.07745275822866582</v>
       </c>
       <c r="C2">
-        <v>44818.5459000077</v>
+        <v>44820.59696688769</v>
       </c>
       <c r="D2">
-        <v>43867.5459000077</v>
+        <v>43869.59696688769</v>
       </c>
       <c r="E2">
         <v>-14265.79498649781</v>
@@ -1457,19 +1457,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.07746754728545668</v>
+        <v>0.07745275822866582</v>
       </c>
       <c r="T2">
         <v>0.6169711731246059</v>
       </c>
       <c r="U2">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V2">
         <v>0.125</v>
       </c>
       <c r="W2">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1488,13 +1488,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07747428324714704</v>
+        <v>0.07744726267667716</v>
       </c>
       <c r="C3">
-        <v>44387.4999274044</v>
+        <v>44406.49797922424</v>
       </c>
       <c r="D3">
-        <v>43858.21687726938</v>
+        <v>43877.21492908922</v>
       </c>
       <c r="E3">
         <v>-13844.07803663284</v>
@@ -1521,37 +1521,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M3">
-        <v>24.30633817946086</v>
+        <v>23.71593444964989</v>
       </c>
       <c r="N3">
-        <v>1514.918151616458</v>
+        <v>1515.508555346269</v>
       </c>
       <c r="O3">
-        <v>189.3647689520572</v>
+        <v>189.4385694182836</v>
       </c>
       <c r="P3">
-        <v>1325.5533826644</v>
+        <v>1326.069985927985</v>
       </c>
       <c r="Q3">
-        <v>2347.5533826644</v>
+        <v>2348.069985927985</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.07774743722358572</v>
+        <v>0.07773251745543433</v>
       </c>
       <c r="T3">
         <v>0.6224242011698992</v>
       </c>
       <c r="U3">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V3">
         <v>0.125</v>
       </c>
       <c r="W3">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>63.32605423455275</v>
+        <v>64.90254445017837</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1570,13 +1570,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.0774810192088374</v>
+        <v>0.07744176712468849</v>
       </c>
       <c r="C4">
-        <v>43956.45792184139</v>
+        <v>43992.40163774092</v>
       </c>
       <c r="D4">
-        <v>43848.89182157135</v>
+        <v>43884.83553747088</v>
       </c>
       <c r="E4">
         <v>-13422.36108676786</v>
@@ -1603,37 +1603,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M4">
-        <v>48.61267635892172</v>
+        <v>47.43186889929978</v>
       </c>
       <c r="N4">
-        <v>1490.611813436997</v>
+        <v>1491.792620896619</v>
       </c>
       <c r="O4">
-        <v>186.3264766796246</v>
+        <v>186.4740776120773</v>
       </c>
       <c r="P4">
-        <v>1304.285336757372</v>
+        <v>1305.318543284541</v>
       </c>
       <c r="Q4">
-        <v>2326.285336757372</v>
+        <v>2327.318543284541</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.07803303920126842</v>
+        <v>0.0780179860541777</v>
       </c>
       <c r="T4">
         <v>0.627988515501831</v>
       </c>
       <c r="U4">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V4">
         <v>0.125</v>
       </c>
       <c r="W4">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>31.66302711727637</v>
+        <v>32.45127222508918</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1652,13 +1652,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.07748775517052775</v>
+        <v>0.07743627157269983</v>
       </c>
       <c r="C5">
-        <v>43525.41988078883</v>
+        <v>43578.3079438167</v>
       </c>
       <c r="D5">
-        <v>43839.57073038376</v>
+        <v>43892.45879341164</v>
       </c>
       <c r="E5">
         <v>-13000.64413690288</v>
@@ -1685,37 +1685,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M5">
-        <v>72.91901453838257</v>
+        <v>71.14780334894967</v>
       </c>
       <c r="N5">
-        <v>1466.305475257536</v>
+        <v>1468.076686446969</v>
       </c>
       <c r="O5">
-        <v>183.288184407192</v>
+        <v>183.5095858058711</v>
       </c>
       <c r="P5">
-        <v>1283.017290850344</v>
+        <v>1284.567100641098</v>
       </c>
       <c r="Q5">
-        <v>2305.017290850344</v>
+        <v>2306.567100641098</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07832452987952188</v>
+        <v>0.07830934060341063</v>
       </c>
       <c r="T5">
         <v>0.6336675579643182</v>
       </c>
       <c r="U5">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V5">
         <v>0.125</v>
       </c>
       <c r="W5">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>21.10868474485092</v>
+        <v>21.63418148339279</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1734,13 +1734,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07749449113221808</v>
+        <v>0.07743077602071118</v>
       </c>
       <c r="C6">
-        <v>43094.38580171901</v>
+        <v>43164.21689883155</v>
       </c>
       <c r="D6">
-        <v>43830.25360117893</v>
+        <v>43900.08469829147</v>
       </c>
       <c r="E6">
         <v>-12578.9271870379</v>
@@ -1767,37 +1767,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M6">
-        <v>97.22535271784344</v>
+        <v>94.86373779859956</v>
       </c>
       <c r="N6">
-        <v>1441.999137078075</v>
+        <v>1444.360751997319</v>
       </c>
       <c r="O6">
-        <v>180.2498921347594</v>
+        <v>180.5450939996649</v>
       </c>
       <c r="P6">
-        <v>1261.749244943316</v>
+        <v>1263.815657997654</v>
       </c>
       <c r="Q6">
-        <v>2283.749244943316</v>
+        <v>2285.815657997654</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.07862209328023896</v>
+        <v>0.07860676503908592</v>
       </c>
       <c r="T6">
         <v>0.6394649138114404</v>
       </c>
       <c r="U6">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V6">
         <v>0.125</v>
       </c>
       <c r="W6">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>15.83151355863819</v>
+        <v>16.22563611254459</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1816,13 +1816,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.07750122709390844</v>
+        <v>0.07742528046872252</v>
       </c>
       <c r="C7">
-        <v>42663.35568210632</v>
+        <v>42750.12850416642</v>
       </c>
       <c r="D7">
-        <v>43820.94043143121</v>
+        <v>43907.7132534913</v>
       </c>
       <c r="E7">
         <v>-12157.21023717292</v>
@@ -1849,37 +1849,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M7">
-        <v>121.5316908973043</v>
+        <v>118.5796722482494</v>
       </c>
       <c r="N7">
-        <v>1417.692798898614</v>
+        <v>1420.644817547669</v>
       </c>
       <c r="O7">
-        <v>177.2115998623268</v>
+        <v>177.5806021934586</v>
       </c>
       <c r="P7">
-        <v>1240.481199036288</v>
+        <v>1243.064215354211</v>
       </c>
       <c r="Q7">
-        <v>2262.481199036288</v>
+        <v>2265.06421535421</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.07892592117360273</v>
+        <v>0.07891045104182806</v>
       </c>
       <c r="T7">
         <v>0.6453843192553443</v>
       </c>
       <c r="U7">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V7">
         <v>0.125</v>
       </c>
       <c r="W7">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>12.66521084691055</v>
+        <v>12.98050889003568</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1898,13 +1898,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.0775079630555988</v>
+        <v>0.07741978491673385</v>
       </c>
       <c r="C8">
-        <v>42232.32951942739</v>
+        <v>42336.04276120318</v>
       </c>
       <c r="D8">
-        <v>43811.63121861726</v>
+        <v>43915.34446039305</v>
       </c>
       <c r="E8">
         <v>-11735.49328730795</v>
@@ -1931,37 +1931,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M8">
-        <v>145.8380290767651</v>
+        <v>142.2956066978993</v>
       </c>
       <c r="N8">
-        <v>1393.386460719153</v>
+        <v>1396.928883098019</v>
       </c>
       <c r="O8">
-        <v>174.1733075898942</v>
+        <v>174.6161103872524</v>
       </c>
       <c r="P8">
-        <v>1219.213153129259</v>
+        <v>1222.312772710767</v>
       </c>
       <c r="Q8">
-        <v>2241.213153129259</v>
+        <v>2244.312772710767</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07923621349022954</v>
+        <v>0.07922059844888385</v>
       </c>
       <c r="T8">
         <v>0.6514296694959271</v>
       </c>
       <c r="U8">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V8">
         <v>0.125</v>
       </c>
       <c r="W8">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>10.55434237242546</v>
+        <v>10.8170907416964</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1980,13 +1980,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.07751469901728915</v>
+        <v>0.0774142893647452</v>
       </c>
       <c r="C9">
-        <v>41801.30731116096</v>
+        <v>41921.95967132464</v>
       </c>
       <c r="D9">
-        <v>43802.3259602158</v>
+        <v>43922.97832037948</v>
       </c>
       <c r="E9">
         <v>-11313.77633744297</v>
@@ -2013,37 +2013,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M9">
-        <v>170.144367256226</v>
+        <v>166.0115411475492</v>
       </c>
       <c r="N9">
-        <v>1369.080122539693</v>
+        <v>1373.212948648369</v>
       </c>
       <c r="O9">
-        <v>171.1350153174616</v>
+        <v>171.6516185810462</v>
       </c>
       <c r="P9">
-        <v>1197.945107222231</v>
+        <v>1201.561330067323</v>
       </c>
       <c r="Q9">
-        <v>2219.945107222231</v>
+        <v>2223.561330067323</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07955317875990209</v>
+        <v>0.07953741569265052</v>
       </c>
       <c r="T9">
         <v>0.6576050272685652</v>
       </c>
       <c r="U9">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V9">
         <v>0.125</v>
       </c>
       <c r="W9">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>9.046579176364681</v>
+        <v>9.271792064311196</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2062,13 +2062,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.0775984349789795</v>
+        <v>0.07751379381275654</v>
       </c>
       <c r="C10">
-        <v>41264.24412205566</v>
+        <v>41362.43102543276</v>
       </c>
       <c r="D10">
-        <v>43686.97972097549</v>
+        <v>43785.16662435259</v>
       </c>
       <c r="E10">
         <v>-10892.05938757799</v>
@@ -2095,37 +2095,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M10">
-        <v>198.1618145944987</v>
+        <v>194.7880789955788</v>
       </c>
       <c r="N10">
-        <v>1341.06267520142</v>
+        <v>1344.43641080034</v>
       </c>
       <c r="O10">
-        <v>167.6328344001775</v>
+        <v>168.0545513500425</v>
       </c>
       <c r="P10">
-        <v>1173.429840801243</v>
+        <v>1176.381859450297</v>
       </c>
       <c r="Q10">
-        <v>2195.429840801243</v>
+        <v>2198.381859450297</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07987703457891535</v>
+        <v>0.07986112026780343</v>
       </c>
       <c r="T10">
         <v>0.6639146319493042</v>
       </c>
       <c r="U10">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V10">
         <v>0.125</v>
       </c>
       <c r="W10">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>7.767513095021136</v>
+        <v>7.902046663907265</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2144,13 +2144,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.07761479594066985</v>
+        <v>0.07752142326076789</v>
       </c>
       <c r="C11">
-        <v>40820.06086428431</v>
+        <v>40930.18312777007</v>
       </c>
       <c r="D11">
-        <v>43664.51341306911</v>
+        <v>43774.63567655487</v>
       </c>
       <c r="E11">
         <v>-10470.34243771301</v>
@@ -2177,37 +2177,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M11">
-        <v>222.932041418811</v>
+        <v>219.1365888700262</v>
       </c>
       <c r="N11">
-        <v>1316.292448377108</v>
+        <v>1320.087900925892</v>
       </c>
       <c r="O11">
-        <v>164.5365560471384</v>
+        <v>165.0109876157366</v>
       </c>
       <c r="P11">
-        <v>1151.755892329969</v>
+        <v>1155.076913310156</v>
       </c>
       <c r="Q11">
-        <v>2173.755892329969</v>
+        <v>2177.076913310156</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08020800810823658</v>
+        <v>0.08019193922922344</v>
       </c>
       <c r="T11">
         <v>0.6703629092603891</v>
       </c>
       <c r="U11">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V11">
         <v>0.125</v>
       </c>
       <c r="W11">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>6.904456084463232</v>
+        <v>7.024041479028681</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2226,13 +2226,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.07782365690236022</v>
+        <v>0.07767780270877923</v>
       </c>
       <c r="C12">
-        <v>40113.5603155005</v>
+        <v>40293.72573840446</v>
       </c>
       <c r="D12">
-        <v>43379.72981415028</v>
+        <v>43559.89523705424</v>
       </c>
       <c r="E12">
         <v>-10048.62548784803</v>
@@ -2259,37 +2259,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M12">
-        <v>256.9800411401528</v>
+        <v>250.6542868921782</v>
       </c>
       <c r="N12">
-        <v>1282.244448655766</v>
+        <v>1288.57020290374</v>
       </c>
       <c r="O12">
-        <v>160.2805560819707</v>
+        <v>161.0712753629676</v>
       </c>
       <c r="P12">
-        <v>1121.963892573795</v>
+        <v>1127.498927540773</v>
       </c>
       <c r="Q12">
-        <v>2143.963892573795</v>
+        <v>2149.498927540773</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.08054633660487609</v>
+        <v>0.08053010972311944</v>
       </c>
       <c r="T12">
         <v>0.6769544816228316</v>
       </c>
       <c r="U12">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V12">
         <v>0.125</v>
       </c>
       <c r="W12">
-        <v>0.05331953957971734</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>5.989665512414055</v>
+        <v>6.140826510013107</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2308,13 +2308,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.07800364286405057</v>
+        <v>0.07770030715679056</v>
       </c>
       <c r="C13">
-        <v>39449.39432279189</v>
+        <v>39841.2789465689</v>
       </c>
       <c r="D13">
-        <v>43137.28077130665</v>
+        <v>43529.16539508366</v>
       </c>
       <c r="E13">
         <v>-9626.908537983054</v>
@@ -2341,45 +2341,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M13">
-        <v>289.6363749269403</v>
+        <v>275.719715581396</v>
       </c>
       <c r="N13">
-        <v>1249.588114868978</v>
+        <v>1263.504774214523</v>
       </c>
       <c r="O13">
-        <v>156.1985143586223</v>
+        <v>157.9380967768153</v>
       </c>
       <c r="P13">
-        <v>1093.389600510356</v>
+        <v>1105.566677437707</v>
       </c>
       <c r="Q13">
-        <v>2115.389600510356</v>
+        <v>2127.566677437707</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.08089226798908052</v>
+        <v>0.08087587955395692</v>
       </c>
       <c r="T13">
         <v>0.6836941792069018</v>
       </c>
       <c r="U13">
-        <v>0.0624366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V13">
         <v>0.125</v>
       </c>
       <c r="W13">
-        <v>0.05463203957971734</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>5.314334189495992</v>
+        <v>5.58256955455737</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2390,13 +2390,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07805237882574091</v>
+        <v>0.07780681160480192</v>
       </c>
       <c r="C14">
-        <v>38962.49344108564</v>
+        <v>39274.71627479819</v>
       </c>
       <c r="D14">
-        <v>43072.09683946538</v>
+        <v>43384.31967317792</v>
       </c>
       <c r="E14">
         <v>-9205.191588118076</v>
@@ -2423,37 +2423,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M14">
-        <v>315.966954465753</v>
+        <v>304.8336269893176</v>
       </c>
       <c r="N14">
-        <v>1223.257535330165</v>
+        <v>1234.390862806601</v>
       </c>
       <c r="O14">
-        <v>152.9071919162707</v>
+        <v>154.2988578508251</v>
       </c>
       <c r="P14">
-        <v>1070.350343413895</v>
+        <v>1080.092004955776</v>
       </c>
       <c r="Q14">
-        <v>2092.350343413895</v>
+        <v>2102.092004955776</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.08124606145019868</v>
+        <v>0.08122950779004072</v>
       </c>
       <c r="T14">
         <v>0.6905870517360646</v>
       </c>
       <c r="U14">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V14">
         <v>0.125</v>
       </c>
       <c r="W14">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>4.871473007037993</v>
+        <v>5.049392040497744</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2472,13 +2472,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.07810111478743129</v>
+        <v>0.07783631605281324</v>
       </c>
       <c r="C15">
-        <v>38475.7892585723</v>
+        <v>38813.04371948239</v>
       </c>
       <c r="D15">
-        <v>43007.10960681702</v>
+        <v>43344.3640677271</v>
       </c>
       <c r="E15">
         <v>-8783.474638253098</v>
@@ -2505,37 +2505,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M15">
-        <v>342.2975340045658</v>
+        <v>330.2364292384274</v>
       </c>
       <c r="N15">
-        <v>1196.926955791353</v>
+        <v>1208.988060557491</v>
       </c>
       <c r="O15">
-        <v>149.6158694739191</v>
+        <v>151.1235075696864</v>
       </c>
       <c r="P15">
-        <v>1047.311086317434</v>
+        <v>1057.864552987805</v>
       </c>
       <c r="Q15">
-        <v>2069.311086317434</v>
+        <v>2079.864552987805</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.08160798809433106</v>
+        <v>0.08159126541086206</v>
       </c>
       <c r="T15">
         <v>0.6976383811049782</v>
       </c>
       <c r="U15">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V15">
         <v>0.125</v>
       </c>
       <c r="W15">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>4.496744314188917</v>
+        <v>4.660977268151765</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2554,13 +2554,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07832135074912162</v>
+        <v>0.07786582050082459</v>
       </c>
       <c r="C16">
-        <v>37762.82634488354</v>
+        <v>38351.4446921827</v>
       </c>
       <c r="D16">
-        <v>42715.86364299324</v>
+        <v>43304.48199029239</v>
       </c>
       <c r="E16">
         <v>-8361.757688388119</v>
@@ -2587,45 +2587,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M16">
-        <v>376.8937657607321</v>
+        <v>355.6392314875372</v>
       </c>
       <c r="N16">
-        <v>1162.330724035186</v>
+        <v>1183.585258308381</v>
       </c>
       <c r="O16">
-        <v>145.2913405043983</v>
+        <v>147.9481572885477</v>
       </c>
       <c r="P16">
-        <v>1017.039383530788</v>
+        <v>1035.637101019834</v>
       </c>
       <c r="Q16">
-        <v>2039.039383530788</v>
+        <v>2057.637101019834</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.08197833163716418</v>
+        <v>0.08196143599960949</v>
       </c>
       <c r="T16">
         <v>0.7048536948778201</v>
       </c>
       <c r="U16">
-        <v>0.0638366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V16">
         <v>0.125</v>
       </c>
       <c r="W16">
-        <v>0.05585703957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>4.083974397106591</v>
+        <v>4.328050320426637</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2636,13 +2636,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07838233671081198</v>
+        <v>0.07802657494883594</v>
       </c>
       <c r="C17">
-        <v>37261.15601270521</v>
+        <v>37713.7138435457</v>
       </c>
       <c r="D17">
-        <v>42635.91026067988</v>
+        <v>43088.46809152037</v>
       </c>
       <c r="E17">
         <v>-7940.040738523142</v>
@@ -2669,37 +2669,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M17">
-        <v>403.8147490293558</v>
+        <v>387.3677879846217</v>
       </c>
       <c r="N17">
-        <v>1135.409740766563</v>
+        <v>1151.856701811297</v>
       </c>
       <c r="O17">
-        <v>141.9262175958203</v>
+        <v>143.9820877264121</v>
       </c>
       <c r="P17">
-        <v>993.4835231707423</v>
+        <v>1007.874614084885</v>
       </c>
       <c r="Q17">
-        <v>2015.483523170742</v>
+        <v>2029.874614084885</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.08235738914571103</v>
+        <v>0.08234031648456275</v>
       </c>
       <c r="T17">
         <v>0.7122387807394347</v>
       </c>
       <c r="U17">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V17">
         <v>0.125</v>
       </c>
       <c r="W17">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>3.811709437299485</v>
+        <v>3.973547975695451</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2718,13 +2718,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07844332267250231</v>
+        <v>0.07806482939684727</v>
       </c>
       <c r="C18">
-        <v>36759.78442670294</v>
+        <v>37240.90951484413</v>
       </c>
       <c r="D18">
-        <v>42556.25562454259</v>
+        <v>43037.38071268379</v>
       </c>
       <c r="E18">
         <v>-7518.323788658164</v>
@@ -2751,37 +2751,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M18">
-        <v>430.7357322979796</v>
+        <v>413.1923071835965</v>
       </c>
       <c r="N18">
-        <v>1108.488757497939</v>
+        <v>1126.032182612322</v>
       </c>
       <c r="O18">
-        <v>138.5610946872424</v>
+        <v>140.7540228265403</v>
       </c>
       <c r="P18">
-        <v>969.9276628106966</v>
+        <v>985.2781597857818</v>
       </c>
       <c r="Q18">
-        <v>1991.927662810697</v>
+        <v>2007.278159785782</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.0827454718330328</v>
+        <v>0.08272821793344345</v>
       </c>
       <c r="T18">
         <v>0.7197997019787069</v>
       </c>
       <c r="U18">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V18">
         <v>0.125</v>
       </c>
       <c r="W18">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.573477597468266</v>
+        <v>3.725201227214486</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2800,13 +2800,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07850430863419268</v>
+        <v>0.0781030838448586</v>
       </c>
       <c r="C19">
-        <v>36258.70991559937</v>
+        <v>36768.22618508415</v>
       </c>
       <c r="D19">
-        <v>42476.898063304</v>
+        <v>42986.41433278877</v>
       </c>
       <c r="E19">
         <v>-7096.606838793185</v>
@@ -2833,37 +2833,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M19">
-        <v>457.6567155666033</v>
+        <v>439.0168263825713</v>
       </c>
       <c r="N19">
-        <v>1081.567774229315</v>
+        <v>1100.207663413347</v>
       </c>
       <c r="O19">
-        <v>135.1959717786644</v>
+        <v>137.5259579266684</v>
       </c>
       <c r="P19">
-        <v>946.3718024506509</v>
+        <v>962.6817054866789</v>
       </c>
       <c r="Q19">
-        <v>1968.371802450651</v>
+        <v>1984.681705486679</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.08314290591041051</v>
+        <v>0.08312546640518875</v>
       </c>
       <c r="T19">
         <v>0.7275428140912145</v>
       </c>
       <c r="U19">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V19">
         <v>0.125</v>
       </c>
       <c r="W19">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.36327303291131</v>
+        <v>3.506071743260693</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2882,13 +2882,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07856529459588303</v>
+        <v>0.07814133829286996</v>
       </c>
       <c r="C20">
-        <v>35757.93082056023</v>
+        <v>36295.66342490059</v>
       </c>
       <c r="D20">
-        <v>42397.83591812984</v>
+        <v>42935.5685224702</v>
       </c>
       <c r="E20">
         <v>-6674.889888928208</v>
@@ -2915,37 +2915,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M20">
-        <v>484.577698835227</v>
+        <v>464.841345581546</v>
       </c>
       <c r="N20">
-        <v>1054.646790960692</v>
+        <v>1074.383144214373</v>
       </c>
       <c r="O20">
-        <v>131.8308488700864</v>
+        <v>134.2978930267966</v>
       </c>
       <c r="P20">
-        <v>922.8159420906051</v>
+        <v>940.085251187576</v>
       </c>
       <c r="Q20">
-        <v>1944.815942090605</v>
+        <v>1962.085251187576</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.08355003350187062</v>
+        <v>0.08353240386404981</v>
       </c>
       <c r="T20">
         <v>0.7354747825967102</v>
       </c>
       <c r="U20">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V20">
         <v>0.125</v>
       </c>
       <c r="W20">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.176424531082904</v>
+        <v>3.31128997974621</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2964,13 +2964,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.0786262805575734</v>
+        <v>0.07817959274088131</v>
       </c>
       <c r="C21">
-        <v>35257.44549507857</v>
+        <v>35823.22080695743</v>
       </c>
       <c r="D21">
-        <v>42319.06754251316</v>
+        <v>42884.84285439202</v>
       </c>
       <c r="E21">
         <v>-6253.172939063229</v>
@@ -2997,37 +2997,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M21">
-        <v>511.4986821038507</v>
+        <v>490.6658647805208</v>
       </c>
       <c r="N21">
-        <v>1027.725807692068</v>
+        <v>1048.558625015398</v>
       </c>
       <c r="O21">
-        <v>128.4657259615085</v>
+        <v>131.0698281269247</v>
       </c>
       <c r="P21">
-        <v>899.2600817305592</v>
+        <v>917.4887968884732</v>
       </c>
       <c r="Q21">
-        <v>1921.260081730559</v>
+        <v>1939.488796888473</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.08396721362645319</v>
+        <v>0.08394938916140124</v>
       </c>
       <c r="T21">
         <v>0.7436026021764154</v>
       </c>
       <c r="U21">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V21">
         <v>0.125</v>
       </c>
       <c r="W21">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.009244292604856</v>
+        <v>3.137011559759568</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3046,13 +3046,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.07914226651926375</v>
+        <v>0.07865534718889264</v>
       </c>
       <c r="C22">
-        <v>34180.82271416739</v>
+        <v>34780.519558161</v>
       </c>
       <c r="D22">
-        <v>41664.16171146696</v>
+        <v>42263.85855546056</v>
       </c>
       <c r="E22">
         <v>-5831.455989198252</v>
@@ -3079,37 +3079,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M22">
-        <v>560.3489467654532</v>
+        <v>537.5762314727444</v>
       </c>
       <c r="N22">
-        <v>978.8755430304653</v>
+        <v>1001.648258323174</v>
       </c>
       <c r="O22">
-        <v>122.3594428788082</v>
+        <v>125.2060322903968</v>
       </c>
       <c r="P22">
-        <v>856.5161001516572</v>
+        <v>876.4422260327774</v>
       </c>
       <c r="Q22">
-        <v>1878.516100151657</v>
+        <v>1898.442226032777</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.08439482325415035</v>
+        <v>0.08437679909118646</v>
       </c>
       <c r="T22">
         <v>0.7519336172456135</v>
       </c>
       <c r="U22">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V22">
         <v>0.125</v>
       </c>
       <c r="W22">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.746903511965011</v>
+        <v>2.863267383639819</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3128,13 +3128,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.07922600248095409</v>
+        <v>0.07871547663690398</v>
       </c>
       <c r="C23">
-        <v>33654.73227091446</v>
+        <v>34281.5956908996</v>
       </c>
       <c r="D23">
-        <v>41559.788218079</v>
+        <v>42186.65163806414</v>
       </c>
       <c r="E23">
         <v>-5409.739039333273</v>
@@ -3161,37 +3161,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M23">
-        <v>588.3663941037258</v>
+        <v>564.4550430463817</v>
       </c>
       <c r="N23">
-        <v>950.8580956921927</v>
+        <v>974.7694467495369</v>
       </c>
       <c r="O23">
-        <v>118.8572619615241</v>
+        <v>121.8461808436921</v>
       </c>
       <c r="P23">
-        <v>832.0008337306687</v>
+        <v>852.9232659058448</v>
       </c>
       <c r="Q23">
-        <v>1854.000833730669</v>
+        <v>1874.923265905845</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.08483325844204234</v>
+        <v>0.08481502952552322</v>
       </c>
       <c r="T23">
         <v>0.7604755440887152</v>
       </c>
       <c r="U23">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V23">
         <v>0.125</v>
       </c>
       <c r="W23">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.61609858282382</v>
+        <v>2.726921317752208</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3210,13 +3210,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.07982948844264445</v>
+        <v>0.07877560608491532</v>
       </c>
       <c r="C24">
-        <v>32495.98547110895</v>
+        <v>33782.95338991563</v>
       </c>
       <c r="D24">
-        <v>40822.75836813847</v>
+        <v>42109.72628694515</v>
       </c>
       <c r="E24">
         <v>-4988.022089468295</v>
@@ -3243,45 +3243,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M24">
-        <v>641.4338282639783</v>
+        <v>591.3338546200189</v>
       </c>
       <c r="N24">
-        <v>897.7906615319403</v>
+        <v>947.8906351758997</v>
       </c>
       <c r="O24">
-        <v>112.2238326914925</v>
+        <v>118.4863293969875</v>
       </c>
       <c r="P24">
-        <v>785.5668288404477</v>
+        <v>829.4043057789122</v>
       </c>
       <c r="Q24">
-        <v>1807.566828840448</v>
+        <v>1851.404305778912</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.08528293555782901</v>
+        <v>0.08526449663766347</v>
       </c>
       <c r="T24">
         <v>0.7692364946970247</v>
       </c>
       <c r="U24">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V24">
         <v>0.125</v>
       </c>
       <c r="W24">
-        <v>0.06049453957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.399662166184444</v>
+        <v>2.602970348763471</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3292,13 +3292,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.07993684940433479</v>
+        <v>0.07954011053292667</v>
       </c>
       <c r="C25">
-        <v>31945.88026416308</v>
+        <v>32407.08802315401</v>
       </c>
       <c r="D25">
-        <v>40694.37011105757</v>
+        <v>41155.5778700485</v>
       </c>
       <c r="E25">
         <v>-4566.305139603317</v>
@@ -3325,37 +3325,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M25">
-        <v>670.5899113668864</v>
+        <v>652.1608806577868</v>
       </c>
       <c r="N25">
-        <v>868.6345784290321</v>
+        <v>887.0636091381317</v>
       </c>
       <c r="O25">
-        <v>108.579322303629</v>
+        <v>110.8829511422665</v>
       </c>
       <c r="P25">
-        <v>760.055256125403</v>
+        <v>776.1806579958652</v>
       </c>
       <c r="Q25">
-        <v>1782.055256125403</v>
+        <v>1798.180657995865</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.08574429259870105</v>
+        <v>0.08572563822024892</v>
       </c>
       <c r="T25">
         <v>0.7782250024639915</v>
       </c>
       <c r="U25">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V25">
         <v>0.125</v>
       </c>
       <c r="W25">
-        <v>0.06049453957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.29532902852425</v>
+        <v>2.360191381371136</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3374,13 +3374,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08103121036602515</v>
+        <v>0.07963086498093801</v>
       </c>
       <c r="C26">
-        <v>30260.10427268576</v>
+        <v>31874.9674003623</v>
       </c>
       <c r="D26">
-        <v>39430.31106944524</v>
+        <v>41045.17419712178</v>
       </c>
       <c r="E26">
         <v>-4144.588189738339</v>
@@ -3407,45 +3407,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M26">
-        <v>747.3156664145641</v>
+        <v>680.5157015559515</v>
       </c>
       <c r="N26">
-        <v>791.9088233813544</v>
+        <v>858.708788239967</v>
       </c>
       <c r="O26">
-        <v>98.9886029226693</v>
+        <v>107.3385985299959</v>
       </c>
       <c r="P26">
-        <v>692.9202204586851</v>
+        <v>751.3701897099711</v>
       </c>
       <c r="Q26">
-        <v>1714.920220458685</v>
+        <v>1773.370189709971</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.08621779061433288</v>
+        <v>0.08619891510763927</v>
       </c>
       <c r="T26">
         <v>0.7874500499090364</v>
       </c>
       <c r="U26">
-        <v>0.0738366166625341</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V26">
         <v>0.125</v>
       </c>
       <c r="W26">
-        <v>0.06460703957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.059671112183072</v>
+        <v>2.261850073814005</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3456,13 +3456,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08321407132771548</v>
+        <v>0.08033411942894934</v>
       </c>
       <c r="C27">
-        <v>27537.89225007421</v>
+        <v>30617.40457398921</v>
       </c>
       <c r="D27">
-        <v>37129.81599669866</v>
+        <v>40209.32832061366</v>
       </c>
       <c r="E27">
         <v>-3722.871239873361</v>
@@ -3489,45 +3489,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M27">
-        <v>876.503010025445</v>
+        <v>738.3907089446647</v>
       </c>
       <c r="N27">
-        <v>662.7214797704736</v>
+        <v>800.8337808512539</v>
       </c>
       <c r="O27">
-        <v>82.8401849713092</v>
+        <v>100.1042226064067</v>
       </c>
       <c r="P27">
-        <v>579.8812947991644</v>
+        <v>700.7295582448471</v>
       </c>
       <c r="Q27">
-        <v>1601.881294799164</v>
+        <v>1722.729558244847</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.08670391524371487</v>
+        <v>0.08668481271202667</v>
       </c>
       <c r="T27">
         <v>0.7969210986192825</v>
       </c>
       <c r="U27">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V27">
         <v>0.125</v>
       </c>
       <c r="W27">
-        <v>0.07274453957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>1.756097209239743</v>
+        <v>2.084566437727576</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3538,13 +3538,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08451318228940585</v>
+        <v>0.08044937387696068</v>
       </c>
       <c r="C28">
-        <v>25870.19788077973</v>
+        <v>30061.93906182826</v>
       </c>
       <c r="D28">
-        <v>35883.83857726917</v>
+        <v>40075.5797583177</v>
       </c>
       <c r="E28">
         <v>-3301.154290008382</v>
@@ -3571,45 +3571,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M28">
-        <v>963.0969416999631</v>
+        <v>767.9263373024512</v>
       </c>
       <c r="N28">
-        <v>576.1275480959555</v>
+        <v>771.2981524934673</v>
       </c>
       <c r="O28">
-        <v>72.01594351199444</v>
+        <v>96.41226906168342</v>
       </c>
       <c r="P28">
-        <v>504.111604583961</v>
+        <v>674.8858834317839</v>
       </c>
       <c r="Q28">
-        <v>1526.111604583961</v>
+        <v>1696.885883431784</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.08720317837659372</v>
+        <v>0.08718384268410023</v>
       </c>
       <c r="T28">
         <v>0.8066481216189949</v>
       </c>
       <c r="U28">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V28">
         <v>0.125</v>
       </c>
       <c r="W28">
-        <v>0.07685703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>1.598203070896511</v>
+        <v>2.004390805507284</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3620,13 +3620,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08478416825109622</v>
+        <v>0.08332875332497203</v>
       </c>
       <c r="C29">
-        <v>25199.04591813288</v>
+        <v>26565.4383661772</v>
       </c>
       <c r="D29">
-        <v>35634.40356448729</v>
+        <v>37000.79601253161</v>
       </c>
       <c r="E29">
         <v>-2879.437340143404</v>
@@ -3653,37 +3653,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M29">
-        <v>1000.139131765346</v>
+        <v>930.6823501225844</v>
       </c>
       <c r="N29">
-        <v>539.0853580305723</v>
+        <v>608.5421396733342</v>
       </c>
       <c r="O29">
-        <v>67.38566975382153</v>
+        <v>76.06776745916677</v>
       </c>
       <c r="P29">
-        <v>471.6996882767507</v>
+        <v>532.4743722141674</v>
       </c>
       <c r="Q29">
-        <v>1493.699688276751</v>
+        <v>1554.474372214167</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.08771611995146922</v>
+        <v>0.08769654471020322</v>
       </c>
       <c r="T29">
         <v>0.8166416383995213</v>
       </c>
       <c r="U29">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V29">
         <v>0.125</v>
       </c>
       <c r="W29">
-        <v>0.07685703957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>1.53901036456701</v>
+        <v>1.653866638379013</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3702,13 +3702,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08904865421278656</v>
+        <v>0.08354638277298337</v>
       </c>
       <c r="C30">
-        <v>21263.63781371085</v>
+        <v>25930.39070166818</v>
       </c>
       <c r="D30">
-        <v>32120.71240993025</v>
+        <v>36787.46529788757</v>
       </c>
       <c r="E30">
         <v>-2457.720390278426</v>
@@ -3735,45 +3735,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M30">
-        <v>1229.652937749106</v>
+        <v>965.1520667937913</v>
       </c>
       <c r="N30">
-        <v>309.5715520468129</v>
+        <v>574.0724230021273</v>
       </c>
       <c r="O30">
-        <v>38.69644400585162</v>
+        <v>71.75905287526591</v>
       </c>
       <c r="P30">
-        <v>270.8751080409613</v>
+        <v>502.3133701268613</v>
       </c>
       <c r="Q30">
-        <v>1292.875108040961</v>
+        <v>1524.313370126861</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.08824330990342459</v>
+        <v>0.08822348845925349</v>
       </c>
       <c r="T30">
         <v>0.8269127528683955</v>
       </c>
       <c r="U30">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V30">
         <v>0.125</v>
       </c>
       <c r="W30">
-        <v>0.09111953957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y30">
-        <v>1.251755225025923</v>
+        <v>1.59479997272262</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3784,13 +3784,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.0982499397897565</v>
+        <v>0.08376401222099471</v>
       </c>
       <c r="C31">
-        <v>15206.98879330017</v>
+        <v>25297.78888220853</v>
       </c>
       <c r="D31">
-        <v>26485.78033938453</v>
+        <v>36576.58042829289</v>
       </c>
       <c r="E31">
         <v>-2036.003440413449</v>
@@ -3817,45 +3817,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M31">
-        <v>1673.483297654247</v>
+        <v>999.621783464998</v>
       </c>
       <c r="N31">
-        <v>-134.2588078583281</v>
+        <v>539.6027063309206</v>
       </c>
       <c r="O31">
-        <v>-16.78235098229101</v>
+        <v>67.45033829136507</v>
       </c>
       <c r="P31">
-        <v>-117.476456876037</v>
+        <v>472.1523680395555</v>
       </c>
       <c r="Q31">
-        <v>904.523543123963</v>
+        <v>1494.152368039556</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.08891506387106524</v>
+        <v>0.08876527569419251</v>
       </c>
       <c r="T31">
-        <v>0.8400003731293019</v>
+        <v>0.8374731945054069</v>
       </c>
       <c r="U31">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V31">
-        <v>0.1149716053301427</v>
+        <v>0.125</v>
       </c>
       <c r="W31">
-        <v>0.1211042911768972</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y31">
-        <v>0.9197728426411419</v>
+        <v>1.539806870214944</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3866,13 +3866,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.09916030595638184</v>
+        <v>0.08770914166900605</v>
       </c>
       <c r="C32">
-        <v>14333.40490066773</v>
+        <v>21432.92471413339</v>
       </c>
       <c r="D32">
-        <v>26033.91339661708</v>
+        <v>33133.43321008274</v>
       </c>
       <c r="E32">
         <v>-1614.286490548469</v>
@@ -3899,45 +3899,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M32">
-        <v>1731.189618263014</v>
+        <v>1213.742920778686</v>
       </c>
       <c r="N32">
-        <v>-191.9651284670954</v>
+        <v>325.4815690172329</v>
       </c>
       <c r="O32">
-        <v>-23.99564105838692</v>
+        <v>40.68519612715411</v>
       </c>
       <c r="P32">
-        <v>-167.9694874087085</v>
+        <v>284.7963728900788</v>
       </c>
       <c r="Q32">
-        <v>854.0305125912915</v>
+        <v>1306.796372890079</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.08953099335493758</v>
+        <v>0.08932254256441549</v>
       </c>
       <c r="T32">
-        <v>0.8520003784597204</v>
+        <v>0.8483353630463332</v>
       </c>
       <c r="U32">
-        <v>0.1368366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V32">
-        <v>0.1111392184858046</v>
+        <v>0.125</v>
       </c>
       <c r="W32">
-        <v>0.1216287020264184</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>0.889113747886437</v>
+        <v>1.26816351588557</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3948,13 +3948,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1000706721230072</v>
+        <v>0.09613914244793575</v>
       </c>
       <c r="C33">
-        <v>13474.98073834339</v>
+        <v>15462.5461425791</v>
       </c>
       <c r="D33">
-        <v>25597.20618415771</v>
+        <v>27584.77158839342</v>
       </c>
       <c r="E33">
         <v>-1192.569540683491</v>
@@ -3981,37 +3981,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M33">
-        <v>1788.895938871781</v>
+        <v>1628.095265888265</v>
       </c>
       <c r="N33">
-        <v>-249.6714490758625</v>
+        <v>-88.8707760923462</v>
       </c>
       <c r="O33">
-        <v>-31.20893113448281</v>
+        <v>-11.10884701154328</v>
       </c>
       <c r="P33">
-        <v>-218.4625179413797</v>
+        <v>-77.76192908080293</v>
       </c>
       <c r="Q33">
-        <v>803.5374820586203</v>
+        <v>944.2380709191971</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.09016477586732799</v>
+        <v>0.08999299372954334</v>
       </c>
       <c r="T33">
-        <v>0.8643482100316003</v>
+        <v>0.8614037041647723</v>
       </c>
       <c r="U33">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V33">
-        <v>0.1075540824056174</v>
+        <v>0.1181767831746121</v>
       </c>
       <c r="W33">
-        <v>0.122119279917906</v>
+        <v>0.109819279917906</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.8604326592449391</v>
+        <v>0.9454142653968964</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4030,13 +4030,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1009810382896325</v>
+        <v>0.09692650861456112</v>
       </c>
       <c r="C34">
-        <v>12630.96599937414</v>
+        <v>14616.0140341722</v>
       </c>
       <c r="D34">
-        <v>25174.90839505344</v>
+        <v>27159.9564298515</v>
       </c>
       <c r="E34">
         <v>-770.8525908185129</v>
@@ -4063,37 +4063,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M34">
-        <v>1846.602259480548</v>
+        <v>1680.614468013693</v>
       </c>
       <c r="N34">
-        <v>-307.3777696846296</v>
+        <v>-141.3899782177741</v>
       </c>
       <c r="O34">
-        <v>-38.4222212105787</v>
+        <v>-17.67374727722176</v>
       </c>
       <c r="P34">
-        <v>-268.9555484740509</v>
+        <v>-123.7162309405524</v>
       </c>
       <c r="Q34">
-        <v>753.0444515259492</v>
+        <v>898.2837690594476</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.09081719904184753</v>
+        <v>0.09064289069615428</v>
       </c>
       <c r="T34">
-        <v>0.8770592131203006</v>
+        <v>0.8740714056966071</v>
       </c>
       <c r="U34">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V34">
-        <v>0.1041930173304418</v>
+        <v>0.1144837587004054</v>
       </c>
       <c r="W34">
-        <v>0.1225791966911757</v>
+        <v>0.1102791966911757</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8335441386435347</v>
+        <v>0.9158700696032434</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4112,13 +4112,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1018914044562579</v>
+        <v>0.09771387478118645</v>
       </c>
       <c r="C35">
-        <v>11800.65908687734</v>
+        <v>13782.36807939246</v>
       </c>
       <c r="D35">
-        <v>24766.31843242162</v>
+        <v>26748.02742493674</v>
       </c>
       <c r="E35">
         <v>-349.1356409535347</v>
@@ -4145,37 +4145,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M35">
-        <v>1904.308580089315</v>
+        <v>1733.133670139121</v>
       </c>
       <c r="N35">
-        <v>-365.0840902933969</v>
+        <v>-193.909180343202</v>
       </c>
       <c r="O35">
-        <v>-45.63551128667461</v>
+        <v>-24.23864754290025</v>
       </c>
       <c r="P35">
-        <v>-319.4485790067223</v>
+        <v>-169.6705328003018</v>
       </c>
       <c r="Q35">
-        <v>702.5514209932777</v>
+        <v>852.3294671996982</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.09148909753500942</v>
+        <v>0.09131218757221628</v>
       </c>
       <c r="T35">
-        <v>0.8901496491370213</v>
+        <v>0.8871172475726758</v>
       </c>
       <c r="U35">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V35">
-        <v>0.1010356531689133</v>
+        <v>0.1110145538913022</v>
       </c>
       <c r="W35">
-        <v>0.1230112397206108</v>
+        <v>0.1107112397206108</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8082852253513063</v>
+        <v>0.8881164311304178</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4194,13 +4194,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1320720422799535</v>
+        <v>0.09850124094781179</v>
       </c>
       <c r="C36">
-        <v>2714.915332016712</v>
+        <v>12961.03071377262</v>
       </c>
       <c r="D36">
-        <v>16102.29162742597</v>
+        <v>26348.40700918188</v>
       </c>
       <c r="E36">
         <v>72.58130891144356</v>
@@ -4227,45 +4227,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M36">
-        <v>3179.343048178328</v>
+        <v>1785.652872264548</v>
       </c>
       <c r="N36">
-        <v>-1640.11855838241</v>
+        <v>-246.4283824686299</v>
       </c>
       <c r="O36">
-        <v>-205.0148197978012</v>
+        <v>-30.80354780857874</v>
       </c>
       <c r="P36">
-        <v>-1435.103738584609</v>
+        <v>-215.6248346600512</v>
       </c>
       <c r="Q36">
-        <v>-413.1037385846087</v>
+        <v>806.3751653399488</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.0927938894023131</v>
+        <v>0.09200176617179531</v>
       </c>
       <c r="T36">
-        <v>0.9155705938599333</v>
+        <v>0.9005584179904437</v>
       </c>
       <c r="U36">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V36">
-        <v>0.06051660934630228</v>
+        <v>0.1077494199533228</v>
       </c>
       <c r="W36">
-        <v>0.2083178684541968</v>
+        <v>0.1111178684541967</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y36">
-        <v>0.4841328747704182</v>
+        <v>0.861995359626582</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4276,13 +4276,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1338314084465789</v>
+        <v>0.09928860711443713</v>
       </c>
       <c r="C37">
-        <v>1971.383389135697</v>
+        <v>12151.45838044031</v>
       </c>
       <c r="D37">
-        <v>15780.47663440993</v>
+        <v>25960.55162571455</v>
       </c>
       <c r="E37">
         <v>494.2982587764218</v>
@@ -4309,45 +4309,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M37">
-        <v>3272.853137830632</v>
+        <v>1838.172074389976</v>
       </c>
       <c r="N37">
-        <v>-1733.628648034714</v>
+        <v>-298.9475845940578</v>
       </c>
       <c r="O37">
-        <v>-216.7035810043392</v>
+        <v>-37.36844807425723</v>
       </c>
       <c r="P37">
-        <v>-1516.925067030375</v>
+        <v>-261.5791365198006</v>
       </c>
       <c r="Q37">
-        <v>-494.9250670303747</v>
+        <v>760.4208634801994</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.09351687231619484</v>
+        <v>0.09271256257443831</v>
       </c>
       <c r="T37">
-        <v>0.9296562953039322</v>
+        <v>0.9144131628826043</v>
       </c>
       <c r="U37">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V37">
-        <v>0.05878756336497935</v>
+        <v>0.1046708650975135</v>
       </c>
       <c r="W37">
-        <v>0.2087012612601492</v>
+        <v>0.1115012612601492</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y37">
-        <v>0.4703005069198348</v>
+        <v>0.8373669207801082</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4358,13 +4358,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1355907746132042</v>
+        <v>0.1000759732810625</v>
       </c>
       <c r="C38">
-        <v>1240.462773266034</v>
+        <v>11353.13906342533</v>
       </c>
       <c r="D38">
-        <v>15471.27296840525</v>
+        <v>25583.94925856455</v>
       </c>
       <c r="E38">
         <v>916.0152086413982</v>
@@ -4391,45 +4391,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M38">
-        <v>3366.363227482936</v>
+        <v>1890.691276515404</v>
       </c>
       <c r="N38">
-        <v>-1827.138737687017</v>
+        <v>-351.4667867194855</v>
       </c>
       <c r="O38">
-        <v>-228.3923422108771</v>
+        <v>-43.93334833993569</v>
       </c>
       <c r="P38">
-        <v>-1598.74639547614</v>
+        <v>-307.5334383795498</v>
       </c>
       <c r="Q38">
-        <v>-576.7463954761399</v>
+        <v>714.4665616204502</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.09426244844613538</v>
+        <v>0.09344557136466392</v>
       </c>
       <c r="T38">
-        <v>0.9441821749180561</v>
+        <v>0.928700868552645</v>
       </c>
       <c r="U38">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V38">
-        <v>0.05715457549372994</v>
+        <v>0.1017633410670271</v>
       </c>
       <c r="W38">
-        <v>0.209063354465771</v>
+        <v>0.111863354465771</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.4572366039498396</v>
+        <v>0.8141067285362165</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4440,13 +4440,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1373501407798295</v>
+        <v>0.1317384019802129</v>
       </c>
       <c r="C39">
-        <v>521.4264093250313</v>
+        <v>1505.485040300671</v>
       </c>
       <c r="D39">
-        <v>15173.95355432922</v>
+        <v>16158.01218530486</v>
       </c>
       <c r="E39">
         <v>1337.732158506376</v>
@@ -4473,37 +4473,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M39">
-        <v>3459.87331713524</v>
+        <v>3225.820409960177</v>
       </c>
       <c r="N39">
-        <v>-1920.648827339321</v>
+        <v>-1686.595920164258</v>
       </c>
       <c r="O39">
-        <v>-240.0811034174151</v>
+        <v>-210.8244900205323</v>
       </c>
       <c r="P39">
-        <v>-1680.567723921906</v>
+        <v>-1475.771430143726</v>
       </c>
       <c r="Q39">
-        <v>-658.567723921906</v>
+        <v>-453.7714301437259</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.0950316936595661</v>
+        <v>0.09493369556493644</v>
       </c>
       <c r="T39">
-        <v>0.9591691935675491</v>
+        <v>0.9577071790600742</v>
       </c>
       <c r="U39">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V39">
-        <v>0.05560985723714264</v>
+        <v>0.05964469089178621</v>
       </c>
       <c r="W39">
-        <v>0.2094058750656836</v>
+        <v>0.1944058750656835</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.4448788578971411</v>
+        <v>0.4771575271342897</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4522,13 +4522,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1391095069464549</v>
+        <v>0.1333477681468382</v>
       </c>
       <c r="C40">
-        <v>-186.3979412869194</v>
+        <v>786.7398659430346</v>
       </c>
       <c r="D40">
-        <v>14887.84615358225</v>
+        <v>15860.98396081221</v>
       </c>
       <c r="E40">
         <v>1759.449108371356</v>
@@ -4555,37 +4555,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M40">
-        <v>3553.383406787544</v>
+        <v>3313.004745364506</v>
       </c>
       <c r="N40">
-        <v>-2014.158916991625</v>
+        <v>-1773.780255568588</v>
       </c>
       <c r="O40">
-        <v>-251.7698646239531</v>
+        <v>-221.7225319460734</v>
       </c>
       <c r="P40">
-        <v>-1762.389052367672</v>
+        <v>-1552.057723622514</v>
       </c>
       <c r="Q40">
-        <v>-740.3890523676719</v>
+        <v>-530.057723622514</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.0958257532347204</v>
+        <v>0.09572617452566125</v>
       </c>
       <c r="T40">
-        <v>0.9746396644315419</v>
+        <v>0.9731540690449143</v>
       </c>
       <c r="U40">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V40">
-        <v>0.05414643994142836</v>
+        <v>0.05807509376305499</v>
       </c>
       <c r="W40">
-        <v>0.2097303682656007</v>
+        <v>0.1947303682656007</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4331715195314269</v>
+        <v>0.4646007501044399</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4604,13 +4604,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1408688731130802</v>
+        <v>0.1349571343134636</v>
       </c>
       <c r="C41">
-        <v>-883.6327547683122</v>
+        <v>78.71794281397888</v>
       </c>
       <c r="D41">
-        <v>14612.32828996584</v>
+        <v>15574.67898754812</v>
       </c>
       <c r="E41">
         <v>2181.166058236333</v>
@@ -4637,37 +4637,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M41">
-        <v>3646.893496439847</v>
+        <v>3400.189080768835</v>
       </c>
       <c r="N41">
-        <v>-2107.669006643929</v>
+        <v>-1860.964590972916</v>
       </c>
       <c r="O41">
-        <v>-263.4586258304911</v>
+        <v>-232.6205738716145</v>
       </c>
       <c r="P41">
-        <v>-1844.210380813437</v>
+        <v>-1628.344017101302</v>
       </c>
       <c r="Q41">
-        <v>-822.2103808134375</v>
+        <v>-606.3440171013017</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.09664584755004368</v>
+        <v>0.0965446364031311</v>
       </c>
       <c r="T41">
-        <v>0.9906173638484523</v>
+        <v>0.9891074144390931</v>
       </c>
       <c r="U41">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V41">
-        <v>0.05275806968651994</v>
+        <v>0.05658598879477154</v>
       </c>
       <c r="W41">
-        <v>0.210038220788599</v>
+        <v>0.195038220788599</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.4220645574921595</v>
+        <v>0.4526879103581724</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4686,13 +4686,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1426282392797056</v>
+        <v>0.1365665004800889</v>
       </c>
       <c r="C42">
-        <v>-1570.855265823187</v>
+        <v>-619.1511257956172</v>
       </c>
       <c r="D42">
-        <v>14346.82272877594</v>
+        <v>15298.52686880351</v>
       </c>
       <c r="E42">
         <v>2602.883008101311</v>
@@ -4719,37 +4719,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M42">
-        <v>3740.403586092151</v>
+        <v>3487.373416173164</v>
       </c>
       <c r="N42">
-        <v>-2201.179096296232</v>
+        <v>-1948.148926377245</v>
       </c>
       <c r="O42">
-        <v>-275.147387037029</v>
+        <v>-243.5186157971556</v>
       </c>
       <c r="P42">
-        <v>-1926.031709259203</v>
+        <v>-1704.630310580089</v>
       </c>
       <c r="Q42">
-        <v>-904.0317092592031</v>
+        <v>-682.6303105800894</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.0974932783425444</v>
+        <v>0.09739038034318329</v>
       </c>
       <c r="T42">
-        <v>1.007127653245927</v>
+        <v>1.005592538013078</v>
       </c>
       <c r="U42">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V42">
-        <v>0.05143911794435695</v>
+        <v>0.05517133907490225</v>
       </c>
       <c r="W42">
-        <v>0.2103306806854474</v>
+        <v>0.1953306806854473</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.4115129435548556</v>
+        <v>0.441370712599218</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4768,13 +4768,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1443876054463309</v>
+        <v>0.1381758666467142</v>
       </c>
       <c r="C43">
-        <v>-2248.601504494876</v>
+        <v>-1307.397986941671</v>
       </c>
       <c r="D43">
-        <v>14090.79343996923</v>
+        <v>15031.99695752244</v>
       </c>
       <c r="E43">
         <v>3024.599957966293</v>
@@ -4801,37 +4801,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M43">
-        <v>3833.913675744456</v>
+        <v>3574.557751577493</v>
       </c>
       <c r="N43">
-        <v>-2294.689185948537</v>
+        <v>-2035.333261781575</v>
       </c>
       <c r="O43">
-        <v>-286.8361482435672</v>
+        <v>-254.4166577226969</v>
       </c>
       <c r="P43">
-        <v>-2007.85303770497</v>
+        <v>-1780.916604058878</v>
       </c>
       <c r="Q43">
-        <v>-985.8530377049701</v>
+        <v>-758.916604058878</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.09836943560258754</v>
+        <v>0.09826479356933893</v>
       </c>
       <c r="T43">
-        <v>1.024197613470434</v>
+        <v>1.022636479335334</v>
       </c>
       <c r="U43">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V43">
-        <v>0.05018450531156773</v>
+        <v>0.05382569665844121</v>
       </c>
       <c r="W43">
-        <v>0.2106088742458641</v>
+        <v>0.1956088742458641</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.4014760424925419</v>
+        <v>0.4306055732675297</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4850,13 +4850,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1461469716129563</v>
+        <v>0.1397852328133396</v>
       </c>
       <c r="C44">
-        <v>-2917.369908337032</v>
+        <v>-1986.516941314079</v>
       </c>
       <c r="D44">
-        <v>13843.74198599205</v>
+        <v>14774.594953015</v>
       </c>
       <c r="E44">
         <v>3446.316907831268</v>
@@ -4883,37 +4883,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M44">
-        <v>3927.423765396758</v>
+        <v>3661.742086981822</v>
       </c>
       <c r="N44">
-        <v>-2388.19927560084</v>
+        <v>-2122.517597185903</v>
       </c>
       <c r="O44">
-        <v>-298.524909450105</v>
+        <v>-265.3146996482379</v>
       </c>
       <c r="P44">
-        <v>-2089.674366150735</v>
+        <v>-1857.202897537666</v>
       </c>
       <c r="Q44">
-        <v>-1067.674366150735</v>
+        <v>-835.2028975376656</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.09927580518194248</v>
+        <v>0.09916935897570683</v>
       </c>
       <c r="T44">
-        <v>1.041856193013027</v>
+        <v>1.04026814277215</v>
       </c>
       <c r="U44">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V44">
-        <v>0.04898963613748281</v>
+        <v>0.05254413245228785</v>
       </c>
       <c r="W44">
-        <v>0.21087382049388</v>
+        <v>0.1958738204938801</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3919170890998624</v>
+        <v>0.4203530596183028</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4932,13 +4932,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1479063377795816</v>
+        <v>0.1413945989799649</v>
       </c>
       <c r="C45">
-        <v>-3577.624561142877</v>
+        <v>-2656.969002751201</v>
       </c>
       <c r="D45">
-        <v>13605.20428305118</v>
+        <v>14525.85984144286</v>
       </c>
       <c r="E45">
         <v>3868.033857696246</v>
@@ -4965,37 +4965,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M45">
-        <v>4020.933855049062</v>
+        <v>3748.926422386151</v>
       </c>
       <c r="N45">
-        <v>-2481.709365253144</v>
+        <v>-2209.701932590232</v>
       </c>
       <c r="O45">
-        <v>-310.213670656643</v>
+        <v>-276.2127415737791</v>
       </c>
       <c r="P45">
-        <v>-2171.495694596501</v>
+        <v>-1933.489191016453</v>
       </c>
       <c r="Q45">
-        <v>-1149.495694596501</v>
+        <v>-911.4891910164533</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1002139772026783</v>
+        <v>0.1001056635191403</v>
       </c>
       <c r="T45">
-        <v>1.060134371837817</v>
+        <v>1.058518461066398</v>
       </c>
       <c r="U45">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V45">
-        <v>0.04785034227382041</v>
+        <v>0.05132217588363</v>
       </c>
       <c r="W45">
-        <v>0.2111264436605929</v>
+        <v>0.1961264436605929</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3828027381905633</v>
+        <v>0.41057740706904</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5014,13 +5014,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1496657039462069</v>
+        <v>0.1430039651465903</v>
       </c>
       <c r="C46">
-        <v>-4229.798102512043</v>
+        <v>-3319.184653823531</v>
       </c>
       <c r="D46">
-        <v>13374.747691547</v>
+        <v>14285.36114023551</v>
       </c>
       <c r="E46">
         <v>4289.750807561224</v>
@@ -5047,37 +5047,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M46">
-        <v>4114.443944701366</v>
+        <v>3836.11075779048</v>
       </c>
       <c r="N46">
-        <v>-2575.219454905448</v>
+        <v>-2296.886267994562</v>
       </c>
       <c r="O46">
-        <v>-321.902431863181</v>
+        <v>-287.1107834993202</v>
       </c>
       <c r="P46">
-        <v>-2253.317023042267</v>
+        <v>-2009.775484495242</v>
       </c>
       <c r="Q46">
-        <v>-1231.317023042267</v>
+        <v>-987.7754844952417</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1011856553670119</v>
+        <v>0.1010754075105535</v>
       </c>
       <c r="T46">
-        <v>1.079065342763493</v>
+        <v>1.077420576442583</v>
       </c>
       <c r="U46">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V46">
-        <v>0.04676283449486994</v>
+        <v>0.05015576279536568</v>
       </c>
       <c r="W46">
-        <v>0.2113675839560916</v>
+        <v>0.1963675839560916</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3741026759589595</v>
+        <v>0.4012461023629255</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5096,13 +5096,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1514250701128323</v>
+        <v>0.1446133313132156</v>
       </c>
       <c r="C47">
-        <v>-4874.294346634737</v>
+        <v>-3973.5663321374</v>
       </c>
       <c r="D47">
-        <v>13151.96839728928</v>
+        <v>14052.69641178662</v>
       </c>
       <c r="E47">
         <v>4711.467757426202</v>
@@ -5129,37 +5129,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M47">
-        <v>4207.95403435367</v>
+        <v>3923.295093194809</v>
       </c>
       <c r="N47">
-        <v>-2668.729544557752</v>
+        <v>-2384.070603398891</v>
       </c>
       <c r="O47">
-        <v>-333.5911930697189</v>
+        <v>-298.0088254248614</v>
       </c>
       <c r="P47">
-        <v>-2335.138351488033</v>
+        <v>-2086.06177797403</v>
       </c>
       <c r="Q47">
-        <v>-1313.138351488033</v>
+        <v>-1064.06177797403</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1021926672827757</v>
+        <v>0.1020804149198363</v>
       </c>
       <c r="T47">
-        <v>1.09868471263192</v>
+        <v>1.097010041468812</v>
       </c>
       <c r="U47">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V47">
-        <v>0.04572366039498395</v>
+        <v>0.049041190288802</v>
       </c>
       <c r="W47">
-        <v>0.2115980069051236</v>
+        <v>0.1965980069051236</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3657892831598716</v>
+        <v>0.392329522310416</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5178,13 +5178,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1531844362794576</v>
+        <v>0.146222697479841</v>
       </c>
       <c r="C48">
-        <v>-5511.49064364178</v>
+        <v>-4620.490677566782</v>
       </c>
       <c r="D48">
-        <v>12936.48905014721</v>
+        <v>13827.48901622221</v>
       </c>
       <c r="E48">
         <v>5133.184707291181</v>
@@ -5211,37 +5211,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M48">
-        <v>4301.464124005974</v>
+        <v>4010.479428599138</v>
       </c>
       <c r="N48">
-        <v>-2762.239634210055</v>
+        <v>-2471.25493880322</v>
       </c>
       <c r="O48">
-        <v>-345.2799542762569</v>
+        <v>-308.9068673504025</v>
       </c>
       <c r="P48">
-        <v>-2416.959679933798</v>
+        <v>-2162.348071452817</v>
       </c>
       <c r="Q48">
-        <v>-1394.959679933798</v>
+        <v>-1140.348071452817</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1032369759361605</v>
+        <v>0.1031226448257592</v>
       </c>
       <c r="T48">
-        <v>1.119030725828807</v>
+        <v>1.117325042236753</v>
       </c>
       <c r="U48">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V48">
-        <v>0.04472966777770169</v>
+        <v>0.04797507745643674</v>
       </c>
       <c r="W48">
-        <v>0.2118184114650674</v>
+        <v>0.1968184114650674</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3578373422216135</v>
+        <v>0.3838006196514939</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5260,13 +5260,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.154943802446083</v>
+        <v>0.1478320636464663</v>
       </c>
       <c r="C49">
-        <v>-6141.740012569137</v>
+        <v>-5260.310566809705</v>
       </c>
       <c r="D49">
-        <v>12727.95663108484</v>
+        <v>13609.38607684427</v>
       </c>
       <c r="E49">
         <v>5554.901657156159</v>
@@ -5293,37 +5293,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M49">
-        <v>4394.974213658277</v>
+        <v>4097.663764003468</v>
       </c>
       <c r="N49">
-        <v>-2855.749723862359</v>
+        <v>-2558.439274207549</v>
       </c>
       <c r="O49">
-        <v>-356.9687154827948</v>
+        <v>-319.8049092759437</v>
       </c>
       <c r="P49">
-        <v>-2498.781008379564</v>
+        <v>-2238.634364931605</v>
       </c>
       <c r="Q49">
-        <v>-1476.781008379564</v>
+        <v>-1216.634364931605</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1043206924632578</v>
+        <v>0.1042042041620943</v>
       </c>
       <c r="T49">
-        <v>1.140144513108596</v>
+        <v>1.138406646807258</v>
       </c>
       <c r="U49">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V49">
-        <v>0.04377797271860166</v>
+        <v>0.04695433112757638</v>
       </c>
       <c r="W49">
-        <v>0.2120294371075667</v>
+        <v>0.1970294371075667</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3502237817488132</v>
+        <v>0.3756346490206111</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5342,13 +5342,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1567031686127083</v>
+        <v>0.1494414298130916</v>
       </c>
       <c r="C50">
-        <v>-6765.373071298469</v>
+        <v>-5893.356958386494</v>
       </c>
       <c r="D50">
-        <v>12526.04052222048</v>
+        <v>13398.05663513246</v>
       </c>
       <c r="E50">
         <v>5976.618607021137</v>
@@ -5375,37 +5375,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M50">
-        <v>4488.484303310582</v>
+        <v>4184.848099407796</v>
       </c>
       <c r="N50">
-        <v>-2949.259813514663</v>
+        <v>-2645.623609611878</v>
       </c>
       <c r="O50">
-        <v>-368.6574766893329</v>
+        <v>-330.7029512014847</v>
       </c>
       <c r="P50">
-        <v>-2580.60233682533</v>
+        <v>-2314.920658410393</v>
       </c>
       <c r="Q50">
-        <v>-1558.60233682533</v>
+        <v>-1292.920658410393</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1054460903952436</v>
+        <v>0.1053273619344423</v>
       </c>
       <c r="T50">
-        <v>1.162070369129915</v>
+        <v>1.160299082322782</v>
       </c>
       <c r="U50">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V50">
-        <v>0.04286593162029745</v>
+        <v>0.04597611589575188</v>
       </c>
       <c r="W50">
-        <v>0.2122316700149618</v>
+        <v>0.1972316700149618</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3429274529623796</v>
+        <v>0.367808927166015</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5424,13 +5424,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1584625347793336</v>
+        <v>0.151050795979717</v>
       </c>
       <c r="C51">
-        <v>-7382.699785667126</v>
+        <v>-6519.940568369344</v>
       </c>
       <c r="D51">
-        <v>12330.4307577168</v>
+        <v>13193.18997501459</v>
       </c>
       <c r="E51">
         <v>6398.335556886115</v>
@@ -5457,37 +5457,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M51">
-        <v>4581.994392962885</v>
+        <v>4272.032434812126</v>
       </c>
       <c r="N51">
-        <v>-3042.769903166967</v>
+        <v>-2732.807945016207</v>
       </c>
       <c r="O51">
-        <v>-380.3462378958708</v>
+        <v>-341.6009931270259</v>
       </c>
       <c r="P51">
-        <v>-2662.423665271096</v>
+        <v>-2391.206951889181</v>
       </c>
       <c r="Q51">
-        <v>-1640.423665271096</v>
+        <v>-1369.206951889181</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.106615621579464</v>
+        <v>0.1064945651096274</v>
       </c>
       <c r="T51">
-        <v>1.184856062642267</v>
+        <v>1.183050044721268</v>
       </c>
       <c r="U51">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V51">
-        <v>0.04199111668927097</v>
+        <v>0.04503782781624673</v>
       </c>
       <c r="W51">
-        <v>0.2124256485179735</v>
+        <v>0.1974256485179735</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3359289335141677</v>
+        <v>0.3603026225299739</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5506,13 +5506,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.160221900945959</v>
+        <v>0.1526601621463423</v>
       </c>
       <c r="C52">
-        <v>-7994.011057210866</v>
+        <v>-7140.353394687998</v>
       </c>
       <c r="D52">
-        <v>12140.83643603804</v>
+        <v>12994.49409856091</v>
       </c>
       <c r="E52">
         <v>6820.052506751093</v>
@@ -5539,37 +5539,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M52">
-        <v>4675.504482615189</v>
+        <v>4359.216770216455</v>
       </c>
       <c r="N52">
-        <v>-3136.27999281927</v>
+        <v>-2819.992280420537</v>
       </c>
       <c r="O52">
-        <v>-392.0349991024088</v>
+        <v>-352.4990350525671</v>
       </c>
       <c r="P52">
-        <v>-2744.244993716862</v>
+        <v>-2467.493245367969</v>
       </c>
       <c r="Q52">
-        <v>-1722.244993716862</v>
+        <v>-1445.493245367969</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1078319340110533</v>
+        <v>0.1077084564118199</v>
       </c>
       <c r="T52">
-        <v>1.208553183895112</v>
+        <v>1.206711045615694</v>
       </c>
       <c r="U52">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V52">
-        <v>0.04115129435548555</v>
+        <v>0.04413707125992179</v>
       </c>
       <c r="W52">
-        <v>0.2126118678808647</v>
+        <v>0.1976118678808647</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3292103548438844</v>
+        <v>0.3530965700793743</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5588,13 +5588,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1619812671125843</v>
+        <v>0.1542695283129676</v>
       </c>
       <c r="C53">
-        <v>-8599.580166644722</v>
+        <v>-7754.87010573841</v>
       </c>
       <c r="D53">
-        <v>11956.98427646916</v>
+        <v>12801.69433737548</v>
       </c>
       <c r="E53">
         <v>7241.769456616072</v>
@@ -5621,37 +5621,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M53">
-        <v>4769.014572267492</v>
+        <v>4446.401105620784</v>
       </c>
       <c r="N53">
-        <v>-3229.790082471574</v>
+        <v>-2907.176615824865</v>
       </c>
       <c r="O53">
-        <v>-403.7237603089467</v>
+        <v>-363.3970769781081</v>
       </c>
       <c r="P53">
-        <v>-2826.066322162627</v>
+        <v>-2543.779538846757</v>
       </c>
       <c r="Q53">
-        <v>-1804.066322162627</v>
+        <v>-1521.779538846757</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1090978918480136</v>
+        <v>0.1089718942977755</v>
       </c>
       <c r="T53">
-        <v>1.233217534586849</v>
+        <v>1.231337801648667</v>
       </c>
       <c r="U53">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V53">
-        <v>0.04034440623086819</v>
+        <v>0.04327163849011941</v>
       </c>
       <c r="W53">
-        <v>0.2127907845236425</v>
+        <v>0.1977907845236425</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3227552498469455</v>
+        <v>0.3461731079209553</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5670,13 +5670,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1637406332792097</v>
+        <v>0.155878894479593</v>
       </c>
       <c r="C54">
-        <v>-9199.664088146093</v>
+        <v>-8363.749307181697</v>
       </c>
       <c r="D54">
-        <v>11778.61730483277</v>
+        <v>12614.53208579717</v>
       </c>
       <c r="E54">
         <v>7663.48640648105</v>
@@ -5703,37 +5703,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M54">
-        <v>4862.524661919796</v>
+        <v>4533.585441025113</v>
       </c>
       <c r="N54">
-        <v>-3323.300172123877</v>
+        <v>-2994.360951229195</v>
       </c>
       <c r="O54">
-        <v>-415.4125215154847</v>
+        <v>-374.2951189036493</v>
       </c>
       <c r="P54">
-        <v>-2907.887650608393</v>
+        <v>-2620.065832325545</v>
       </c>
       <c r="Q54">
-        <v>-1885.887650608393</v>
+        <v>-1598.065832325545</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1104165979281805</v>
+        <v>0.1102879754289791</v>
       </c>
       <c r="T54">
-        <v>1.258909566557408</v>
+        <v>1.256990672516348</v>
       </c>
       <c r="U54">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V54">
-        <v>0.03956855226488996</v>
+        <v>0.04243949159607865</v>
       </c>
       <c r="W54">
-        <v>0.2129628197570828</v>
+        <v>0.1979628197570827</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3165484181191197</v>
+        <v>0.3395159327686292</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5752,13 +5752,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.165499999445835</v>
+        <v>0.1574882606462183</v>
       </c>
       <c r="C55">
-        <v>-9794.504687732791</v>
+        <v>-8967.234699219818</v>
       </c>
       <c r="D55">
-        <v>11605.49365511105</v>
+        <v>12432.76364362402</v>
       </c>
       <c r="E55">
         <v>8085.203356346028</v>
@@ -5785,37 +5785,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M55">
-        <v>4956.034751572101</v>
+        <v>4620.769776429443</v>
       </c>
       <c r="N55">
-        <v>-3416.810261776182</v>
+        <v>-3081.545286633524</v>
       </c>
       <c r="O55">
-        <v>-427.1012827220227</v>
+        <v>-385.1931608291905</v>
       </c>
       <c r="P55">
-        <v>-2989.708979054159</v>
+        <v>-2696.352125804333</v>
       </c>
       <c r="Q55">
-        <v>-1967.708979054159</v>
+        <v>-1674.352125804333</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.111791419160695</v>
+        <v>0.1116600600125744</v>
       </c>
       <c r="T55">
-        <v>1.285694876484162</v>
+        <v>1.283735154910312</v>
       </c>
       <c r="U55">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V55">
-        <v>0.03882197580706184</v>
+        <v>0.04163874647162433</v>
       </c>
       <c r="W55">
-        <v>0.2131283630949215</v>
+        <v>0.1981283630949214</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3105758064564947</v>
+        <v>0.3331099717729947</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5834,13 +5834,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1672593656124604</v>
+        <v>0.1590976268128437</v>
       </c>
       <c r="C56">
-        <v>-10384.32981748845</v>
+        <v>-9565.556135238341</v>
       </c>
       <c r="D56">
-        <v>11437.38547522037</v>
+        <v>12256.15915747048</v>
       </c>
       <c r="E56">
         <v>8506.920306211006</v>
@@ -5867,37 +5867,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M56">
-        <v>5049.544841224404</v>
+        <v>4707.954111833771</v>
       </c>
       <c r="N56">
-        <v>-3510.320351428486</v>
+        <v>-3168.729622037853</v>
       </c>
       <c r="O56">
-        <v>-438.7900439285607</v>
+        <v>-396.0912027547316</v>
       </c>
       <c r="P56">
-        <v>-3071.530307499925</v>
+        <v>-2772.638419283121</v>
       </c>
       <c r="Q56">
-        <v>-2049.530307499925</v>
+        <v>-1750.638419283121</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1132260152294058</v>
+        <v>0.1130918004476304</v>
       </c>
       <c r="T56">
-        <v>1.313644765103383</v>
+        <v>1.311642440886624</v>
       </c>
       <c r="U56">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V56">
-        <v>0.03810305032915329</v>
+        <v>0.04086765857400167</v>
       </c>
       <c r="W56">
-        <v>0.2132877751980254</v>
+        <v>0.1982877751980254</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3048244026332263</v>
+        <v>0.3269412685920133</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5916,13 +5916,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1690187317790857</v>
+        <v>0.1607069929794691</v>
       </c>
       <c r="C57">
-        <v>-10969.35431604523</v>
+        <v>-10158.93059148618</v>
       </c>
       <c r="D57">
-        <v>11274.07792652857</v>
+        <v>12084.50165108762</v>
       </c>
       <c r="E57">
         <v>8928.637256075985</v>
@@ -5949,37 +5949,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M57">
-        <v>5143.054930876708</v>
+        <v>4795.138447238101</v>
       </c>
       <c r="N57">
-        <v>-3603.830441080789</v>
+        <v>-3255.913957442182</v>
       </c>
       <c r="O57">
-        <v>-450.4788051350986</v>
+        <v>-406.9892446802727</v>
       </c>
       <c r="P57">
-        <v>-3153.35163594569</v>
+        <v>-2848.924712761909</v>
       </c>
       <c r="Q57">
-        <v>-2131.35163594569</v>
+        <v>-1826.924712761909</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1147243711233926</v>
+        <v>0.1145871737909111</v>
       </c>
       <c r="T57">
-        <v>1.342836870994569</v>
+        <v>1.340790050684104</v>
       </c>
       <c r="U57">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V57">
-        <v>0.03741026759589595</v>
+        <v>0.04012461023629255</v>
       </c>
       <c r="W57">
-        <v>0.2134413904973801</v>
+        <v>0.1984413904973801</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2992821407671676</v>
+        <v>0.3209968818903404</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5998,13 +5998,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.170778097945711</v>
+        <v>0.1623163591460944</v>
       </c>
       <c r="C58">
-        <v>-11549.78092456134</v>
+        <v>-10747.56305639401</v>
       </c>
       <c r="D58">
-        <v>11115.36826787744</v>
+        <v>11917.58613604476</v>
       </c>
       <c r="E58">
         <v>9350.354205940963</v>
@@ -6031,37 +6031,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M58">
-        <v>5236.565020529011</v>
+        <v>4882.32278264243</v>
       </c>
       <c r="N58">
-        <v>-3697.340530733093</v>
+        <v>-3343.098292846511</v>
       </c>
       <c r="O58">
-        <v>-462.1675663416366</v>
+        <v>-417.8872866058139</v>
       </c>
       <c r="P58">
-        <v>-3235.172964391456</v>
+        <v>-2925.211006240697</v>
       </c>
       <c r="Q58">
-        <v>-2213.172964391456</v>
+        <v>-1903.211006240697</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1162908341034697</v>
+        <v>0.1161505186497954</v>
       </c>
       <c r="T58">
-        <v>1.3733558907899</v>
+        <v>1.371262551836016</v>
       </c>
       <c r="U58">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V58">
-        <v>0.0367422271031121</v>
+        <v>0.03940809933921589</v>
       </c>
       <c r="W58">
-        <v>0.2135895195360435</v>
+        <v>0.1985895195360436</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2939378168248968</v>
+        <v>0.3152647947137271</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6080,13 +6080,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1725374641123364</v>
+        <v>0.1639257253127197</v>
       </c>
       <c r="C59">
-        <v>-12125.80112640516</v>
+        <v>-11331.64734719525</v>
       </c>
       <c r="D59">
-        <v>10961.0650158986</v>
+        <v>11755.21879510851</v>
       </c>
       <c r="E59">
         <v>9772.071155805945</v>
@@ -6113,37 +6113,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M59">
-        <v>5330.075110181317</v>
+        <v>4969.507118046759</v>
       </c>
       <c r="N59">
-        <v>-3790.850620385398</v>
+        <v>-3430.282628250841</v>
       </c>
       <c r="O59">
-        <v>-473.8563275481748</v>
+        <v>-428.7853285313551</v>
       </c>
       <c r="P59">
-        <v>-3316.994292837223</v>
+        <v>-3001.497299719486</v>
       </c>
       <c r="Q59">
-        <v>-2294.994292837223</v>
+        <v>-1979.497299719486</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1179301558268062</v>
+        <v>0.1177865772230464</v>
       </c>
       <c r="T59">
-        <v>1.405294399878037</v>
+        <v>1.4031523786229</v>
       </c>
       <c r="U59">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V59">
-        <v>0.0360976266276189</v>
+        <v>0.03871672917536999</v>
       </c>
       <c r="W59">
-        <v>0.2137324510645785</v>
+        <v>0.1987324510645785</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2887810130209512</v>
+        <v>0.3097338334029599</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6162,13 +6162,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1742968302789617</v>
+        <v>0.165535091479345</v>
       </c>
       <c r="C60">
-        <v>-12697.59591785802</v>
+        <v>-11911.36686068953</v>
       </c>
       <c r="D60">
-        <v>10810.98717431071</v>
+        <v>11597.2162314792</v>
       </c>
       <c r="E60">
         <v>10193.78810567092</v>
@@ -6195,37 +6195,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M60">
-        <v>5423.585199833618</v>
+        <v>5056.691453451087</v>
       </c>
       <c r="N60">
-        <v>-3884.3607100377</v>
+        <v>-3517.466963655168</v>
       </c>
       <c r="O60">
-        <v>-485.5450887547125</v>
+        <v>-439.6833704568961</v>
       </c>
       <c r="P60">
-        <v>-3398.815621282987</v>
+        <v>-3077.783593198272</v>
       </c>
       <c r="Q60">
-        <v>-2376.815621282987</v>
+        <v>-2055.783593198272</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1196475404893491</v>
+        <v>0.1195005433474047</v>
       </c>
       <c r="T60">
-        <v>1.438753790351323</v>
+        <v>1.436560768590111</v>
       </c>
       <c r="U60">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V60">
-        <v>0.03547525375472893</v>
+        <v>0.03804919936200155</v>
       </c>
       <c r="W60">
-        <v>0.2138704539197157</v>
+        <v>0.1988704539197156</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2838020300378314</v>
+        <v>0.3043935948960125</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6244,13 +6244,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1760561964455871</v>
+        <v>0.1671444576459704</v>
       </c>
       <c r="C61">
-        <v>-13265.33651635801</v>
+        <v>-12486.89526426288</v>
       </c>
       <c r="D61">
-        <v>10664.9635256757</v>
+        <v>11443.40477777083</v>
       </c>
       <c r="E61">
         <v>10615.50505553589</v>
@@ -6277,37 +6277,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M61">
-        <v>5517.095289485922</v>
+        <v>5143.875788855416</v>
       </c>
       <c r="N61">
-        <v>-3977.870799690003</v>
+        <v>-3604.651299059498</v>
       </c>
       <c r="O61">
-        <v>-497.2338499612504</v>
+        <v>-450.5814123824372</v>
       </c>
       <c r="P61">
-        <v>-3480.636949728753</v>
+        <v>-3154.069886677061</v>
       </c>
       <c r="Q61">
-        <v>-2458.636949728753</v>
+        <v>-2132.069886677061</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1214487000134796</v>
+        <v>0.1212981175753902</v>
       </c>
       <c r="T61">
-        <v>1.473845346213551</v>
+        <v>1.471598836116699</v>
       </c>
       <c r="U61">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V61">
-        <v>0.03487397826736064</v>
+        <v>0.03740429767789983</v>
       </c>
       <c r="W61">
-        <v>0.2140037787119668</v>
+        <v>0.1990037787119668</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2789918261388852</v>
+        <v>0.2992343814231987</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6326,13 +6326,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1778155626122124</v>
+        <v>0.1687538238125957</v>
       </c>
       <c r="C62">
-        <v>-13829.18501211114</v>
+        <v>-13058.39713263852</v>
       </c>
       <c r="D62">
-        <v>10522.83197978755</v>
+        <v>11293.61985926017</v>
       </c>
       <c r="E62">
         <v>11037.22200540088</v>
@@ -6359,37 +6359,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M62">
-        <v>5610.605379138226</v>
+        <v>5231.060124259746</v>
       </c>
       <c r="N62">
-        <v>-4071.380889342308</v>
+        <v>-3691.835634463827</v>
       </c>
       <c r="O62">
-        <v>-508.9226111677885</v>
+        <v>-461.4794543079784</v>
       </c>
       <c r="P62">
-        <v>-3562.458278174519</v>
+        <v>-3230.356180155849</v>
       </c>
       <c r="Q62">
-        <v>-2540.458278174519</v>
+        <v>-2208.356180155849</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1233399175138166</v>
+        <v>0.1231855705147749</v>
       </c>
       <c r="T62">
-        <v>1.51069147986889</v>
+        <v>1.508388807019617</v>
       </c>
       <c r="U62">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V62">
-        <v>0.03429274529623796</v>
+        <v>0.0367808927166015</v>
       </c>
       <c r="W62">
-        <v>0.2141326593444763</v>
+        <v>0.1991326593444763</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2743419623699037</v>
+        <v>0.294247141732812</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6408,13 +6408,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1795749287788378</v>
+        <v>0.1703631899792211</v>
       </c>
       <c r="C63">
-        <v>-14389.29496828396</v>
+        <v>-13626.02853526642</v>
       </c>
       <c r="D63">
-        <v>10384.43897347971</v>
+        <v>11147.70540649725</v>
       </c>
       <c r="E63">
         <v>11458.93895526585</v>
@@ -6441,37 +6441,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M63">
-        <v>5704.115468790531</v>
+        <v>5318.244459664075</v>
       </c>
       <c r="N63">
-        <v>-4164.890978994612</v>
+        <v>-3779.019969868157</v>
       </c>
       <c r="O63">
-        <v>-520.6113723743265</v>
+        <v>-472.3774962335196</v>
       </c>
       <c r="P63">
-        <v>-3644.279606620285</v>
+        <v>-3306.642473634637</v>
       </c>
       <c r="Q63">
-        <v>-2622.279606620285</v>
+        <v>-2284.642473634637</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1253281205269914</v>
+        <v>0.1251698159125897</v>
       </c>
       <c r="T63">
-        <v>1.549427158839887</v>
+        <v>1.547065443097043</v>
       </c>
       <c r="U63">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V63">
-        <v>0.03373056914384061</v>
+        <v>0.03617792726223098</v>
       </c>
       <c r="W63">
-        <v>0.2142573143824772</v>
+        <v>0.1992573143824772</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.269844553150725</v>
+        <v>0.2894234180978479</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6490,13 +6490,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1813342949454631</v>
+        <v>0.1719725561458464</v>
       </c>
       <c r="C64">
-        <v>-14945.81197444965</v>
+        <v>-14189.93757875899</v>
       </c>
       <c r="D64">
-        <v>10249.638917179</v>
+        <v>11005.51331286966</v>
       </c>
       <c r="E64">
         <v>11880.65590513083</v>
@@ -6523,37 +6523,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M64">
-        <v>5797.625558442835</v>
+        <v>5405.428795068405</v>
       </c>
       <c r="N64">
-        <v>-4258.401068646916</v>
+        <v>-3866.204305272486</v>
       </c>
       <c r="O64">
-        <v>-532.3001335808644</v>
+        <v>-483.2755381590608</v>
       </c>
       <c r="P64">
-        <v>-3726.100935066051</v>
+        <v>-3382.928767113425</v>
       </c>
       <c r="Q64">
-        <v>-2704.100935066051</v>
+        <v>-2360.928767113425</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1274209658040175</v>
+        <v>0.1272584952787104</v>
       </c>
       <c r="T64">
-        <v>1.590201557756726</v>
+        <v>1.587777691599597</v>
       </c>
       <c r="U64">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V64">
-        <v>0.03318652770603674</v>
+        <v>0.03559441230638855</v>
       </c>
       <c r="W64">
-        <v>0.2143779482902201</v>
+        <v>0.1993779482902201</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.265492221648294</v>
+        <v>0.2847552984511084</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6572,13 +6572,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1830936611120884</v>
+        <v>0.1735819223124718</v>
       </c>
       <c r="C65">
-        <v>-15498.87415748085</v>
+        <v>-14750.2649083361</v>
       </c>
       <c r="D65">
-        <v>10118.29368401278</v>
+        <v>10866.90293315753</v>
       </c>
       <c r="E65">
         <v>12302.37285499581</v>
@@ -6605,37 +6605,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M65">
-        <v>5891.135648095138</v>
+        <v>5492.613130472733</v>
       </c>
       <c r="N65">
-        <v>-4351.911158299219</v>
+        <v>-3953.388640676815</v>
       </c>
       <c r="O65">
-        <v>-543.9888947874024</v>
+        <v>-494.1735800846018</v>
       </c>
       <c r="P65">
-        <v>-3807.922263511817</v>
+        <v>-3459.215060592213</v>
       </c>
       <c r="Q65">
-        <v>-2785.922263511817</v>
+        <v>-2437.215060592213</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1296269378527747</v>
+        <v>0.1294600762321891</v>
       </c>
       <c r="T65">
-        <v>1.633179978236638</v>
+        <v>1.63069060218337</v>
       </c>
       <c r="U65">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V65">
-        <v>0.03265975742498854</v>
+        <v>0.03502942163485857</v>
       </c>
       <c r="W65">
-        <v>0.2144947525500981</v>
+        <v>0.1994947525500981</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2612780593999083</v>
+        <v>0.2802353730788686</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6654,13 +6654,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1848530272787138</v>
+        <v>0.1751912884790971</v>
       </c>
       <c r="C66">
-        <v>-16048.61265365815</v>
+        <v>-15307.14417184826</v>
       </c>
       <c r="D66">
-        <v>9990.272137700453</v>
+        <v>10731.74061951034</v>
       </c>
       <c r="E66">
         <v>12724.08980486079</v>
@@ -6687,37 +6687,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M66">
-        <v>5984.645737747442</v>
+        <v>5579.797465877063</v>
       </c>
       <c r="N66">
-        <v>-4445.421247951523</v>
+        <v>-4040.572976081144</v>
       </c>
       <c r="O66">
-        <v>-555.6776559939403</v>
+        <v>-505.071622010143</v>
       </c>
       <c r="P66">
-        <v>-3889.743591957582</v>
+        <v>-3535.501354071001</v>
       </c>
       <c r="Q66">
-        <v>-2867.743591957582</v>
+        <v>-2513.501354071001</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1319554639042407</v>
+        <v>0.1317839672386388</v>
       </c>
       <c r="T66">
-        <v>1.678546088743211</v>
+        <v>1.67598756335513</v>
       </c>
       <c r="U66">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V66">
-        <v>0.03214944871522309</v>
+        <v>0.03448208692181391</v>
       </c>
       <c r="W66">
-        <v>0.2146079066768549</v>
+        <v>0.1996079066768549</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2571955897217848</v>
+        <v>0.2758566953745112</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6736,13 +6736,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1866123934453391</v>
+        <v>0.1768006546457224</v>
       </c>
       <c r="C67">
-        <v>-16595.15204538634</v>
+        <v>-15860.70244959627</v>
       </c>
       <c r="D67">
-        <v>9865.449695837242</v>
+        <v>10599.89929162731</v>
       </c>
       <c r="E67">
         <v>13145.80675472577</v>
@@ -6769,37 +6769,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M67">
-        <v>6078.155827399746</v>
+        <v>5666.981801281392</v>
       </c>
       <c r="N67">
-        <v>-4538.931337603828</v>
+        <v>-4127.757311485473</v>
       </c>
       <c r="O67">
-        <v>-567.3664172004785</v>
+        <v>-515.9696639356841</v>
       </c>
       <c r="P67">
-        <v>-3971.56492040335</v>
+        <v>-3611.787647549789</v>
       </c>
       <c r="Q67">
-        <v>-2949.56492040335</v>
+        <v>-2589.787647549789</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.134417048587219</v>
+        <v>0.1342406520168856</v>
       </c>
       <c r="T67">
-        <v>1.726504548421589</v>
+        <v>1.723872922308134</v>
       </c>
       <c r="U67">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V67">
-        <v>0.03165484181191196</v>
+        <v>0.03395159327686292</v>
       </c>
       <c r="W67">
-        <v>0.214717579138173</v>
+        <v>0.199717579138173</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2532387344952957</v>
+        <v>0.2716127462149034</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6818,13 +6818,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1883717596119645</v>
+        <v>0.1784100208123477</v>
       </c>
       <c r="C68">
-        <v>-17138.61076557554</v>
+        <v>-16411.06065285281</v>
       </c>
       <c r="D68">
-        <v>9743.707925513019</v>
+        <v>10471.25803823575</v>
       </c>
       <c r="E68">
         <v>13567.52370459075</v>
@@ -6851,37 +6851,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M68">
-        <v>6171.66591705205</v>
+        <v>5754.166136685721</v>
       </c>
       <c r="N68">
-        <v>-4632.441427256132</v>
+        <v>-4214.941646889802</v>
       </c>
       <c r="O68">
-        <v>-579.0551784070165</v>
+        <v>-526.8677058612252</v>
       </c>
       <c r="P68">
-        <v>-4053.386248849115</v>
+        <v>-3688.073941028576</v>
       </c>
       <c r="Q68">
-        <v>-3031.386248849115</v>
+        <v>-2666.073941028576</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.137023432369196</v>
+        <v>0.1368418476644411</v>
       </c>
       <c r="T68">
-        <v>1.7772840939634</v>
+        <v>1.774575067081902</v>
       </c>
       <c r="U68">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V68">
-        <v>0.03117522299657996</v>
+        <v>0.03343717519691045</v>
       </c>
       <c r="W68">
-        <v>0.2148239281915724</v>
+        <v>0.1998239281915724</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2494017839726396</v>
+        <v>0.2674974015752837</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6900,13 +6900,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1901311257785898</v>
+        <v>0.1800193869789731</v>
       </c>
       <c r="C69">
-        <v>-17679.10147244651</v>
+        <v>-16958.33389371307</v>
       </c>
       <c r="D69">
-        <v>9624.934168507032</v>
+        <v>10345.70174724047</v>
       </c>
       <c r="E69">
         <v>13989.24065445572</v>
@@ -6933,37 +6933,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M69">
-        <v>6265.176006704353</v>
+        <v>5841.35047209005</v>
       </c>
       <c r="N69">
-        <v>-4725.951516908435</v>
+        <v>-4302.125982294132</v>
       </c>
       <c r="O69">
-        <v>-590.7439396135544</v>
+        <v>-537.7657477867665</v>
       </c>
       <c r="P69">
-        <v>-4135.207577294881</v>
+        <v>-3764.360234507365</v>
       </c>
       <c r="Q69">
-        <v>-3113.207577294881</v>
+        <v>-2742.360234507365</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1397877788046262</v>
+        <v>0.1396006915330605</v>
       </c>
       <c r="T69">
-        <v>1.831141187719867</v>
+        <v>1.828350069114688</v>
       </c>
       <c r="U69">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V69">
-        <v>0.03070992116081011</v>
+        <v>0.03293811288053865</v>
       </c>
       <c r="W69">
-        <v>0.2149271026463629</v>
+        <v>0.1999271026463629</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2456793692864808</v>
+        <v>0.2635049030443092</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6982,13 +6982,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1918904919452151</v>
+        <v>0.1816287531455985</v>
       </c>
       <c r="C70">
-        <v>-18216.73139725319</v>
+        <v>-17502.63182865237</v>
       </c>
       <c r="D70">
-        <v>9509.021193565326</v>
+        <v>10223.12076216614</v>
       </c>
       <c r="E70">
         <v>14410.9576043207</v>
@@ -7015,37 +7015,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M70">
-        <v>6358.686096356657</v>
+        <v>5928.534807494379</v>
       </c>
       <c r="N70">
-        <v>-4819.461606560739</v>
+        <v>-4389.31031769846</v>
       </c>
       <c r="O70">
-        <v>-602.4327008200924</v>
+        <v>-548.6637897123076</v>
       </c>
       <c r="P70">
-        <v>-4217.028905740646</v>
+        <v>-3840.646527986153</v>
       </c>
       <c r="Q70">
-        <v>-3195.028905740646</v>
+        <v>-2818.646527986153</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1427248968922708</v>
+        <v>0.1425319631434687</v>
       </c>
       <c r="T70">
-        <v>1.888364349836113</v>
+        <v>1.885486008774522</v>
       </c>
       <c r="U70">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V70">
-        <v>0.03025830467315114</v>
+        <v>0.03245372886758956</v>
       </c>
       <c r="W70">
-        <v>0.2150272425583654</v>
+        <v>0.2000272425583654</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2420664373852091</v>
+        <v>0.2596298309407163</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7064,13 +7064,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1936498581118405</v>
+        <v>0.1832381193122238</v>
       </c>
       <c r="C71">
-        <v>-18751.60266717864</v>
+        <v>-18044.05897794593</v>
       </c>
       <c r="D71">
-        <v>9395.866873504854</v>
+        <v>10103.41056273756</v>
       </c>
       <c r="E71">
         <v>14832.67455418568</v>
@@ -7097,37 +7097,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M71">
-        <v>6452.196186008961</v>
+        <v>6015.719142898708</v>
       </c>
       <c r="N71">
-        <v>-4912.971696213042</v>
+        <v>-4476.494653102789</v>
       </c>
       <c r="O71">
-        <v>-614.1214620266303</v>
+        <v>-559.5618316378486</v>
       </c>
       <c r="P71">
-        <v>-4298.850234186412</v>
+        <v>-3916.93282146494</v>
       </c>
       <c r="Q71">
-        <v>-3276.850234186412</v>
+        <v>-2894.93282146494</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1458515064694408</v>
+        <v>0.1456523490513225</v>
       </c>
       <c r="T71">
-        <v>1.949279328863084</v>
+        <v>1.946308138089829</v>
       </c>
       <c r="U71">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V71">
-        <v>0.02981977851846779</v>
+        <v>0.03198338497095782</v>
       </c>
       <c r="W71">
-        <v>0.215124479864223</v>
+        <v>0.2001244798642229</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2385582281477424</v>
+        <v>0.2558670797676627</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7146,13 +7146,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1954092242784659</v>
+        <v>0.1848474854788492</v>
       </c>
       <c r="C72">
-        <v>-19283.81260544781</v>
+        <v>-18582.71502290637</v>
       </c>
       <c r="D72">
-        <v>9285.373885100664</v>
+        <v>9986.471467642106</v>
       </c>
       <c r="E72">
         <v>15254.39150405066</v>
@@ -7179,37 +7179,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M72">
-        <v>6545.706275661265</v>
+        <v>6102.903478303037</v>
       </c>
       <c r="N72">
-        <v>-5006.481785865346</v>
+        <v>-4563.678988507119</v>
       </c>
       <c r="O72">
-        <v>-625.8102232331682</v>
+        <v>-570.4598735633899</v>
       </c>
       <c r="P72">
-        <v>-4380.671562632177</v>
+        <v>-3993.219114943729</v>
       </c>
       <c r="Q72">
-        <v>-3358.671562632177</v>
+        <v>-2971.219114943729</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1491865566850888</v>
+        <v>0.1489807606863666</v>
       </c>
       <c r="T72">
-        <v>2.014255306491854</v>
+        <v>2.011185076026157</v>
       </c>
       <c r="U72">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V72">
-        <v>0.02939378168248968</v>
+        <v>0.03152647947137271</v>
       </c>
       <c r="W72">
-        <v>0.2152189389613417</v>
+        <v>0.2002189389613417</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2351502534599175</v>
+        <v>0.2522118357709816</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7228,13 +7228,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1971685904450912</v>
+        <v>0.1864568516454745</v>
       </c>
       <c r="C73">
-        <v>-19813.45401051103</v>
+        <v>-19118.69508271569</v>
       </c>
       <c r="D73">
-        <v>9177.449429902421</v>
+        <v>9872.208357697758</v>
       </c>
       <c r="E73">
         <v>15676.10845391563</v>
@@ -7261,37 +7261,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M73">
-        <v>6639.216365313568</v>
+        <v>6190.087813707366</v>
       </c>
       <c r="N73">
-        <v>-5099.99187551765</v>
+        <v>-4650.863323911448</v>
       </c>
       <c r="O73">
-        <v>-637.4989844397062</v>
+        <v>-581.357915488931</v>
       </c>
       <c r="P73">
-        <v>-4462.492891077944</v>
+        <v>-4069.505408422517</v>
       </c>
       <c r="Q73">
-        <v>-3440.492891077944</v>
+        <v>-3047.505408422517</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.152751610363885</v>
+        <v>0.1525387179514137</v>
       </c>
       <c r="T73">
-        <v>2.083712386026055</v>
+        <v>2.080536285544299</v>
       </c>
       <c r="U73">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V73">
-        <v>0.0289797847573842</v>
+        <v>0.0310824445492407</v>
       </c>
       <c r="W73">
-        <v>0.2153107372388233</v>
+        <v>0.2003107372388233</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2318382780590735</v>
+        <v>0.2486595563939256</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7310,13 +7310,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1989279566117165</v>
+        <v>0.1880662178120998</v>
       </c>
       <c r="C74">
-        <v>-20340.61541598137</v>
+        <v>-19652.08997246755</v>
       </c>
       <c r="D74">
-        <v>9072.004974297051</v>
+        <v>9760.530417810874</v>
       </c>
       <c r="E74">
         <v>16097.82540378061</v>
@@ -7343,37 +7343,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M74">
-        <v>6732.726454965871</v>
+        <v>6277.272149111694</v>
       </c>
       <c r="N74">
-        <v>-5193.501965169953</v>
+        <v>-4738.047659315776</v>
       </c>
       <c r="O74">
-        <v>-649.1877456462441</v>
+        <v>-592.2559574144721</v>
       </c>
       <c r="P74">
-        <v>-4544.314219523709</v>
+        <v>-4145.791701901304</v>
       </c>
       <c r="Q74">
-        <v>-3522.314219523709</v>
+        <v>-3123.791701901304</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1565713107340237</v>
+        <v>0.156350815021107</v>
       </c>
       <c r="T74">
-        <v>2.158130685526985</v>
+        <v>2.154841152885167</v>
       </c>
       <c r="U74">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V74">
-        <v>0.02857728774686497</v>
+        <v>0.03065074393050125</v>
       </c>
       <c r="W74">
-        <v>0.2153999855641526</v>
+        <v>0.2003999855641526</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2286183019749197</v>
+        <v>0.2452059514440099</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7392,13 +7392,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2006873227783418</v>
+        <v>0.1896755839787252</v>
       </c>
       <c r="C75">
-        <v>-20865.38133285624</v>
+        <v>-20182.986443891</v>
       </c>
       <c r="D75">
-        <v>8968.956007287165</v>
+        <v>9651.350896252403</v>
       </c>
       <c r="E75">
         <v>16519.54235364559</v>
@@ -7425,37 +7425,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M75">
-        <v>6826.236544618176</v>
+        <v>6364.456484516024</v>
       </c>
       <c r="N75">
-        <v>-5287.012054822257</v>
+        <v>-4825.231994720105</v>
       </c>
       <c r="O75">
-        <v>-660.8765068527821</v>
+        <v>-603.1539993400131</v>
       </c>
       <c r="P75">
-        <v>-4626.135547969475</v>
+        <v>-4222.077995380092</v>
       </c>
       <c r="Q75">
-        <v>-3604.135547969475</v>
+        <v>-3200.077995380092</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1606739518723209</v>
+        <v>0.1604452896515184</v>
       </c>
       <c r="T75">
-        <v>2.238061451657614</v>
+        <v>2.234650084473506</v>
       </c>
       <c r="U75">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V75">
-        <v>0.02818581805170243</v>
+        <v>0.03023087072597384</v>
       </c>
       <c r="W75">
-        <v>0.2154867887298838</v>
+        <v>0.2004867887298838</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2254865444136195</v>
+        <v>0.2418469658077907</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7474,13 +7474,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2024466889449672</v>
+        <v>0.1912849501453505</v>
       </c>
       <c r="C76">
-        <v>-21387.83247541594</v>
+        <v>-20711.46741009677</v>
       </c>
       <c r="D76">
-        <v>8868.221814592445</v>
+        <v>9544.586879911611</v>
       </c>
       <c r="E76">
         <v>16941.25930351057</v>
@@ -7507,37 +7507,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M76">
-        <v>6919.746634270479</v>
+        <v>6451.640819920353</v>
       </c>
       <c r="N76">
-        <v>-5380.52214447456</v>
+        <v>-4912.416330124435</v>
       </c>
       <c r="O76">
-        <v>-672.56526805932</v>
+        <v>-614.0520412655544</v>
       </c>
       <c r="P76">
-        <v>-4707.95687641524</v>
+        <v>-4298.364288858881</v>
       </c>
       <c r="Q76">
-        <v>-3685.95687641524</v>
+        <v>-3276.364288858881</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1650921807904871</v>
+        <v>0.1648547238688845</v>
       </c>
       <c r="T76">
-        <v>2.32414073825983</v>
+        <v>2.320598164645564</v>
       </c>
       <c r="U76">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V76">
-        <v>0.02780492861857132</v>
+        <v>0.02982234544589311</v>
       </c>
       <c r="W76">
-        <v>0.2155712458641088</v>
+        <v>0.2005712458641088</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2224394289485706</v>
+        <v>0.2385787635671448</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7556,13 +7556,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2042060551115925</v>
+        <v>0.1928943163119758</v>
       </c>
       <c r="C77">
-        <v>-21908.04597206843</v>
+        <v>-21237.6121555699</v>
       </c>
       <c r="D77">
-        <v>8769.725267804937</v>
+        <v>9440.159084303468</v>
       </c>
       <c r="E77">
         <v>17362.97625337555</v>
@@ -7589,37 +7589,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M77">
-        <v>7013.256723922784</v>
+        <v>6538.825155324683</v>
       </c>
       <c r="N77">
-        <v>-5474.032234126866</v>
+        <v>-4999.600665528764</v>
       </c>
       <c r="O77">
-        <v>-684.2540292658582</v>
+        <v>-624.9500831910955</v>
       </c>
       <c r="P77">
-        <v>-4789.778204861008</v>
+        <v>-4374.650582337668</v>
       </c>
       <c r="Q77">
-        <v>-3767.778204861008</v>
+        <v>-3352.650582337668</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1698638680221066</v>
+        <v>0.1696169128236399</v>
       </c>
       <c r="T77">
-        <v>2.417106367790224</v>
+        <v>2.413422091231387</v>
       </c>
       <c r="U77">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V77">
-        <v>0.02743419623699037</v>
+        <v>0.0294247141732812</v>
       </c>
       <c r="W77">
-        <v>0.2156534508080878</v>
+        <v>0.2006534508080878</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2194735698959228</v>
+        <v>0.2353977133862496</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7638,13 +7638,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2059654212782179</v>
+        <v>0.1945036824786012</v>
       </c>
       <c r="C78">
-        <v>-22426.0955622976</v>
+        <v>-21761.49653252616</v>
       </c>
       <c r="D78">
-        <v>8673.39262744074</v>
+        <v>9337.99165721218</v>
       </c>
       <c r="E78">
         <v>17784.69320324053</v>
@@ -7671,37 +7671,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M78">
-        <v>7106.766813575087</v>
+        <v>6626.009490729012</v>
       </c>
       <c r="N78">
-        <v>-5567.542323779169</v>
+        <v>-5086.785000933094</v>
       </c>
       <c r="O78">
-        <v>-695.9427904723962</v>
+        <v>-635.8481251166368</v>
       </c>
       <c r="P78">
-        <v>-4871.599533306773</v>
+        <v>-4450.936875816457</v>
       </c>
       <c r="Q78">
-        <v>-3849.599533306773</v>
+        <v>-3428.936875816457</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.175033195856361</v>
+        <v>0.1747759508579582</v>
       </c>
       <c r="T78">
-        <v>2.517819133114816</v>
+        <v>2.513981345032696</v>
       </c>
       <c r="U78">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V78">
-        <v>0.02707321997071418</v>
+        <v>0.02903754688152749</v>
       </c>
       <c r="W78">
-        <v>0.2157334924640674</v>
+        <v>0.2007334924640674</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2165857597657134</v>
+        <v>0.2323003750522199</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7720,13 +7720,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2077247874448432</v>
+        <v>0.1961130486452265</v>
       </c>
       <c r="C79">
-        <v>-22942.05178077224</v>
+        <v>-22283.19314465464</v>
       </c>
       <c r="D79">
-        <v>8579.153358831079</v>
+        <v>9238.011994948678</v>
       </c>
       <c r="E79">
         <v>18206.41015310551</v>
@@ -7753,37 +7753,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M79">
-        <v>7200.276903227391</v>
+        <v>6713.193826133341</v>
       </c>
       <c r="N79">
-        <v>-5661.052413431473</v>
+        <v>-5173.969336337423</v>
       </c>
       <c r="O79">
-        <v>-707.6315516789341</v>
+        <v>-646.7461670421778</v>
       </c>
       <c r="P79">
-        <v>-4953.420861752538</v>
+        <v>-4527.223169295245</v>
       </c>
       <c r="Q79">
-        <v>-3931.420861752538</v>
+        <v>-3505.223169295245</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1806520304588115</v>
+        <v>0.1803836008952608</v>
       </c>
       <c r="T79">
-        <v>2.627289530206765</v>
+        <v>2.623284881773247</v>
       </c>
       <c r="U79">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V79">
-        <v>0.02672161971135426</v>
+        <v>0.0286604358830661</v>
       </c>
       <c r="W79">
-        <v>0.2158114551159955</v>
+        <v>0.2008114551159955</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2137729576908339</v>
+        <v>0.2292834870645287</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7802,13 +7802,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2094841536114685</v>
+        <v>0.1977224148118518</v>
       </c>
       <c r="C80">
-        <v>-23455.98212958141</v>
+        <v>-22802.77151918142</v>
       </c>
       <c r="D80">
-        <v>8486.93995988688</v>
+        <v>9140.150570286874</v>
       </c>
       <c r="E80">
         <v>18628.12710297048</v>
@@ -7835,37 +7835,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M80">
-        <v>7293.786992879694</v>
+        <v>6800.378161537669</v>
       </c>
       <c r="N80">
-        <v>-5754.562503083776</v>
+        <v>-5261.153671741751</v>
       </c>
       <c r="O80">
-        <v>-719.320312885472</v>
+        <v>-657.6442089677189</v>
       </c>
       <c r="P80">
-        <v>-5035.242190198304</v>
+        <v>-4603.509462774033</v>
       </c>
       <c r="Q80">
-        <v>-4013.242190198304</v>
+        <v>-3581.509462774033</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1867816682069393</v>
+        <v>0.1865010372995908</v>
       </c>
       <c r="T80">
-        <v>2.7467117815798</v>
+        <v>2.742525103672031</v>
       </c>
       <c r="U80">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V80">
-        <v>0.02637903484325997</v>
+        <v>0.02829299439738577</v>
       </c>
       <c r="W80">
-        <v>0.2158874187255665</v>
+        <v>0.2008874187255665</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2110322787460797</v>
+        <v>0.2263439551790861</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7884,13 +7884,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2112435197780939</v>
+        <v>0.1993317809784772</v>
       </c>
       <c r="C81">
-        <v>-23967.95123948043</v>
+        <v>-23320.29826811168</v>
       </c>
       <c r="D81">
-        <v>8396.687799852851</v>
+        <v>9044.340771221601</v>
       </c>
       <c r="E81">
         <v>19049.84405283546</v>
@@ -7917,37 +7917,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M81">
-        <v>7387.297082531999</v>
+        <v>6887.562496942</v>
       </c>
       <c r="N81">
-        <v>-5848.07259273608</v>
+        <v>-5348.338007146082</v>
       </c>
       <c r="O81">
-        <v>-731.00907409201</v>
+        <v>-668.5422508932602</v>
       </c>
       <c r="P81">
-        <v>-5117.06351864407</v>
+        <v>-4679.795756252821</v>
       </c>
       <c r="Q81">
-        <v>-4095.06351864407</v>
+        <v>-3657.795756252821</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1934950809786983</v>
+        <v>0.1932010866948094</v>
       </c>
       <c r="T81">
-        <v>2.877507580702648</v>
+        <v>2.873121537180223</v>
       </c>
       <c r="U81">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V81">
-        <v>0.02604512300980098</v>
+        <v>0.0279348552277986</v>
       </c>
       <c r="W81">
-        <v>0.2159614592057813</v>
+        <v>0.2009614592057813</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2083609840784079</v>
+        <v>0.2234788418223888</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7966,13 +7966,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2130028859447192</v>
+        <v>0.2009411471451025</v>
       </c>
       <c r="C82">
-        <v>-24478.02102095658</v>
+        <v>-23835.83723943573</v>
       </c>
       <c r="D82">
-        <v>8308.334968241674</v>
+        <v>8950.518749762525</v>
       </c>
       <c r="E82">
         <v>19471.56100270044</v>
@@ -7999,37 +7999,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M82">
-        <v>7480.807172184302</v>
+        <v>6974.746832346327</v>
       </c>
       <c r="N82">
-        <v>-5941.582682388384</v>
+        <v>-5435.522342550408</v>
       </c>
       <c r="O82">
-        <v>-742.6978352985479</v>
+        <v>-679.440292818801</v>
       </c>
       <c r="P82">
-        <v>-5198.884847089836</v>
+        <v>-4756.082049731607</v>
       </c>
       <c r="Q82">
-        <v>-4176.884847089836</v>
+        <v>-3734.082049731607</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2008798350276332</v>
+        <v>0.2005711410295499</v>
       </c>
       <c r="T82">
-        <v>3.02138295973778</v>
+        <v>3.016777614039234</v>
       </c>
       <c r="U82">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V82">
-        <v>0.02571955897217847</v>
+        <v>0.02758566953745113</v>
       </c>
       <c r="W82">
-        <v>0.2160336486739907</v>
+        <v>0.2010336486739907</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2057564717774277</v>
+        <v>0.2206853562996091</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8048,13 +8048,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2147622521113446</v>
+        <v>0.2025505133117279</v>
       </c>
       <c r="C83">
-        <v>-24986.25080585694</v>
+        <v>-24349.44965902059</v>
       </c>
       <c r="D83">
-        <v>8221.822133206293</v>
+        <v>8858.623280042644</v>
       </c>
       <c r="E83">
         <v>19893.27795256542</v>
@@ -8081,37 +8081,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M83">
-        <v>7574.317261836606</v>
+        <v>7061.931167750658</v>
       </c>
       <c r="N83">
-        <v>-6035.092772040687</v>
+        <v>-5522.706677954739</v>
       </c>
       <c r="O83">
-        <v>-754.3865965050859</v>
+        <v>-690.3383347443423</v>
       </c>
       <c r="P83">
-        <v>-5280.706175535601</v>
+        <v>-4832.368343210396</v>
       </c>
       <c r="Q83">
-        <v>-4258.706175535601</v>
+        <v>-3810.368343210396</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.209041931608035</v>
+        <v>0.2087169905574209</v>
       </c>
       <c r="T83">
-        <v>3.180403115513453</v>
+        <v>3.175555383199194</v>
       </c>
       <c r="U83">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V83">
-        <v>0.02540203355276886</v>
+        <v>0.02724510571600111</v>
       </c>
       <c r="W83">
-        <v>0.216104055686195</v>
+        <v>0.2011040556861949</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2032162684221509</v>
+        <v>0.2179608457280089</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8130,13 +8130,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2165216182779699</v>
+        <v>0.2041598794783532</v>
       </c>
       <c r="C84">
-        <v>-25492.69748025875</v>
+        <v>-24861.19426384933</v>
       </c>
       <c r="D84">
-        <v>8137.092408669464</v>
+        <v>8768.59562507888</v>
       </c>
       <c r="E84">
         <v>20314.9949024304</v>
@@ -8163,37 +8163,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M84">
-        <v>7667.827351488912</v>
+        <v>7149.115503154987</v>
       </c>
       <c r="N84">
-        <v>-6128.602861692993</v>
+        <v>-5609.891013359069</v>
       </c>
       <c r="O84">
-        <v>-766.0753577116241</v>
+        <v>-701.2363766698836</v>
       </c>
       <c r="P84">
-        <v>-5362.527503981369</v>
+        <v>-4908.654636689185</v>
       </c>
       <c r="Q84">
-        <v>-4340.527503981369</v>
+        <v>-3886.654636689185</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2181109278084815</v>
+        <v>0.2177679344772777</v>
       </c>
       <c r="T84">
-        <v>3.357092177486424</v>
+        <v>3.351975126710261</v>
       </c>
       <c r="U84">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V84">
-        <v>0.02509225265578387</v>
+        <v>0.02691284832922061</v>
       </c>
       <c r="W84">
-        <v>0.2161727454541991</v>
+        <v>0.2011727454541991</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.200738021246271</v>
+        <v>0.2153027866337648</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8212,13 +8212,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2432586346833927</v>
+        <v>0.2057692456449786</v>
       </c>
       <c r="C85">
-        <v>-27016.22278391832</v>
+        <v>-25371.12742721786</v>
       </c>
       <c r="D85">
-        <v>7035.284054874869</v>
+        <v>8680.379411575324</v>
       </c>
       <c r="E85">
         <v>20736.71185229538</v>
@@ -8245,45 +8245,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M85">
-        <v>8811.412646305009</v>
+        <v>7236.299838559316</v>
       </c>
       <c r="N85">
-        <v>-7272.18815650909</v>
+        <v>-5697.075348763397</v>
       </c>
       <c r="O85">
-        <v>-909.0235195636362</v>
+        <v>-712.1344185954247</v>
       </c>
       <c r="P85">
-        <v>-6363.164636945454</v>
+        <v>-4984.940930167973</v>
       </c>
       <c r="Q85">
-        <v>-5341.164636945454</v>
+        <v>-3962.940930167973</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2287036308489652</v>
+        <v>0.2278836953288822</v>
       </c>
       <c r="T85">
-        <v>3.563467251707887</v>
+        <v>3.549150134163805</v>
       </c>
       <c r="U85">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V85">
-        <v>0.02183566573802129</v>
+        <v>0.0265885971445312</v>
       </c>
       <c r="W85">
-        <v>0.2462397800470706</v>
+        <v>0.2012397800470706</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.1746853259041704</v>
+        <v>0.2127087771562496</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8294,13 +8294,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.245318000850018</v>
+        <v>0.2073786118116039</v>
       </c>
       <c r="C86">
-        <v>-27510.5558681345</v>
+        <v>-25879.30327644973</v>
       </c>
       <c r="D86">
-        <v>6962.66792052367</v>
+        <v>8593.92051220844</v>
       </c>
       <c r="E86">
         <v>21158.42880216035</v>
@@ -8327,45 +8327,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M86">
-        <v>8917.574244453263</v>
+        <v>7323.484173963644</v>
       </c>
       <c r="N86">
-        <v>-7378.349754657344</v>
+        <v>-5784.259684167726</v>
       </c>
       <c r="O86">
-        <v>-922.2937193321679</v>
+        <v>-723.0324605209657</v>
       </c>
       <c r="P86">
-        <v>-6456.056035325176</v>
+        <v>-5061.22722364676</v>
       </c>
       <c r="Q86">
-        <v>-5434.056035325176</v>
+        <v>-4039.22722364676</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2401351077770254</v>
+        <v>0.2392639262869373</v>
       </c>
       <c r="T86">
-        <v>3.786183954939628</v>
+        <v>3.770972017549042</v>
       </c>
       <c r="U86">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V86">
-        <v>0.02157571733637818</v>
+        <v>0.02627206622614393</v>
       </c>
       <c r="W86">
-        <v>0.2463052185782071</v>
+        <v>0.201305218578207</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.1726057386910255</v>
+        <v>0.2101765298091514</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8376,13 +8376,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2473773670166433</v>
+        <v>0.2089879779782292</v>
       </c>
       <c r="C87">
-        <v>-28003.40522218348</v>
+        <v>-26385.7738036454</v>
       </c>
       <c r="D87">
-        <v>6891.535516339672</v>
+        <v>8509.166934877747</v>
       </c>
       <c r="E87">
         <v>21580.14575202533</v>
@@ -8409,45 +8409,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M87">
-        <v>9023.735842601516</v>
+        <v>7410.668509367974</v>
       </c>
       <c r="N87">
-        <v>-7484.511352805597</v>
+        <v>-5871.444019572056</v>
       </c>
       <c r="O87">
-        <v>-935.5639191006996</v>
+        <v>-733.930502446507</v>
       </c>
       <c r="P87">
-        <v>-6548.947433704898</v>
+        <v>-5137.51351712555</v>
       </c>
       <c r="Q87">
-        <v>-5526.947433704898</v>
+        <v>-4115.51351712555</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2530907816288271</v>
+        <v>0.2521615213727331</v>
       </c>
       <c r="T87">
-        <v>4.03859621860227</v>
+        <v>4.022370152052312</v>
       </c>
       <c r="U87">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V87">
-        <v>0.02132188536771491</v>
+        <v>0.02596298309407164</v>
       </c>
       <c r="W87">
-        <v>0.2463691173791991</v>
+        <v>0.2013691173791992</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.1705750829417193</v>
+        <v>0.2077038647525731</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8458,13 +8458,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2494367331832687</v>
+        <v>0.2105973441448546</v>
       </c>
       <c r="C88">
-        <v>-28494.81586068995</v>
+        <v>-26890.58896994232</v>
       </c>
       <c r="D88">
-        <v>6821.841827698174</v>
+        <v>8426.068718445804</v>
       </c>
       <c r="E88">
         <v>22001.86270189031</v>
@@ -8491,45 +8491,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M88">
-        <v>9129.897440749768</v>
+        <v>7497.852844772302</v>
       </c>
       <c r="N88">
-        <v>-7590.672950953849</v>
+        <v>-5958.628354976383</v>
       </c>
       <c r="O88">
-        <v>-948.8341188692311</v>
+        <v>-744.8285443720479</v>
       </c>
       <c r="P88">
-        <v>-6641.838832084618</v>
+        <v>-5213.799810604335</v>
       </c>
       <c r="Q88">
-        <v>-5619.838832084618</v>
+        <v>-4191.799810604335</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2678972660308862</v>
+        <v>0.266901630042214</v>
       </c>
       <c r="T88">
-        <v>4.327067377073861</v>
+        <v>4.309682305770334</v>
       </c>
       <c r="U88">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V88">
-        <v>0.02107395646809032</v>
+        <v>0.025661087941815</v>
       </c>
       <c r="W88">
-        <v>0.2464315301615635</v>
+        <v>0.2014315301615635</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.1685916517447226</v>
+        <v>0.2052887035345201</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8540,13 +8540,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.251496099349894</v>
+        <v>0.2122067103114799</v>
       </c>
       <c r="C89">
-        <v>-28984.83099558825</v>
+        <v>-27393.79680372504</v>
       </c>
       <c r="D89">
-        <v>6753.543642664855</v>
+        <v>8344.57783452806</v>
       </c>
       <c r="E89">
         <v>22423.57965175529</v>
@@ -8573,45 +8573,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M89">
-        <v>9236.059038898022</v>
+        <v>7585.037180176632</v>
       </c>
       <c r="N89">
-        <v>-7696.834549102103</v>
+        <v>-6045.812690380713</v>
       </c>
       <c r="O89">
-        <v>-962.1043186377628</v>
+        <v>-755.7265862975892</v>
       </c>
       <c r="P89">
-        <v>-6734.73023046434</v>
+        <v>-5290.086104083124</v>
       </c>
       <c r="Q89">
-        <v>-5712.73023046434</v>
+        <v>-4268.086104083124</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2849816711101851</v>
+        <v>0.2839094477377689</v>
       </c>
       <c r="T89">
-        <v>4.659918713771851</v>
+        <v>4.641196329291128</v>
       </c>
       <c r="U89">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V89">
-        <v>0.02083172708339963</v>
+        <v>0.02536613290800103</v>
       </c>
       <c r="W89">
-        <v>0.2464925081673218</v>
+        <v>0.2014925081673218</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.166653816667197</v>
+        <v>0.2029290632640083</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2535554655165194</v>
+        <v>0.2138160764781053</v>
       </c>
       <c r="C90">
-        <v>-29473.49212546771</v>
+        <v>-27895.44349319093</v>
       </c>
       <c r="D90">
-        <v>6686.599462650363</v>
+        <v>8264.648094927146</v>
       </c>
       <c r="E90">
         <v>22845.29660162026</v>
@@ -8655,45 +8655,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M90">
-        <v>9342.220637046274</v>
+        <v>7672.221515580961</v>
       </c>
       <c r="N90">
-        <v>-7802.996147250355</v>
+        <v>-6132.997025785042</v>
       </c>
       <c r="O90">
-        <v>-975.3745184062943</v>
+        <v>-766.6246282231302</v>
       </c>
       <c r="P90">
-        <v>-6827.62162884406</v>
+        <v>-5366.372397561911</v>
       </c>
       <c r="Q90">
-        <v>-5805.62162884406</v>
+        <v>-4344.372397561911</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3049134770360339</v>
+        <v>0.3037519017159165</v>
       </c>
       <c r="T90">
-        <v>5.048245273252838</v>
+        <v>5.027962690065391</v>
       </c>
       <c r="U90">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V90">
-        <v>0.02059500291199736</v>
+        <v>0.02507788139768284</v>
       </c>
       <c r="W90">
-        <v>0.2465521003093128</v>
+        <v>0.2015521003093128</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.1647600232959789</v>
+        <v>0.2006230511814627</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8704,13 +8704,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2556148316831447</v>
+        <v>0.2466765797878494</v>
       </c>
       <c r="C91">
-        <v>-29960.83911965651</v>
+        <v>-29669.13734531125</v>
       </c>
       <c r="D91">
-        <v>6620.969418326555</v>
+        <v>6912.671192671814</v>
       </c>
       <c r="E91">
         <v>23267.01355148524</v>
@@ -8737,37 +8737,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M91">
-        <v>9448.382235194529</v>
+        <v>9073.054149814698</v>
       </c>
       <c r="N91">
-        <v>-7909.15774539861</v>
+        <v>-7533.829660018779</v>
       </c>
       <c r="O91">
-        <v>-988.6447181748263</v>
+        <v>-941.7287075023473</v>
       </c>
       <c r="P91">
-        <v>-6920.513027223784</v>
+        <v>-6592.100952516432</v>
       </c>
       <c r="Q91">
-        <v>-5898.513027223784</v>
+        <v>-5570.100952516432</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3284692476756734</v>
+        <v>0.3281215031729889</v>
       </c>
       <c r="T91">
-        <v>5.50717666173037</v>
+        <v>5.502971581579072</v>
       </c>
       <c r="U91">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V91">
-        <v>0.02036359838489626</v>
+        <v>0.02120598621451183</v>
       </c>
       <c r="W91">
-        <v>0.2466103533020457</v>
+        <v>0.2366103533020457</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1629087870791701</v>
+        <v>0.1696478897160947</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8786,13 +8786,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2576741978497701</v>
+        <v>0.2486359459544747</v>
       </c>
       <c r="C92">
-        <v>-30446.9102974017</v>
+        <v>-30157.62970814453</v>
       </c>
       <c r="D92">
-        <v>6556.615190446337</v>
+        <v>6845.895779703506</v>
       </c>
       <c r="E92">
         <v>23688.73050135022</v>
@@ -8819,37 +8819,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M92">
-        <v>9554.543833342781</v>
+        <v>9174.998578464299</v>
       </c>
       <c r="N92">
-        <v>-8015.319343546862</v>
+        <v>-7635.774088668381</v>
       </c>
       <c r="O92">
-        <v>-1001.914917943358</v>
+        <v>-954.4717610835476</v>
       </c>
       <c r="P92">
-        <v>-7013.404425603504</v>
+        <v>-6681.302327584833</v>
       </c>
       <c r="Q92">
-        <v>-5991.404425603504</v>
+        <v>-5659.302327584833</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3567361724432408</v>
+        <v>0.3563536534902877</v>
       </c>
       <c r="T92">
-        <v>6.057894327903408</v>
+        <v>6.053268739736978</v>
       </c>
       <c r="U92">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V92">
-        <v>0.02013733618061964</v>
+        <v>0.0209703641454617</v>
       </c>
       <c r="W92">
-        <v>0.2466673117838289</v>
+        <v>0.2366673117838289</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1610986894449571</v>
+        <v>0.1677629131636936</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8868,13 +8868,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2597335640163954</v>
+        <v>0.2505953121211001</v>
       </c>
       <c r="C93">
-        <v>-30931.74250247625</v>
+        <v>-30644.84433191653</v>
       </c>
       <c r="D93">
-        <v>6493.499935236768</v>
+        <v>6780.398105796486</v>
       </c>
       <c r="E93">
         <v>24110.4474512152</v>
@@ -8901,37 +8901,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M93">
-        <v>9660.705431491035</v>
+        <v>9276.943007113905</v>
       </c>
       <c r="N93">
-        <v>-8121.480941695116</v>
+        <v>-7737.718517317986</v>
       </c>
       <c r="O93">
-        <v>-1015.185117711889</v>
+        <v>-967.2148146647482</v>
       </c>
       <c r="P93">
-        <v>-7106.295823983226</v>
+        <v>-6770.503702653237</v>
       </c>
       <c r="Q93">
-        <v>-6084.295823983226</v>
+        <v>-5748.503702653237</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.3912846360480454</v>
+        <v>0.3908596149892087</v>
       </c>
       <c r="T93">
-        <v>6.730993697670454</v>
+        <v>6.725854155263312</v>
       </c>
       <c r="U93">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V93">
-        <v>0.0199160467720414</v>
+        <v>0.02073992058342366</v>
       </c>
       <c r="W93">
-        <v>0.2467230184308476</v>
+        <v>0.2367230184308476</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1593283741763313</v>
+        <v>0.1659193646673893</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8950,13 +8950,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2617929301830207</v>
+        <v>0.2525546782877254</v>
       </c>
       <c r="C94">
-        <v>-31415.37117351783</v>
+        <v>-31130.81754313806</v>
       </c>
       <c r="D94">
-        <v>6431.588214060156</v>
+        <v>6716.141844439927</v>
       </c>
       <c r="E94">
         <v>24532.16440108018</v>
@@ -8983,37 +8983,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M94">
-        <v>9766.867029639287</v>
+        <v>9378.887435763507</v>
       </c>
       <c r="N94">
-        <v>-8227.642539843368</v>
+        <v>-7839.662945967588</v>
       </c>
       <c r="O94">
-        <v>-1028.455317480421</v>
+        <v>-979.9578682459485</v>
       </c>
       <c r="P94">
-        <v>-7199.187222362947</v>
+        <v>-6859.705077721639</v>
       </c>
       <c r="Q94">
-        <v>-6177.187222362947</v>
+        <v>-5837.705077721639</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4344702155540511</v>
+        <v>0.4339920668628599</v>
       </c>
       <c r="T94">
-        <v>7.572367909879262</v>
+        <v>7.566585924671227</v>
       </c>
       <c r="U94">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V94">
-        <v>0.01969956800278008</v>
+        <v>0.02051448666403862</v>
       </c>
       <c r="W94">
-        <v>0.2467775140638007</v>
+        <v>0.2367775140638007</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1575965440222407</v>
+        <v>0.164115893312309</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9032,13 +9032,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2638522963496461</v>
+        <v>0.2545140444543508</v>
       </c>
       <c r="C95">
-        <v>-31897.830410382</v>
+        <v>-31615.58430421559</v>
       </c>
       <c r="D95">
-        <v>6370.845927060969</v>
+        <v>6653.092033227383</v>
       </c>
       <c r="E95">
         <v>24953.88135094516</v>
@@ -9065,37 +9065,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M95">
-        <v>9873.02862778754</v>
+        <v>9480.83186441311</v>
       </c>
       <c r="N95">
-        <v>-8333.804137991621</v>
+        <v>-7941.607374617191</v>
       </c>
       <c r="O95">
-        <v>-1041.725517248953</v>
+        <v>-992.7009218271489</v>
       </c>
       <c r="P95">
-        <v>-7292.078620742668</v>
+        <v>-6948.906452790043</v>
       </c>
       <c r="Q95">
-        <v>-6270.078620742668</v>
+        <v>-5926.906452790043</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.4899945320617727</v>
+        <v>0.4894480764146971</v>
       </c>
       <c r="T95">
-        <v>8.654134754147728</v>
+        <v>8.647526771052831</v>
       </c>
       <c r="U95">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V95">
-        <v>0.01948774469092223</v>
+        <v>0.02029390078593067</v>
       </c>
       <c r="W95">
-        <v>0.2468308377476581</v>
+        <v>0.2368308377476581</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1559019575273779</v>
+        <v>0.1623512062874455</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9114,13 +9114,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2659116625162714</v>
+        <v>0.2564734106209761</v>
       </c>
       <c r="C96">
-        <v>-32379.15303677037</v>
+        <v>-32099.17827688532</v>
       </c>
       <c r="D96">
-        <v>6311.240250537576</v>
+        <v>6591.215010422628</v>
       </c>
       <c r="E96">
         <v>25375.59830081013</v>
@@ -9147,37 +9147,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M96">
-        <v>9979.190225935794</v>
+        <v>9582.776293062714</v>
       </c>
       <c r="N96">
-        <v>-8439.965736139875</v>
+        <v>-8043.551803266795</v>
       </c>
       <c r="O96">
-        <v>-1054.995717017484</v>
+        <v>-1005.443975408349</v>
       </c>
       <c r="P96">
-        <v>-7384.970019122391</v>
+        <v>-7038.107827858445</v>
       </c>
       <c r="Q96">
-        <v>-6362.970019122391</v>
+        <v>-6016.107827858445</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.5640269540720682</v>
+        <v>0.5633894224838134</v>
       </c>
       <c r="T96">
-        <v>10.09649054650568</v>
+        <v>10.08878123289497</v>
       </c>
       <c r="U96">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V96">
-        <v>0.01928042825804008</v>
+        <v>0.02007800822437822</v>
       </c>
       <c r="W96">
-        <v>0.2468830268850504</v>
+        <v>0.2368830268850504</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1542434260643206</v>
+        <v>0.1606240657950259</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9196,13 +9196,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2679710286828968</v>
+        <v>0.2584327767876015</v>
       </c>
       <c r="C97">
-        <v>-32859.37065937587</v>
+        <v>-32581.63188214034</v>
       </c>
       <c r="D97">
-        <v>6252.739577797061</v>
+        <v>6530.478355032589</v>
       </c>
       <c r="E97">
         <v>25797.31525067511</v>
@@ -9229,37 +9229,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M97">
-        <v>10085.35182408405</v>
+        <v>9684.720721712318</v>
       </c>
       <c r="N97">
-        <v>-8546.127334288129</v>
+        <v>-8145.496231916399</v>
       </c>
       <c r="O97">
-        <v>-1068.265916786016</v>
+        <v>-1018.18702898955</v>
       </c>
       <c r="P97">
-        <v>-7477.861417502112</v>
+        <v>-7127.309202926849</v>
       </c>
       <c r="Q97">
-        <v>-6455.861417502112</v>
+        <v>-6105.309202926849</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.6676723448864822</v>
+        <v>0.6669073069805763</v>
       </c>
       <c r="T97">
-        <v>12.11578865580683</v>
+        <v>12.10653747947397</v>
       </c>
       <c r="U97">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V97">
-        <v>0.01907747638163965</v>
+        <v>0.01986666076938477</v>
       </c>
       <c r="W97">
-        <v>0.2469341173037607</v>
+        <v>0.2369341173037607</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1526198110531173</v>
+        <v>0.1589332861550782</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9278,13 +9278,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2700303948495221</v>
+        <v>0.2603921429542268</v>
       </c>
       <c r="C98">
-        <v>-33338.51372376861</v>
+        <v>-33062.97635687447</v>
       </c>
       <c r="D98">
-        <v>6195.313463269299</v>
+        <v>6470.85083016343</v>
       </c>
       <c r="E98">
         <v>26219.03220054009</v>
@@ -9311,37 +9311,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M98">
-        <v>10191.5134222323</v>
+        <v>9786.66515036192</v>
       </c>
       <c r="N98">
-        <v>-8652.28893243638</v>
+        <v>-8247.440660566001</v>
       </c>
       <c r="O98">
-        <v>-1081.536116554548</v>
+        <v>-1030.93008257075</v>
       </c>
       <c r="P98">
-        <v>-7570.752815881833</v>
+        <v>-7216.51057799525</v>
       </c>
       <c r="Q98">
-        <v>-6548.752815881833</v>
+        <v>-6194.51057799525</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.823140431108101</v>
+        <v>0.8221841337257186</v>
       </c>
       <c r="T98">
-        <v>15.1447358197585</v>
+        <v>15.13317184934243</v>
       </c>
       <c r="U98">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V98">
-        <v>0.01887875266933091</v>
+        <v>0.01965971638637034</v>
       </c>
       <c r="W98">
-        <v>0.246984143338748</v>
+        <v>0.236984143338748</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1510300213546473</v>
+        <v>0.1572777310909628</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9360,13 +9360,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2720897610161475</v>
+        <v>0.2623515091208521</v>
       </c>
       <c r="C99">
-        <v>-33816.61156723037</v>
+        <v>-33543.24180745124</v>
       </c>
       <c r="D99">
-        <v>6138.932569672503</v>
+        <v>6412.302329451637</v>
       </c>
       <c r="E99">
         <v>26640.74915040506</v>
@@ -9393,37 +9393,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M99">
-        <v>10297.67502038055</v>
+        <v>9888.609579011523</v>
       </c>
       <c r="N99">
-        <v>-8758.450530584632</v>
+        <v>-8349.385089215604</v>
       </c>
       <c r="O99">
-        <v>-1094.806316323079</v>
+        <v>-1043.673136151951</v>
       </c>
       <c r="P99">
-        <v>-7663.644214261553</v>
+        <v>-7305.711953063654</v>
       </c>
       <c r="Q99">
-        <v>-6641.644214261553</v>
+        <v>-6283.711953063654</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.082253908144135</v>
+        <v>1.080978844967625</v>
       </c>
       <c r="T99">
-        <v>20.19298109301134</v>
+        <v>20.17756246578991</v>
       </c>
       <c r="U99">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V99">
-        <v>0.01868412635315224</v>
+        <v>0.01945703889785106</v>
       </c>
       <c r="W99">
-        <v>0.2470331379090963</v>
+        <v>0.2370331379090962</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.149473010825218</v>
+        <v>0.1556563111828085</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9442,13 +9442,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2741491271827728</v>
+        <v>0.2643108752874775</v>
       </c>
       <c r="C100">
-        <v>-34293.69246873008</v>
+        <v>-34022.4572603906</v>
       </c>
       <c r="D100">
-        <v>6083.568618037782</v>
+        <v>6354.803826377265</v>
       </c>
       <c r="E100">
         <v>27062.46610027004</v>
@@ -9475,37 +9475,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M100">
-        <v>10403.83661852881</v>
+        <v>9990.554007661127</v>
       </c>
       <c r="N100">
-        <v>-8864.612128732886</v>
+        <v>-8451.329517865208</v>
       </c>
       <c r="O100">
-        <v>-1108.076516091611</v>
+        <v>-1056.416189733151</v>
       </c>
       <c r="P100">
-        <v>-7756.535612641275</v>
+        <v>-7394.913328132057</v>
       </c>
       <c r="Q100">
-        <v>-6734.535612641275</v>
+        <v>-6372.913328132057</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.600480862216202</v>
+        <v>1.598568267451437</v>
       </c>
       <c r="T100">
-        <v>30.289471639517</v>
+        <v>30.26634369868487</v>
       </c>
       <c r="U100">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V100">
-        <v>0.01849347200260987</v>
+        <v>0.01925849768460768</v>
       </c>
       <c r="W100">
-        <v>0.2470811325902538</v>
+        <v>0.2370811325902538</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1479477760208791</v>
+        <v>0.1540679814768615</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9524,13 +9524,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2762084933493981</v>
+        <v>0.2662702414541028</v>
       </c>
       <c r="C101">
-        <v>-34769.78369621915</v>
+        <v>-34500.65071035291</v>
       </c>
       <c r="D101">
-        <v>6029.194340413682</v>
+        <v>6298.327326279919</v>
       </c>
       <c r="E101">
         <v>27484.18305013502</v>
@@ -9557,37 +9557,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M101">
-        <v>10509.99821667706</v>
+        <v>10092.49843631073</v>
       </c>
       <c r="N101">
-        <v>-8970.77372688114</v>
+        <v>-8553.27394651481</v>
       </c>
       <c r="O101">
-        <v>-1121.346715860142</v>
+        <v>-1069.159243314351</v>
       </c>
       <c r="P101">
-        <v>-7849.427011020997</v>
+        <v>-7484.114703200458</v>
       </c>
       <c r="Q101">
-        <v>-6827.427011020997</v>
+        <v>-6462.114703200458</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.155161724432404</v>
+        <v>3.151336534902875</v>
       </c>
       <c r="T101">
-        <v>60.57894327903401</v>
+        <v>60.53268739736973</v>
       </c>
       <c r="U101">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V101">
-        <v>0.01830666925510876</v>
+        <v>0.01906396740496518</v>
       </c>
       <c r="W101">
-        <v>0.247128157681893</v>
+        <v>0.237128157681893</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.1464533540408701</v>
+        <v>0.1525117392397215</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/ireland/ireland_packaging_container.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_packaging_container.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07745275822866582</v>
+        <v>0.07744726267667716</v>
       </c>
       <c r="C2">
-        <v>44820.59696688769</v>
+        <v>44406.49797922424</v>
       </c>
       <c r="D2">
-        <v>43869.59696688769</v>
+        <v>43877.21492908922</v>
       </c>
       <c r="E2">
-        <v>-14265.79498649781</v>
+        <v>-13844.07803663284</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>421.7169498649782</v>
       </c>
       <c r="G2">
         <v>951</v>
@@ -1439,28 +1439,28 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>23.71593444964989</v>
       </c>
       <c r="N2">
-        <v>1539.224489795919</v>
+        <v>1515.508555346269</v>
       </c>
       <c r="O2">
-        <v>192.4030612244898</v>
+        <v>189.4385694182836</v>
       </c>
       <c r="P2">
-        <v>1346.821428571429</v>
+        <v>1326.069985927985</v>
       </c>
       <c r="Q2">
-        <v>2368.821428571428</v>
+        <v>2348.069985927985</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07745275822866582</v>
+        <v>0.07773251745543433</v>
       </c>
       <c r="T2">
-        <v>0.6169711731246059</v>
+        <v>0.6224242011698992</v>
       </c>
       <c r="U2">
         <v>0.0562366166625341</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>64.90254445017837</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07744726267667716</v>
+        <v>0.07744176712468849</v>
       </c>
       <c r="C3">
-        <v>44406.49797922424</v>
+        <v>43992.40163774092</v>
       </c>
       <c r="D3">
-        <v>43877.21492908922</v>
+        <v>43884.83553747088</v>
       </c>
       <c r="E3">
-        <v>-13844.07803663284</v>
+        <v>-13422.36108676786</v>
       </c>
       <c r="F3">
-        <v>421.7169498649782</v>
+        <v>843.4338997299564</v>
       </c>
       <c r="G3">
         <v>951</v>
@@ -1521,28 +1521,28 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M3">
-        <v>23.71593444964989</v>
+        <v>47.43186889929978</v>
       </c>
       <c r="N3">
-        <v>1515.508555346269</v>
+        <v>1491.792620896619</v>
       </c>
       <c r="O3">
-        <v>189.4385694182836</v>
+        <v>186.4740776120773</v>
       </c>
       <c r="P3">
-        <v>1326.069985927985</v>
+        <v>1305.318543284541</v>
       </c>
       <c r="Q3">
-        <v>2348.069985927985</v>
+        <v>2327.318543284541</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07773251745543433</v>
+        <v>0.0780179860541777</v>
       </c>
       <c r="T3">
-        <v>0.6224242011698992</v>
+        <v>0.627988515501831</v>
       </c>
       <c r="U3">
         <v>0.0562366166625341</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>64.90254445017837</v>
+        <v>32.45127222508918</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07744176712468849</v>
+        <v>0.07743627157269983</v>
       </c>
       <c r="C4">
-        <v>43992.40163774092</v>
+        <v>43578.3079438167</v>
       </c>
       <c r="D4">
-        <v>43884.83553747088</v>
+        <v>43892.45879341164</v>
       </c>
       <c r="E4">
-        <v>-13422.36108676786</v>
+        <v>-13000.64413690288</v>
       </c>
       <c r="F4">
-        <v>843.4338997299564</v>
+        <v>1265.150849594934</v>
       </c>
       <c r="G4">
         <v>951</v>
@@ -1603,28 +1603,28 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M4">
-        <v>47.43186889929978</v>
+        <v>71.14780334894967</v>
       </c>
       <c r="N4">
-        <v>1491.792620896619</v>
+        <v>1468.076686446969</v>
       </c>
       <c r="O4">
-        <v>186.4740776120773</v>
+        <v>183.5095858058711</v>
       </c>
       <c r="P4">
-        <v>1305.318543284541</v>
+        <v>1284.567100641098</v>
       </c>
       <c r="Q4">
-        <v>2327.318543284541</v>
+        <v>2306.567100641098</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0780179860541777</v>
+        <v>0.07830934060341063</v>
       </c>
       <c r="T4">
-        <v>0.627988515501831</v>
+        <v>0.6336675579643182</v>
       </c>
       <c r="U4">
         <v>0.0562366166625341</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>32.45127222508918</v>
+        <v>21.63418148339279</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07743627157269983</v>
+        <v>0.07743077602071118</v>
       </c>
       <c r="C5">
-        <v>43578.3079438167</v>
+        <v>43164.21689883155</v>
       </c>
       <c r="D5">
-        <v>43892.45879341164</v>
+        <v>43900.08469829147</v>
       </c>
       <c r="E5">
-        <v>-13000.64413690288</v>
+        <v>-12578.9271870379</v>
       </c>
       <c r="F5">
-        <v>1265.150849594934</v>
+        <v>1686.867799459913</v>
       </c>
       <c r="G5">
         <v>951</v>
@@ -1685,28 +1685,28 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M5">
-        <v>71.14780334894967</v>
+        <v>94.86373779859956</v>
       </c>
       <c r="N5">
-        <v>1468.076686446969</v>
+        <v>1444.360751997319</v>
       </c>
       <c r="O5">
-        <v>183.5095858058711</v>
+        <v>180.5450939996649</v>
       </c>
       <c r="P5">
-        <v>1284.567100641098</v>
+        <v>1263.815657997654</v>
       </c>
       <c r="Q5">
-        <v>2306.567100641098</v>
+        <v>2285.815657997654</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07830934060341063</v>
+        <v>0.07860676503908592</v>
       </c>
       <c r="T5">
-        <v>0.6336675579643182</v>
+        <v>0.6394649138114404</v>
       </c>
       <c r="U5">
         <v>0.0562366166625341</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>21.63418148339279</v>
+        <v>16.22563611254459</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07743077602071118</v>
+        <v>0.07742528046872252</v>
       </c>
       <c r="C6">
-        <v>43164.21689883155</v>
+        <v>42750.12850416642</v>
       </c>
       <c r="D6">
-        <v>43900.08469829147</v>
+        <v>43907.7132534913</v>
       </c>
       <c r="E6">
-        <v>-12578.9271870379</v>
+        <v>-12157.21023717292</v>
       </c>
       <c r="F6">
-        <v>1686.867799459913</v>
+        <v>2108.584749324891</v>
       </c>
       <c r="G6">
         <v>951</v>
@@ -1767,28 +1767,28 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M6">
-        <v>94.86373779859956</v>
+        <v>118.5796722482494</v>
       </c>
       <c r="N6">
-        <v>1444.360751997319</v>
+        <v>1420.644817547669</v>
       </c>
       <c r="O6">
-        <v>180.5450939996649</v>
+        <v>177.5806021934586</v>
       </c>
       <c r="P6">
-        <v>1263.815657997654</v>
+        <v>1243.064215354211</v>
       </c>
       <c r="Q6">
-        <v>2285.815657997654</v>
+        <v>2265.06421535421</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07860676503908592</v>
+        <v>0.07891045104182806</v>
       </c>
       <c r="T6">
-        <v>0.6394649138114404</v>
+        <v>0.6453843192553443</v>
       </c>
       <c r="U6">
         <v>0.0562366166625341</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>16.22563611254459</v>
+        <v>12.98050889003568</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07742528046872252</v>
+        <v>0.07741978491673385</v>
       </c>
       <c r="C7">
-        <v>42750.12850416642</v>
+        <v>42336.04276120318</v>
       </c>
       <c r="D7">
-        <v>43907.7132534913</v>
+        <v>43915.34446039305</v>
       </c>
       <c r="E7">
-        <v>-12157.21023717292</v>
+        <v>-11735.49328730795</v>
       </c>
       <c r="F7">
-        <v>2108.584749324891</v>
+        <v>2530.301699189869</v>
       </c>
       <c r="G7">
         <v>951</v>
@@ -1849,28 +1849,28 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M7">
-        <v>118.5796722482494</v>
+        <v>142.2956066978993</v>
       </c>
       <c r="N7">
-        <v>1420.644817547669</v>
+        <v>1396.928883098019</v>
       </c>
       <c r="O7">
-        <v>177.5806021934586</v>
+        <v>174.6161103872524</v>
       </c>
       <c r="P7">
-        <v>1243.064215354211</v>
+        <v>1222.312772710767</v>
       </c>
       <c r="Q7">
-        <v>2265.06421535421</v>
+        <v>2244.312772710767</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07891045104182806</v>
+        <v>0.07922059844888385</v>
       </c>
       <c r="T7">
-        <v>0.6453843192553443</v>
+        <v>0.6514296694959271</v>
       </c>
       <c r="U7">
         <v>0.0562366166625341</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>12.98050889003568</v>
+        <v>10.8170907416964</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07741978491673385</v>
+        <v>0.0774142893647452</v>
       </c>
       <c r="C8">
-        <v>42336.04276120318</v>
+        <v>41921.95967132464</v>
       </c>
       <c r="D8">
-        <v>43915.34446039305</v>
+        <v>43922.97832037948</v>
       </c>
       <c r="E8">
-        <v>-11735.49328730795</v>
+        <v>-11313.77633744297</v>
       </c>
       <c r="F8">
-        <v>2530.301699189869</v>
+        <v>2952.018649054847</v>
       </c>
       <c r="G8">
         <v>951</v>
@@ -1931,28 +1931,28 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M8">
-        <v>142.2956066978993</v>
+        <v>166.0115411475492</v>
       </c>
       <c r="N8">
-        <v>1396.928883098019</v>
+        <v>1373.212948648369</v>
       </c>
       <c r="O8">
-        <v>174.6161103872524</v>
+        <v>171.6516185810462</v>
       </c>
       <c r="P8">
-        <v>1222.312772710767</v>
+        <v>1201.561330067323</v>
       </c>
       <c r="Q8">
-        <v>2244.312772710767</v>
+        <v>2223.561330067323</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07922059844888385</v>
+        <v>0.07953741569265052</v>
       </c>
       <c r="T8">
-        <v>0.6514296694959271</v>
+        <v>0.6576050272685652</v>
       </c>
       <c r="U8">
         <v>0.0562366166625341</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>10.8170907416964</v>
+        <v>9.271792064311198</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0774142893647452</v>
+        <v>0.07751379381275654</v>
       </c>
       <c r="C9">
-        <v>41921.95967132464</v>
+        <v>41362.43102543276</v>
       </c>
       <c r="D9">
-        <v>43922.97832037948</v>
+        <v>43785.16662435259</v>
       </c>
       <c r="E9">
-        <v>-11313.77633744297</v>
+        <v>-10892.05938757799</v>
       </c>
       <c r="F9">
-        <v>2952.018649054847</v>
+        <v>3373.735598919825</v>
       </c>
       <c r="G9">
         <v>951</v>
@@ -2013,45 +2013,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M9">
-        <v>166.0115411475492</v>
+        <v>194.7880789955788</v>
       </c>
       <c r="N9">
-        <v>1373.212948648369</v>
+        <v>1344.43641080034</v>
       </c>
       <c r="O9">
-        <v>171.6516185810462</v>
+        <v>168.0545513500425</v>
       </c>
       <c r="P9">
-        <v>1201.561330067323</v>
+        <v>1176.381859450297</v>
       </c>
       <c r="Q9">
-        <v>2223.561330067323</v>
+        <v>2198.381859450297</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07953741569265052</v>
+        <v>0.07986112026780343</v>
       </c>
       <c r="T9">
-        <v>0.6576050272685652</v>
+        <v>0.6639146319493042</v>
       </c>
       <c r="U9">
-        <v>0.0562366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V9">
         <v>0.125</v>
       </c>
       <c r="W9">
-        <v>0.04920703957971734</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>9.271792064311196</v>
+        <v>7.902046663907265</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07751379381275654</v>
+        <v>0.07752142326076789</v>
       </c>
       <c r="C10">
-        <v>41362.43102543276</v>
+        <v>40930.18312777007</v>
       </c>
       <c r="D10">
-        <v>43785.16662435259</v>
+        <v>43774.63567655487</v>
       </c>
       <c r="E10">
-        <v>-10892.05938757799</v>
+        <v>-10470.34243771301</v>
       </c>
       <c r="F10">
-        <v>3373.735598919825</v>
+        <v>3795.452548784803</v>
       </c>
       <c r="G10">
         <v>951</v>
@@ -2095,28 +2095,28 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M10">
-        <v>194.7880789955788</v>
+        <v>219.1365888700262</v>
       </c>
       <c r="N10">
-        <v>1344.43641080034</v>
+        <v>1320.087900925892</v>
       </c>
       <c r="O10">
-        <v>168.0545513500425</v>
+        <v>165.0109876157366</v>
       </c>
       <c r="P10">
-        <v>1176.381859450297</v>
+        <v>1155.076913310156</v>
       </c>
       <c r="Q10">
-        <v>2198.381859450297</v>
+        <v>2177.076913310156</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07986112026780343</v>
+        <v>0.08019193922922344</v>
       </c>
       <c r="T10">
-        <v>0.6639146319493042</v>
+        <v>0.6703629092603891</v>
       </c>
       <c r="U10">
         <v>0.05773661666253409</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>7.902046663907265</v>
+        <v>7.024041479028681</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07752142326076789</v>
+        <v>0.07767780270877923</v>
       </c>
       <c r="C11">
-        <v>40930.18312777007</v>
+        <v>40293.72573840446</v>
       </c>
       <c r="D11">
-        <v>43774.63567655487</v>
+        <v>43559.89523705424</v>
       </c>
       <c r="E11">
-        <v>-10470.34243771301</v>
+        <v>-10048.62548784803</v>
       </c>
       <c r="F11">
-        <v>3795.452548784803</v>
+        <v>4217.169498649781</v>
       </c>
       <c r="G11">
         <v>951</v>
@@ -2177,45 +2177,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M11">
-        <v>219.1365888700262</v>
+        <v>250.6542868921782</v>
       </c>
       <c r="N11">
-        <v>1320.087900925892</v>
+        <v>1288.57020290374</v>
       </c>
       <c r="O11">
-        <v>165.0109876157366</v>
+        <v>161.0712753629676</v>
       </c>
       <c r="P11">
-        <v>1155.076913310156</v>
+        <v>1127.498927540773</v>
       </c>
       <c r="Q11">
-        <v>2177.076913310156</v>
+        <v>2149.498927540773</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08019193922922344</v>
+        <v>0.08053010972311944</v>
       </c>
       <c r="T11">
-        <v>0.6703629092603891</v>
+        <v>0.6769544816228316</v>
       </c>
       <c r="U11">
-        <v>0.05773661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V11">
         <v>0.125</v>
       </c>
       <c r="W11">
-        <v>0.05051953957971733</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>7.024041479028681</v>
+        <v>6.140826510013107</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07767780270877923</v>
+        <v>0.07770030715679056</v>
       </c>
       <c r="C12">
-        <v>40293.72573840446</v>
+        <v>39841.2789465689</v>
       </c>
       <c r="D12">
-        <v>43559.89523705424</v>
+        <v>43529.16539508366</v>
       </c>
       <c r="E12">
-        <v>-10048.62548784803</v>
+        <v>-9626.908537983054</v>
       </c>
       <c r="F12">
-        <v>4217.169498649781</v>
+        <v>4638.88644851476</v>
       </c>
       <c r="G12">
         <v>951</v>
@@ -2259,28 +2259,28 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M12">
-        <v>250.6542868921782</v>
+        <v>275.719715581396</v>
       </c>
       <c r="N12">
-        <v>1288.57020290374</v>
+        <v>1263.504774214523</v>
       </c>
       <c r="O12">
-        <v>161.0712753629676</v>
+        <v>157.9380967768153</v>
       </c>
       <c r="P12">
-        <v>1127.498927540773</v>
+        <v>1105.566677437707</v>
       </c>
       <c r="Q12">
-        <v>2149.498927540773</v>
+        <v>2127.566677437707</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08053010972311944</v>
+        <v>0.08087587955395692</v>
       </c>
       <c r="T12">
-        <v>0.6769544816228316</v>
+        <v>0.6836941792069018</v>
       </c>
       <c r="U12">
         <v>0.05943661666253409</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>6.140826510013107</v>
+        <v>5.58256955455737</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07770030715679056</v>
+        <v>0.07780681160480192</v>
       </c>
       <c r="C13">
-        <v>39841.2789465689</v>
+        <v>39274.71627479819</v>
       </c>
       <c r="D13">
-        <v>43529.16539508366</v>
+        <v>43384.31967317792</v>
       </c>
       <c r="E13">
-        <v>-9626.908537983054</v>
+        <v>-9205.191588118076</v>
       </c>
       <c r="F13">
-        <v>4638.88644851476</v>
+        <v>5060.603398379738</v>
       </c>
       <c r="G13">
         <v>951</v>
@@ -2341,45 +2341,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M13">
-        <v>275.719715581396</v>
+        <v>304.8336269893176</v>
       </c>
       <c r="N13">
-        <v>1263.504774214523</v>
+        <v>1234.390862806601</v>
       </c>
       <c r="O13">
-        <v>157.9380967768153</v>
+        <v>154.2988578508251</v>
       </c>
       <c r="P13">
-        <v>1105.566677437707</v>
+        <v>1080.092004955776</v>
       </c>
       <c r="Q13">
-        <v>2127.566677437707</v>
+        <v>2102.092004955776</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08087587955395692</v>
+        <v>0.08122950779004072</v>
       </c>
       <c r="T13">
-        <v>0.6836941792069018</v>
+        <v>0.6905870517360646</v>
       </c>
       <c r="U13">
-        <v>0.05943661666253409</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V13">
         <v>0.125</v>
       </c>
       <c r="W13">
-        <v>0.05200703957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y13">
-        <v>5.58256955455737</v>
+        <v>5.049392040497744</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07780681160480192</v>
+        <v>0.07783631605281324</v>
       </c>
       <c r="C14">
-        <v>39274.71627479819</v>
+        <v>38813.04371948239</v>
       </c>
       <c r="D14">
-        <v>43384.31967317792</v>
+        <v>43344.3640677271</v>
       </c>
       <c r="E14">
-        <v>-9205.191588118076</v>
+        <v>-8783.474638253098</v>
       </c>
       <c r="F14">
-        <v>5060.603398379738</v>
+        <v>5482.320348244716</v>
       </c>
       <c r="G14">
         <v>951</v>
@@ -2423,28 +2423,28 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M14">
-        <v>304.8336269893176</v>
+        <v>330.2364292384274</v>
       </c>
       <c r="N14">
-        <v>1234.390862806601</v>
+        <v>1208.988060557491</v>
       </c>
       <c r="O14">
-        <v>154.2988578508251</v>
+        <v>151.1235075696864</v>
       </c>
       <c r="P14">
-        <v>1080.092004955776</v>
+        <v>1057.864552987805</v>
       </c>
       <c r="Q14">
-        <v>2102.092004955776</v>
+        <v>2079.864552987805</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08122950779004072</v>
+        <v>0.08159126541086206</v>
       </c>
       <c r="T14">
-        <v>0.6905870517360646</v>
+        <v>0.6976383811049782</v>
       </c>
       <c r="U14">
         <v>0.0602366166625341</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.049392040497744</v>
+        <v>4.660977268151765</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07783631605281324</v>
+        <v>0.07786582050082459</v>
       </c>
       <c r="C15">
-        <v>38813.04371948239</v>
+        <v>38351.4446921827</v>
       </c>
       <c r="D15">
-        <v>43344.3640677271</v>
+        <v>43304.48199029239</v>
       </c>
       <c r="E15">
-        <v>-8783.474638253098</v>
+        <v>-8361.757688388119</v>
       </c>
       <c r="F15">
-        <v>5482.320348244716</v>
+        <v>5904.037298109694</v>
       </c>
       <c r="G15">
         <v>951</v>
@@ -2505,28 +2505,28 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M15">
-        <v>330.2364292384274</v>
+        <v>355.6392314875372</v>
       </c>
       <c r="N15">
-        <v>1208.988060557491</v>
+        <v>1183.585258308381</v>
       </c>
       <c r="O15">
-        <v>151.1235075696864</v>
+        <v>147.9481572885477</v>
       </c>
       <c r="P15">
-        <v>1057.864552987805</v>
+        <v>1035.637101019834</v>
       </c>
       <c r="Q15">
-        <v>2079.864552987805</v>
+        <v>2057.637101019834</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08159126541086206</v>
+        <v>0.08196143599960949</v>
       </c>
       <c r="T15">
-        <v>0.6976383811049782</v>
+        <v>0.7048536948778201</v>
       </c>
       <c r="U15">
         <v>0.0602366166625341</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>4.660977268151765</v>
+        <v>4.328050320426637</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07786582050082459</v>
+        <v>0.07802657494883594</v>
       </c>
       <c r="C16">
-        <v>38351.4446921827</v>
+        <v>37713.7138435457</v>
       </c>
       <c r="D16">
-        <v>43304.48199029239</v>
+        <v>43088.46809152037</v>
       </c>
       <c r="E16">
-        <v>-8361.757688388119</v>
+        <v>-7940.040738523141</v>
       </c>
       <c r="F16">
-        <v>5904.037298109694</v>
+        <v>6325.754247974673</v>
       </c>
       <c r="G16">
         <v>951</v>
@@ -2587,45 +2587,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M16">
-        <v>355.6392314875372</v>
+        <v>387.3677879846217</v>
       </c>
       <c r="N16">
-        <v>1183.585258308381</v>
+        <v>1151.856701811297</v>
       </c>
       <c r="O16">
-        <v>147.9481572885477</v>
+        <v>143.9820877264121</v>
       </c>
       <c r="P16">
-        <v>1035.637101019834</v>
+        <v>1007.874614084885</v>
       </c>
       <c r="Q16">
-        <v>2057.637101019834</v>
+        <v>2029.874614084885</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08196143599960949</v>
+        <v>0.08234031648456275</v>
       </c>
       <c r="T16">
-        <v>0.7048536948778201</v>
+        <v>0.7122387807394348</v>
       </c>
       <c r="U16">
-        <v>0.0602366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V16">
         <v>0.125</v>
       </c>
       <c r="W16">
-        <v>0.05270703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y16">
-        <v>4.328050320426637</v>
+        <v>3.973547975695451</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07802657494883594</v>
+        <v>0.07806482939684727</v>
       </c>
       <c r="C17">
-        <v>37713.7138435457</v>
+        <v>37240.90951484413</v>
       </c>
       <c r="D17">
-        <v>43088.46809152037</v>
+        <v>43037.38071268379</v>
       </c>
       <c r="E17">
-        <v>-7940.040738523142</v>
+        <v>-7518.323788658164</v>
       </c>
       <c r="F17">
-        <v>6325.754247974673</v>
+        <v>6747.471197839651</v>
       </c>
       <c r="G17">
         <v>951</v>
@@ -2669,28 +2669,28 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M17">
-        <v>387.3677879846217</v>
+        <v>413.1923071835965</v>
       </c>
       <c r="N17">
-        <v>1151.856701811297</v>
+        <v>1126.032182612322</v>
       </c>
       <c r="O17">
-        <v>143.9820877264121</v>
+        <v>140.7540228265403</v>
       </c>
       <c r="P17">
-        <v>1007.874614084885</v>
+        <v>985.2781597857818</v>
       </c>
       <c r="Q17">
-        <v>2029.874614084885</v>
+        <v>2007.278159785782</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08234031648456275</v>
+        <v>0.08272821793344345</v>
       </c>
       <c r="T17">
-        <v>0.7122387807394347</v>
+        <v>0.7197997019787069</v>
       </c>
       <c r="U17">
         <v>0.0612366166625341</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>3.973547975695451</v>
+        <v>3.725201227214486</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07806482939684727</v>
+        <v>0.0781030838448586</v>
       </c>
       <c r="C18">
-        <v>37240.90951484413</v>
+        <v>36768.22618508415</v>
       </c>
       <c r="D18">
-        <v>43037.38071268379</v>
+        <v>42986.41433278877</v>
       </c>
       <c r="E18">
-        <v>-7518.323788658164</v>
+        <v>-7096.606838793185</v>
       </c>
       <c r="F18">
-        <v>6747.471197839651</v>
+        <v>7169.188147704629</v>
       </c>
       <c r="G18">
         <v>951</v>
@@ -2751,28 +2751,28 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M18">
-        <v>413.1923071835965</v>
+        <v>439.0168263825713</v>
       </c>
       <c r="N18">
-        <v>1126.032182612322</v>
+        <v>1100.207663413347</v>
       </c>
       <c r="O18">
-        <v>140.7540228265403</v>
+        <v>137.5259579266684</v>
       </c>
       <c r="P18">
-        <v>985.2781597857818</v>
+        <v>962.6817054866789</v>
       </c>
       <c r="Q18">
-        <v>2007.278159785782</v>
+        <v>1984.681705486679</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08272821793344345</v>
+        <v>0.08312546640518875</v>
       </c>
       <c r="T18">
-        <v>0.7197997019787069</v>
+        <v>0.7275428140912145</v>
       </c>
       <c r="U18">
         <v>0.0612366166625341</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.725201227214486</v>
+        <v>3.506071743260693</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0781030838448586</v>
+        <v>0.07814133829286997</v>
       </c>
       <c r="C19">
-        <v>36768.22618508415</v>
+        <v>36295.66342490057</v>
       </c>
       <c r="D19">
-        <v>42986.41433278877</v>
+        <v>42935.56852247018</v>
       </c>
       <c r="E19">
-        <v>-7096.606838793185</v>
+        <v>-6674.889888928206</v>
       </c>
       <c r="F19">
-        <v>7169.188147704629</v>
+        <v>7590.905097569608</v>
       </c>
       <c r="G19">
         <v>951</v>
@@ -2833,28 +2833,28 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M19">
-        <v>439.0168263825713</v>
+        <v>464.8413455815461</v>
       </c>
       <c r="N19">
-        <v>1100.207663413347</v>
+        <v>1074.383144214372</v>
       </c>
       <c r="O19">
-        <v>137.5259579266684</v>
+        <v>134.2978930267965</v>
       </c>
       <c r="P19">
-        <v>962.6817054866789</v>
+        <v>940.0852511875758</v>
       </c>
       <c r="Q19">
-        <v>1984.681705486679</v>
+        <v>1962.085251187576</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08312546640518875</v>
+        <v>0.08353240386404981</v>
       </c>
       <c r="T19">
-        <v>0.7275428140912145</v>
+        <v>0.7354747825967102</v>
       </c>
       <c r="U19">
         <v>0.0612366166625341</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.506071743260693</v>
+        <v>3.311289979746209</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07814133829286996</v>
+        <v>0.07817959274088131</v>
       </c>
       <c r="C20">
-        <v>36295.66342490059</v>
+        <v>35823.22080695743</v>
       </c>
       <c r="D20">
-        <v>42935.5685224702</v>
+        <v>42884.84285439202</v>
       </c>
       <c r="E20">
-        <v>-6674.889888928208</v>
+        <v>-6253.172939063229</v>
       </c>
       <c r="F20">
-        <v>7590.905097569606</v>
+        <v>8012.622047434586</v>
       </c>
       <c r="G20">
         <v>951</v>
@@ -2915,28 +2915,28 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M20">
-        <v>464.841345581546</v>
+        <v>490.6658647805208</v>
       </c>
       <c r="N20">
-        <v>1074.383144214373</v>
+        <v>1048.558625015398</v>
       </c>
       <c r="O20">
-        <v>134.2978930267966</v>
+        <v>131.0698281269247</v>
       </c>
       <c r="P20">
-        <v>940.085251187576</v>
+        <v>917.4887968884732</v>
       </c>
       <c r="Q20">
-        <v>1962.085251187576</v>
+        <v>1939.488796888473</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08353240386404981</v>
+        <v>0.08394938916140124</v>
       </c>
       <c r="T20">
-        <v>0.7354747825967102</v>
+        <v>0.7436026021764154</v>
       </c>
       <c r="U20">
         <v>0.0612366166625341</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.31128997974621</v>
+        <v>3.137011559759568</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07817959274088131</v>
+        <v>0.07865534718889264</v>
       </c>
       <c r="C21">
-        <v>35823.22080695743</v>
+        <v>34780.519558161</v>
       </c>
       <c r="D21">
-        <v>42884.84285439202</v>
+        <v>42263.85855546056</v>
       </c>
       <c r="E21">
-        <v>-6253.172939063229</v>
+        <v>-5831.455989198252</v>
       </c>
       <c r="F21">
-        <v>8012.622047434586</v>
+        <v>8434.338997299563</v>
       </c>
       <c r="G21">
         <v>951</v>
@@ -2997,45 +2997,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M21">
-        <v>490.6658647805208</v>
+        <v>537.5762314727444</v>
       </c>
       <c r="N21">
-        <v>1048.558625015398</v>
+        <v>1001.648258323174</v>
       </c>
       <c r="O21">
-        <v>131.0698281269247</v>
+        <v>125.2060322903968</v>
       </c>
       <c r="P21">
-        <v>917.4887968884732</v>
+        <v>876.4422260327774</v>
       </c>
       <c r="Q21">
-        <v>1939.488796888473</v>
+        <v>1898.442226032777</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08394938916140124</v>
+        <v>0.08437679909118646</v>
       </c>
       <c r="T21">
-        <v>0.7436026021764154</v>
+        <v>0.7519336172456135</v>
       </c>
       <c r="U21">
-        <v>0.0612366166625341</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V21">
         <v>0.125</v>
       </c>
       <c r="W21">
-        <v>0.05358203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>3.137011559759568</v>
+        <v>2.863267383639819</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07865534718889264</v>
+        <v>0.07871547663690398</v>
       </c>
       <c r="C22">
-        <v>34780.519558161</v>
+        <v>34281.5956908996</v>
       </c>
       <c r="D22">
-        <v>42263.85855546056</v>
+        <v>42186.65163806414</v>
       </c>
       <c r="E22">
-        <v>-5831.455989198252</v>
+        <v>-5409.739039333272</v>
       </c>
       <c r="F22">
-        <v>8434.338997299563</v>
+        <v>8856.055947164543</v>
       </c>
       <c r="G22">
         <v>951</v>
@@ -3079,28 +3079,28 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M22">
-        <v>537.5762314727444</v>
+        <v>564.4550430463818</v>
       </c>
       <c r="N22">
-        <v>1001.648258323174</v>
+        <v>974.7694467495368</v>
       </c>
       <c r="O22">
-        <v>125.2060322903968</v>
+        <v>121.8461808436921</v>
       </c>
       <c r="P22">
-        <v>876.4422260327774</v>
+        <v>852.9232659058447</v>
       </c>
       <c r="Q22">
-        <v>1898.442226032777</v>
+        <v>1874.923265905845</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08437679909118646</v>
+        <v>0.08481502952552322</v>
       </c>
       <c r="T22">
-        <v>0.7519336172456135</v>
+        <v>0.7604755440887153</v>
       </c>
       <c r="U22">
         <v>0.06373661666253409</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.863267383639819</v>
+        <v>2.726921317752208</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07871547663690398</v>
+        <v>0.07877560608491532</v>
       </c>
       <c r="C23">
-        <v>34281.5956908996</v>
+        <v>33782.95338991563</v>
       </c>
       <c r="D23">
-        <v>42186.65163806414</v>
+        <v>42109.72628694515</v>
       </c>
       <c r="E23">
-        <v>-5409.739039333273</v>
+        <v>-4988.022089468295</v>
       </c>
       <c r="F23">
-        <v>8856.055947164541</v>
+        <v>9277.772897029519</v>
       </c>
       <c r="G23">
         <v>951</v>
@@ -3161,28 +3161,28 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M23">
-        <v>564.4550430463817</v>
+        <v>591.3338546200189</v>
       </c>
       <c r="N23">
-        <v>974.7694467495369</v>
+        <v>947.8906351758997</v>
       </c>
       <c r="O23">
-        <v>121.8461808436921</v>
+        <v>118.4863293969875</v>
       </c>
       <c r="P23">
-        <v>852.9232659058448</v>
+        <v>829.4043057789122</v>
       </c>
       <c r="Q23">
-        <v>1874.923265905845</v>
+        <v>1851.404305778912</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08481502952552322</v>
+        <v>0.08526449663766347</v>
       </c>
       <c r="T23">
-        <v>0.7604755440887152</v>
+        <v>0.7692364946970247</v>
       </c>
       <c r="U23">
         <v>0.06373661666253409</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.726921317752208</v>
+        <v>2.602970348763471</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07877560608491532</v>
+        <v>0.07954011053292667</v>
       </c>
       <c r="C24">
-        <v>33782.95338991563</v>
+        <v>32407.08802315401</v>
       </c>
       <c r="D24">
-        <v>42109.72628694515</v>
+        <v>41155.5778700485</v>
       </c>
       <c r="E24">
-        <v>-4988.022089468295</v>
+        <v>-4566.305139603317</v>
       </c>
       <c r="F24">
-        <v>9277.772897029519</v>
+        <v>9699.489846894498</v>
       </c>
       <c r="G24">
         <v>951</v>
@@ -3243,45 +3243,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M24">
-        <v>591.3338546200189</v>
+        <v>652.1608806577868</v>
       </c>
       <c r="N24">
-        <v>947.8906351758997</v>
+        <v>887.0636091381317</v>
       </c>
       <c r="O24">
-        <v>118.4863293969875</v>
+        <v>110.8829511422665</v>
       </c>
       <c r="P24">
-        <v>829.4043057789122</v>
+        <v>776.1806579958652</v>
       </c>
       <c r="Q24">
-        <v>1851.404305778912</v>
+        <v>1798.180657995865</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08526449663766347</v>
+        <v>0.08572563822024892</v>
       </c>
       <c r="T24">
-        <v>0.7692364946970247</v>
+        <v>0.7782250024639915</v>
       </c>
       <c r="U24">
-        <v>0.06373661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V24">
         <v>0.125</v>
       </c>
       <c r="W24">
-        <v>0.05576953957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.602970348763471</v>
+        <v>2.360191381371136</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07954011053292667</v>
+        <v>0.07963086498093801</v>
       </c>
       <c r="C25">
-        <v>32407.08802315401</v>
+        <v>31874.9674003623</v>
       </c>
       <c r="D25">
-        <v>41155.5778700485</v>
+        <v>41045.17419712178</v>
       </c>
       <c r="E25">
-        <v>-4566.305139603317</v>
+        <v>-4144.588189738339</v>
       </c>
       <c r="F25">
-        <v>9699.489846894498</v>
+        <v>10121.20679675948</v>
       </c>
       <c r="G25">
         <v>951</v>
@@ -3325,28 +3325,28 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M25">
-        <v>652.1608806577868</v>
+        <v>680.5157015559515</v>
       </c>
       <c r="N25">
-        <v>887.0636091381317</v>
+        <v>858.708788239967</v>
       </c>
       <c r="O25">
-        <v>110.8829511422665</v>
+        <v>107.3385985299959</v>
       </c>
       <c r="P25">
-        <v>776.1806579958652</v>
+        <v>751.3701897099711</v>
       </c>
       <c r="Q25">
-        <v>1798.180657995865</v>
+        <v>1773.370189709971</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08572563822024892</v>
+        <v>0.08619891510763927</v>
       </c>
       <c r="T25">
-        <v>0.7782250024639915</v>
+        <v>0.7874500499090366</v>
       </c>
       <c r="U25">
         <v>0.0672366166625341</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.360191381371136</v>
+        <v>2.261850073814005</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07963086498093801</v>
+        <v>0.08033411942894934</v>
       </c>
       <c r="C26">
-        <v>31874.9674003623</v>
+        <v>30617.40457398921</v>
       </c>
       <c r="D26">
-        <v>41045.17419712178</v>
+        <v>40209.32832061366</v>
       </c>
       <c r="E26">
-        <v>-4144.588189738339</v>
+        <v>-3722.871239873361</v>
       </c>
       <c r="F26">
-        <v>10121.20679675948</v>
+        <v>10542.92374662445</v>
       </c>
       <c r="G26">
         <v>951</v>
@@ -3407,45 +3407,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M26">
-        <v>680.5157015559515</v>
+        <v>738.3907089446647</v>
       </c>
       <c r="N26">
-        <v>858.708788239967</v>
+        <v>800.8337808512539</v>
       </c>
       <c r="O26">
-        <v>107.3385985299959</v>
+        <v>100.1042226064067</v>
       </c>
       <c r="P26">
-        <v>751.3701897099711</v>
+        <v>700.7295582448471</v>
       </c>
       <c r="Q26">
-        <v>1773.370189709971</v>
+        <v>1722.729558244847</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08619891510763927</v>
+        <v>0.08668481271202667</v>
       </c>
       <c r="T26">
-        <v>0.7874500499090364</v>
+        <v>0.7969210986192825</v>
       </c>
       <c r="U26">
-        <v>0.0672366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V26">
         <v>0.125</v>
       </c>
       <c r="W26">
-        <v>0.05883203957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.261850073814005</v>
+        <v>2.084566437727576</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08033411942894934</v>
+        <v>0.08044937387696068</v>
       </c>
       <c r="C27">
-        <v>30617.40457398921</v>
+        <v>30061.93906182826</v>
       </c>
       <c r="D27">
-        <v>40209.32832061366</v>
+        <v>40075.5797583177</v>
       </c>
       <c r="E27">
-        <v>-3722.871239873361</v>
+        <v>-3301.154290008382</v>
       </c>
       <c r="F27">
-        <v>10542.92374662445</v>
+        <v>10964.64069648943</v>
       </c>
       <c r="G27">
         <v>951</v>
@@ -3489,28 +3489,28 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M27">
-        <v>738.3907089446647</v>
+        <v>767.9263373024512</v>
       </c>
       <c r="N27">
-        <v>800.8337808512539</v>
+        <v>771.2981524934673</v>
       </c>
       <c r="O27">
-        <v>100.1042226064067</v>
+        <v>96.41226906168342</v>
       </c>
       <c r="P27">
-        <v>700.7295582448471</v>
+        <v>674.8858834317839</v>
       </c>
       <c r="Q27">
-        <v>1722.729558244847</v>
+        <v>1696.885883431784</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08668481271202667</v>
+        <v>0.08718384268410023</v>
       </c>
       <c r="T27">
-        <v>0.7969210986192825</v>
+        <v>0.8066481216189949</v>
       </c>
       <c r="U27">
         <v>0.07003661666253409</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.084566437727576</v>
+        <v>2.004390805507284</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08044937387696068</v>
+        <v>0.08332875332497203</v>
       </c>
       <c r="C28">
-        <v>30061.93906182826</v>
+        <v>26565.4383661772</v>
       </c>
       <c r="D28">
-        <v>40075.5797583177</v>
+        <v>37000.79601253161</v>
       </c>
       <c r="E28">
-        <v>-3301.154290008382</v>
+        <v>-2879.437340143404</v>
       </c>
       <c r="F28">
-        <v>10964.64069648943</v>
+        <v>11386.35764635441</v>
       </c>
       <c r="G28">
         <v>951</v>
@@ -3571,45 +3571,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M28">
-        <v>767.9263373024512</v>
+        <v>930.6823501225844</v>
       </c>
       <c r="N28">
-        <v>771.2981524934673</v>
+        <v>608.5421396733342</v>
       </c>
       <c r="O28">
-        <v>96.41226906168342</v>
+        <v>76.06776745916677</v>
       </c>
       <c r="P28">
-        <v>674.8858834317839</v>
+        <v>532.4743722141674</v>
       </c>
       <c r="Q28">
-        <v>1696.885883431784</v>
+        <v>1554.474372214167</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08718384268410023</v>
+        <v>0.08769654471020322</v>
       </c>
       <c r="T28">
-        <v>0.8066481216189949</v>
+        <v>0.8166416383995213</v>
       </c>
       <c r="U28">
-        <v>0.07003661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V28">
         <v>0.125</v>
       </c>
       <c r="W28">
-        <v>0.06128203957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.004390805507284</v>
+        <v>1.653866638379013</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08332875332497203</v>
+        <v>0.08354638277298337</v>
       </c>
       <c r="C29">
-        <v>26565.4383661772</v>
+        <v>25930.39070166818</v>
       </c>
       <c r="D29">
-        <v>37000.79601253161</v>
+        <v>36787.46529788757</v>
       </c>
       <c r="E29">
-        <v>-2879.437340143404</v>
+        <v>-2457.720390278426</v>
       </c>
       <c r="F29">
-        <v>11386.35764635441</v>
+        <v>11808.07459621939</v>
       </c>
       <c r="G29">
         <v>951</v>
@@ -3653,28 +3653,28 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M29">
-        <v>930.6823501225844</v>
+        <v>965.1520667937913</v>
       </c>
       <c r="N29">
-        <v>608.5421396733342</v>
+        <v>574.0724230021273</v>
       </c>
       <c r="O29">
-        <v>76.06776745916677</v>
+        <v>71.75905287526591</v>
       </c>
       <c r="P29">
-        <v>532.4743722141674</v>
+        <v>502.3133701268613</v>
       </c>
       <c r="Q29">
-        <v>1554.474372214167</v>
+        <v>1524.313370126861</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08769654471020322</v>
+        <v>0.08822348845925349</v>
       </c>
       <c r="T29">
-        <v>0.8166416383995213</v>
+        <v>0.8269127528683955</v>
       </c>
       <c r="U29">
         <v>0.0817366166625341</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>1.653866638379013</v>
+        <v>1.59479997272262</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08354638277298337</v>
+        <v>0.08376401222099472</v>
       </c>
       <c r="C30">
-        <v>25930.39070166818</v>
+        <v>25297.78888220851</v>
       </c>
       <c r="D30">
-        <v>36787.46529788757</v>
+        <v>36576.58042829288</v>
       </c>
       <c r="E30">
-        <v>-2457.720390278426</v>
+        <v>-2036.003440413446</v>
       </c>
       <c r="F30">
-        <v>11808.07459621939</v>
+        <v>12229.79154608437</v>
       </c>
       <c r="G30">
         <v>951</v>
@@ -3735,28 +3735,28 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M30">
-        <v>965.1520667937913</v>
+        <v>999.6217834649982</v>
       </c>
       <c r="N30">
-        <v>574.0724230021273</v>
+        <v>539.6027063309203</v>
       </c>
       <c r="O30">
-        <v>71.75905287526591</v>
+        <v>67.45033829136504</v>
       </c>
       <c r="P30">
-        <v>502.3133701268613</v>
+        <v>472.1523680395553</v>
       </c>
       <c r="Q30">
-        <v>1524.313370126861</v>
+        <v>1494.152368039555</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08822348845925349</v>
+        <v>0.08876527569419251</v>
       </c>
       <c r="T30">
-        <v>0.8269127528683955</v>
+        <v>0.837473194505407</v>
       </c>
       <c r="U30">
         <v>0.0817366166625341</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.59479997272262</v>
+        <v>1.539806870214943</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08376401222099471</v>
+        <v>0.08770914166900605</v>
       </c>
       <c r="C31">
-        <v>25297.78888220853</v>
+        <v>21432.92471413339</v>
       </c>
       <c r="D31">
-        <v>36576.58042829289</v>
+        <v>33133.43321008274</v>
       </c>
       <c r="E31">
-        <v>-2036.003440413449</v>
+        <v>-1614.286490548469</v>
       </c>
       <c r="F31">
-        <v>12229.79154608437</v>
+        <v>12651.50849594935</v>
       </c>
       <c r="G31">
         <v>951</v>
@@ -3817,45 +3817,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M31">
-        <v>999.621783464998</v>
+        <v>1213.742920778686</v>
       </c>
       <c r="N31">
-        <v>539.6027063309206</v>
+        <v>325.4815690172329</v>
       </c>
       <c r="O31">
-        <v>67.45033829136507</v>
+        <v>40.68519612715411</v>
       </c>
       <c r="P31">
-        <v>472.1523680395555</v>
+        <v>284.7963728900788</v>
       </c>
       <c r="Q31">
-        <v>1494.152368039556</v>
+        <v>1306.796372890079</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08876527569419251</v>
+        <v>0.08932254256441549</v>
       </c>
       <c r="T31">
-        <v>0.8374731945054069</v>
+        <v>0.8483353630463332</v>
       </c>
       <c r="U31">
-        <v>0.0817366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V31">
         <v>0.125</v>
       </c>
       <c r="W31">
-        <v>0.07151953957971734</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>1.539806870214944</v>
+        <v>1.26816351588557</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08770914166900605</v>
+        <v>0.09613914244793575</v>
       </c>
       <c r="C32">
-        <v>21432.92471413339</v>
+        <v>15462.5461425791</v>
       </c>
       <c r="D32">
-        <v>33133.43321008274</v>
+        <v>27584.77158839342</v>
       </c>
       <c r="E32">
-        <v>-1614.286490548469</v>
+        <v>-1192.569540683491</v>
       </c>
       <c r="F32">
-        <v>12651.50849594935</v>
+        <v>13073.22544581432</v>
       </c>
       <c r="G32">
         <v>951</v>
@@ -3899,45 +3899,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M32">
-        <v>1213.742920778686</v>
+        <v>1628.095265888265</v>
       </c>
       <c r="N32">
-        <v>325.4815690172329</v>
+        <v>-88.8707760923462</v>
       </c>
       <c r="O32">
-        <v>40.68519612715411</v>
+        <v>-11.10884701154328</v>
       </c>
       <c r="P32">
-        <v>284.7963728900788</v>
+        <v>-77.76192908080293</v>
       </c>
       <c r="Q32">
-        <v>1306.796372890079</v>
+        <v>944.2380709191971</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08932254256441549</v>
+        <v>0.08999299372954334</v>
       </c>
       <c r="T32">
-        <v>0.8483353630463332</v>
+        <v>0.8614037041647723</v>
       </c>
       <c r="U32">
-        <v>0.0959366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V32">
-        <v>0.125</v>
+        <v>0.1181767831746121</v>
       </c>
       <c r="W32">
-        <v>0.08394453957971734</v>
+        <v>0.109819279917906</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y32">
-        <v>1.26816351588557</v>
+        <v>0.9454142653968964</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09613914244793575</v>
+        <v>0.09692650861456112</v>
       </c>
       <c r="C33">
-        <v>15462.5461425791</v>
+        <v>14616.0140341722</v>
       </c>
       <c r="D33">
-        <v>27584.77158839342</v>
+        <v>27159.9564298515</v>
       </c>
       <c r="E33">
-        <v>-1192.569540683491</v>
+        <v>-770.8525908185129</v>
       </c>
       <c r="F33">
-        <v>13073.22544581432</v>
+        <v>13494.9423956793</v>
       </c>
       <c r="G33">
         <v>951</v>
@@ -3981,37 +3981,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M33">
-        <v>1628.095265888265</v>
+        <v>1680.614468013693</v>
       </c>
       <c r="N33">
-        <v>-88.8707760923462</v>
+        <v>-141.3899782177741</v>
       </c>
       <c r="O33">
-        <v>-11.10884701154328</v>
+        <v>-17.67374727722176</v>
       </c>
       <c r="P33">
-        <v>-77.76192908080293</v>
+        <v>-123.7162309405524</v>
       </c>
       <c r="Q33">
-        <v>944.2380709191971</v>
+        <v>898.2837690594476</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08999299372954334</v>
+        <v>0.09064289069615428</v>
       </c>
       <c r="T33">
-        <v>0.8614037041647723</v>
+        <v>0.8740714056966071</v>
       </c>
       <c r="U33">
         <v>0.1245366166625341</v>
       </c>
       <c r="V33">
-        <v>0.1181767831746121</v>
+        <v>0.1144837587004054</v>
       </c>
       <c r="W33">
-        <v>0.109819279917906</v>
+        <v>0.1102791966911757</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.9454142653968964</v>
+        <v>0.9158700696032434</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09692650861456112</v>
+        <v>0.09771387478118645</v>
       </c>
       <c r="C34">
-        <v>14616.0140341722</v>
+        <v>13782.36807939246</v>
       </c>
       <c r="D34">
-        <v>27159.9564298515</v>
+        <v>26748.02742493674</v>
       </c>
       <c r="E34">
-        <v>-770.8525908185129</v>
+        <v>-349.1356409535347</v>
       </c>
       <c r="F34">
-        <v>13494.9423956793</v>
+        <v>13916.65934554428</v>
       </c>
       <c r="G34">
         <v>951</v>
@@ -4063,37 +4063,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M34">
-        <v>1680.614468013693</v>
+        <v>1733.133670139121</v>
       </c>
       <c r="N34">
-        <v>-141.3899782177741</v>
+        <v>-193.909180343202</v>
       </c>
       <c r="O34">
-        <v>-17.67374727722176</v>
+        <v>-24.23864754290025</v>
       </c>
       <c r="P34">
-        <v>-123.7162309405524</v>
+        <v>-169.6705328003018</v>
       </c>
       <c r="Q34">
-        <v>898.2837690594476</v>
+        <v>852.3294671996982</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09064289069615428</v>
+        <v>0.09131218757221628</v>
       </c>
       <c r="T34">
-        <v>0.8740714056966071</v>
+        <v>0.8871172475726758</v>
       </c>
       <c r="U34">
         <v>0.1245366166625341</v>
       </c>
       <c r="V34">
-        <v>0.1144837587004054</v>
+        <v>0.1110145538913022</v>
       </c>
       <c r="W34">
-        <v>0.1102791966911757</v>
+        <v>0.1107112397206108</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.9158700696032434</v>
+        <v>0.8881164311304178</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09771387478118645</v>
+        <v>0.09850124094781179</v>
       </c>
       <c r="C35">
-        <v>13782.36807939246</v>
+        <v>12961.03071377262</v>
       </c>
       <c r="D35">
-        <v>26748.02742493674</v>
+        <v>26348.40700918188</v>
       </c>
       <c r="E35">
-        <v>-349.1356409535347</v>
+        <v>72.58130891144356</v>
       </c>
       <c r="F35">
-        <v>13916.65934554428</v>
+        <v>14338.37629540926</v>
       </c>
       <c r="G35">
         <v>951</v>
@@ -4145,37 +4145,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M35">
-        <v>1733.133670139121</v>
+        <v>1785.652872264548</v>
       </c>
       <c r="N35">
-        <v>-193.909180343202</v>
+        <v>-246.4283824686299</v>
       </c>
       <c r="O35">
-        <v>-24.23864754290025</v>
+        <v>-30.80354780857874</v>
       </c>
       <c r="P35">
-        <v>-169.6705328003018</v>
+        <v>-215.6248346600512</v>
       </c>
       <c r="Q35">
-        <v>852.3294671996982</v>
+        <v>806.3751653399488</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09131218757221628</v>
+        <v>0.09200176617179531</v>
       </c>
       <c r="T35">
-        <v>0.8871172475726758</v>
+        <v>0.9005584179904437</v>
       </c>
       <c r="U35">
         <v>0.1245366166625341</v>
       </c>
       <c r="V35">
-        <v>0.1110145538913022</v>
+        <v>0.1077494199533228</v>
       </c>
       <c r="W35">
-        <v>0.1107112397206108</v>
+        <v>0.1111178684541967</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8881164311304178</v>
+        <v>0.861995359626582</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09850124094781179</v>
+        <v>0.09928860711443713</v>
       </c>
       <c r="C36">
-        <v>12961.03071377262</v>
+        <v>12151.45838044031</v>
       </c>
       <c r="D36">
-        <v>26348.40700918188</v>
+        <v>25960.55162571455</v>
       </c>
       <c r="E36">
-        <v>72.58130891144356</v>
+        <v>494.2982587764218</v>
       </c>
       <c r="F36">
-        <v>14338.37629540926</v>
+        <v>14760.09324527424</v>
       </c>
       <c r="G36">
         <v>951</v>
@@ -4227,37 +4227,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M36">
-        <v>1785.652872264548</v>
+        <v>1838.172074389976</v>
       </c>
       <c r="N36">
-        <v>-246.4283824686299</v>
+        <v>-298.9475845940578</v>
       </c>
       <c r="O36">
-        <v>-30.80354780857874</v>
+        <v>-37.36844807425723</v>
       </c>
       <c r="P36">
-        <v>-215.6248346600512</v>
+        <v>-261.5791365198006</v>
       </c>
       <c r="Q36">
-        <v>806.3751653399488</v>
+        <v>760.4208634801994</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09200176617179531</v>
+        <v>0.09271256257443831</v>
       </c>
       <c r="T36">
-        <v>0.9005584179904437</v>
+        <v>0.9144131628826043</v>
       </c>
       <c r="U36">
         <v>0.1245366166625341</v>
       </c>
       <c r="V36">
-        <v>0.1077494199533228</v>
+        <v>0.1046708650975135</v>
       </c>
       <c r="W36">
-        <v>0.1111178684541967</v>
+        <v>0.1115012612601492</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.861995359626582</v>
+        <v>0.8373669207801082</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09928860711443713</v>
+        <v>0.1000759732810625</v>
       </c>
       <c r="C37">
-        <v>12151.45838044031</v>
+        <v>11353.13906342533</v>
       </c>
       <c r="D37">
-        <v>25960.55162571455</v>
+        <v>25583.94925856455</v>
       </c>
       <c r="E37">
-        <v>494.2982587764218</v>
+        <v>916.0152086414018</v>
       </c>
       <c r="F37">
-        <v>14760.09324527424</v>
+        <v>15181.81019513922</v>
       </c>
       <c r="G37">
         <v>951</v>
@@ -4309,37 +4309,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M37">
-        <v>1838.172074389976</v>
+        <v>1890.691276515405</v>
       </c>
       <c r="N37">
-        <v>-298.9475845940578</v>
+        <v>-351.466786719486</v>
       </c>
       <c r="O37">
-        <v>-37.36844807425723</v>
+        <v>-43.93334833993575</v>
       </c>
       <c r="P37">
-        <v>-261.5791365198006</v>
+        <v>-307.5334383795503</v>
       </c>
       <c r="Q37">
-        <v>760.4208634801994</v>
+        <v>714.4665616204497</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09271256257443831</v>
+        <v>0.09344557136466392</v>
       </c>
       <c r="T37">
-        <v>0.9144131628826043</v>
+        <v>0.928700868552645</v>
       </c>
       <c r="U37">
         <v>0.1245366166625341</v>
       </c>
       <c r="V37">
-        <v>0.1046708650975135</v>
+        <v>0.101763341067027</v>
       </c>
       <c r="W37">
-        <v>0.1115012612601492</v>
+        <v>0.111863354465771</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8373669207801082</v>
+        <v>0.8141067285362162</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1000759732810625</v>
+        <v>0.1317384019802129</v>
       </c>
       <c r="C38">
-        <v>11353.13906342533</v>
+        <v>1505.485040300671</v>
       </c>
       <c r="D38">
-        <v>25583.94925856455</v>
+        <v>16158.01218530486</v>
       </c>
       <c r="E38">
-        <v>916.0152086413982</v>
+        <v>1337.732158506376</v>
       </c>
       <c r="F38">
-        <v>15181.81019513921</v>
+        <v>15603.52714500419</v>
       </c>
       <c r="G38">
         <v>951</v>
@@ -4391,45 +4391,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M38">
-        <v>1890.691276515404</v>
+        <v>3225.820409960177</v>
       </c>
       <c r="N38">
-        <v>-351.4667867194855</v>
+        <v>-1686.595920164258</v>
       </c>
       <c r="O38">
-        <v>-43.93334833993569</v>
+        <v>-210.8244900205323</v>
       </c>
       <c r="P38">
-        <v>-307.5334383795498</v>
+        <v>-1475.771430143726</v>
       </c>
       <c r="Q38">
-        <v>714.4665616204502</v>
+        <v>-453.7714301437259</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09344557136466392</v>
+        <v>0.09493369556493644</v>
       </c>
       <c r="T38">
-        <v>0.928700868552645</v>
+        <v>0.9577071790600742</v>
       </c>
       <c r="U38">
-        <v>0.1245366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V38">
-        <v>0.1017633410670271</v>
+        <v>0.05964469089178621</v>
       </c>
       <c r="W38">
-        <v>0.111863354465771</v>
+        <v>0.1944058750656835</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.8141067285362165</v>
+        <v>0.4771575271342897</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1317384019802129</v>
+        <v>0.1333477681468382</v>
       </c>
       <c r="C39">
-        <v>1505.485040300671</v>
+        <v>786.7398659430346</v>
       </c>
       <c r="D39">
-        <v>16158.01218530486</v>
+        <v>15860.98396081221</v>
       </c>
       <c r="E39">
-        <v>1337.732158506376</v>
+        <v>1759.449108371356</v>
       </c>
       <c r="F39">
-        <v>15603.52714500419</v>
+        <v>16025.24409486917</v>
       </c>
       <c r="G39">
         <v>951</v>
@@ -4473,37 +4473,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M39">
-        <v>3225.820409960177</v>
+        <v>3313.004745364506</v>
       </c>
       <c r="N39">
-        <v>-1686.595920164258</v>
+        <v>-1773.780255568588</v>
       </c>
       <c r="O39">
-        <v>-210.8244900205323</v>
+        <v>-221.7225319460734</v>
       </c>
       <c r="P39">
-        <v>-1475.771430143726</v>
+        <v>-1552.057723622514</v>
       </c>
       <c r="Q39">
-        <v>-453.7714301437259</v>
+        <v>-530.057723622514</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09493369556493644</v>
+        <v>0.09572617452566125</v>
       </c>
       <c r="T39">
-        <v>0.9577071790600742</v>
+        <v>0.9731540690449143</v>
       </c>
       <c r="U39">
         <v>0.2067366166625341</v>
       </c>
       <c r="V39">
-        <v>0.05964469089178621</v>
+        <v>0.05807509376305499</v>
       </c>
       <c r="W39">
-        <v>0.1944058750656835</v>
+        <v>0.1947303682656007</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.4771575271342897</v>
+        <v>0.4646007501044399</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1333477681468382</v>
+        <v>0.1349571343134636</v>
       </c>
       <c r="C40">
-        <v>786.7398659430346</v>
+        <v>78.71794281397888</v>
       </c>
       <c r="D40">
-        <v>15860.98396081221</v>
+        <v>15574.67898754812</v>
       </c>
       <c r="E40">
-        <v>1759.449108371356</v>
+        <v>2181.166058236333</v>
       </c>
       <c r="F40">
-        <v>16025.24409486917</v>
+        <v>16446.96104473415</v>
       </c>
       <c r="G40">
         <v>951</v>
@@ -4555,37 +4555,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M40">
-        <v>3313.004745364506</v>
+        <v>3400.189080768835</v>
       </c>
       <c r="N40">
-        <v>-1773.780255568588</v>
+        <v>-1860.964590972916</v>
       </c>
       <c r="O40">
-        <v>-221.7225319460734</v>
+        <v>-232.6205738716145</v>
       </c>
       <c r="P40">
-        <v>-1552.057723622514</v>
+        <v>-1628.344017101302</v>
       </c>
       <c r="Q40">
-        <v>-530.057723622514</v>
+        <v>-606.3440171013017</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09572617452566125</v>
+        <v>0.0965446364031311</v>
       </c>
       <c r="T40">
-        <v>0.9731540690449143</v>
+        <v>0.9891074144390931</v>
       </c>
       <c r="U40">
         <v>0.2067366166625341</v>
       </c>
       <c r="V40">
-        <v>0.05807509376305499</v>
+        <v>0.05658598879477154</v>
       </c>
       <c r="W40">
-        <v>0.1947303682656007</v>
+        <v>0.195038220788599</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4646007501044399</v>
+        <v>0.4526879103581724</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1349571343134636</v>
+        <v>0.1365665004800889</v>
       </c>
       <c r="C41">
-        <v>78.71794281397888</v>
+        <v>-619.1511257956172</v>
       </c>
       <c r="D41">
-        <v>15574.67898754812</v>
+        <v>15298.52686880351</v>
       </c>
       <c r="E41">
-        <v>2181.166058236333</v>
+        <v>2602.883008101311</v>
       </c>
       <c r="F41">
-        <v>16446.96104473415</v>
+        <v>16868.67799459913</v>
       </c>
       <c r="G41">
         <v>951</v>
@@ -4637,37 +4637,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M41">
-        <v>3400.189080768835</v>
+        <v>3487.373416173164</v>
       </c>
       <c r="N41">
-        <v>-1860.964590972916</v>
+        <v>-1948.148926377245</v>
       </c>
       <c r="O41">
-        <v>-232.6205738716145</v>
+        <v>-243.5186157971556</v>
       </c>
       <c r="P41">
-        <v>-1628.344017101302</v>
+        <v>-1704.630310580089</v>
       </c>
       <c r="Q41">
-        <v>-606.3440171013017</v>
+        <v>-682.6303105800894</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.0965446364031311</v>
+        <v>0.09739038034318329</v>
       </c>
       <c r="T41">
-        <v>0.9891074144390931</v>
+        <v>1.005592538013078</v>
       </c>
       <c r="U41">
         <v>0.2067366166625341</v>
       </c>
       <c r="V41">
-        <v>0.05658598879477154</v>
+        <v>0.05517133907490225</v>
       </c>
       <c r="W41">
-        <v>0.195038220788599</v>
+        <v>0.1953306806854473</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.4526879103581724</v>
+        <v>0.441370712599218</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1365665004800889</v>
+        <v>0.1381758666467142</v>
       </c>
       <c r="C42">
-        <v>-619.1511257956172</v>
+        <v>-1307.397986941671</v>
       </c>
       <c r="D42">
-        <v>15298.52686880351</v>
+        <v>15031.99695752244</v>
       </c>
       <c r="E42">
-        <v>2602.883008101311</v>
+        <v>3024.599957966293</v>
       </c>
       <c r="F42">
-        <v>16868.67799459913</v>
+        <v>17290.39494446411</v>
       </c>
       <c r="G42">
         <v>951</v>
@@ -4719,37 +4719,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M42">
-        <v>3487.373416173164</v>
+        <v>3574.557751577493</v>
       </c>
       <c r="N42">
-        <v>-1948.148926377245</v>
+        <v>-2035.333261781575</v>
       </c>
       <c r="O42">
-        <v>-243.5186157971556</v>
+        <v>-254.4166577226969</v>
       </c>
       <c r="P42">
-        <v>-1704.630310580089</v>
+        <v>-1780.916604058878</v>
       </c>
       <c r="Q42">
-        <v>-682.6303105800894</v>
+        <v>-758.916604058878</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09739038034318329</v>
+        <v>0.09826479356933893</v>
       </c>
       <c r="T42">
-        <v>1.005592538013078</v>
+        <v>1.022636479335334</v>
       </c>
       <c r="U42">
         <v>0.2067366166625341</v>
       </c>
       <c r="V42">
-        <v>0.05517133907490225</v>
+        <v>0.05382569665844121</v>
       </c>
       <c r="W42">
-        <v>0.1953306806854473</v>
+        <v>0.1956088742458641</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.441370712599218</v>
+        <v>0.4306055732675297</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1381758666467142</v>
+        <v>0.1397852328133396</v>
       </c>
       <c r="C43">
-        <v>-1307.397986941671</v>
+        <v>-1986.516941314083</v>
       </c>
       <c r="D43">
-        <v>15031.99695752244</v>
+        <v>14774.594953015</v>
       </c>
       <c r="E43">
-        <v>3024.599957966293</v>
+        <v>3446.316907831271</v>
       </c>
       <c r="F43">
-        <v>17290.39494446411</v>
+        <v>17712.11189432909</v>
       </c>
       <c r="G43">
         <v>951</v>
@@ -4801,37 +4801,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M43">
-        <v>3574.557751577493</v>
+        <v>3661.742086981823</v>
       </c>
       <c r="N43">
-        <v>-2035.333261781575</v>
+        <v>-2122.517597185904</v>
       </c>
       <c r="O43">
-        <v>-254.4166577226969</v>
+        <v>-265.314699648238</v>
       </c>
       <c r="P43">
-        <v>-1780.916604058878</v>
+        <v>-1857.202897537666</v>
       </c>
       <c r="Q43">
-        <v>-758.916604058878</v>
+        <v>-835.2028975376663</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09826479356933893</v>
+        <v>0.09916935897570683</v>
       </c>
       <c r="T43">
-        <v>1.022636479335334</v>
+        <v>1.04026814277215</v>
       </c>
       <c r="U43">
         <v>0.2067366166625341</v>
       </c>
       <c r="V43">
-        <v>0.05382569665844121</v>
+        <v>0.05254413245228785</v>
       </c>
       <c r="W43">
-        <v>0.1956088742458641</v>
+        <v>0.1958738204938801</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.4306055732675297</v>
+        <v>0.4203530596183027</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1397852328133396</v>
+        <v>0.1413945989799649</v>
       </c>
       <c r="C44">
-        <v>-1986.516941314079</v>
+        <v>-2656.969002751201</v>
       </c>
       <c r="D44">
-        <v>14774.594953015</v>
+        <v>14525.85984144286</v>
       </c>
       <c r="E44">
-        <v>3446.316907831268</v>
+        <v>3868.033857696246</v>
       </c>
       <c r="F44">
-        <v>17712.11189432908</v>
+        <v>18133.82884419406</v>
       </c>
       <c r="G44">
         <v>951</v>
@@ -4883,37 +4883,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M44">
-        <v>3661.742086981822</v>
+        <v>3748.926422386151</v>
       </c>
       <c r="N44">
-        <v>-2122.517597185903</v>
+        <v>-2209.701932590232</v>
       </c>
       <c r="O44">
-        <v>-265.3146996482379</v>
+        <v>-276.2127415737791</v>
       </c>
       <c r="P44">
-        <v>-1857.202897537666</v>
+        <v>-1933.489191016453</v>
       </c>
       <c r="Q44">
-        <v>-835.2028975376656</v>
+        <v>-911.4891910164533</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09916935897570683</v>
+        <v>0.1001056635191403</v>
       </c>
       <c r="T44">
-        <v>1.04026814277215</v>
+        <v>1.058518461066398</v>
       </c>
       <c r="U44">
         <v>0.2067366166625341</v>
       </c>
       <c r="V44">
-        <v>0.05254413245228785</v>
+        <v>0.05132217588363</v>
       </c>
       <c r="W44">
-        <v>0.1958738204938801</v>
+        <v>0.1961264436605929</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.4203530596183028</v>
+        <v>0.41057740706904</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1413945989799649</v>
+        <v>0.1430039651465903</v>
       </c>
       <c r="C45">
-        <v>-2656.969002751201</v>
+        <v>-3319.184653823531</v>
       </c>
       <c r="D45">
-        <v>14525.85984144286</v>
+        <v>14285.36114023551</v>
       </c>
       <c r="E45">
-        <v>3868.033857696246</v>
+        <v>4289.750807561224</v>
       </c>
       <c r="F45">
-        <v>18133.82884419406</v>
+        <v>18555.54579405904</v>
       </c>
       <c r="G45">
         <v>951</v>
@@ -4965,37 +4965,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M45">
-        <v>3748.926422386151</v>
+        <v>3836.11075779048</v>
       </c>
       <c r="N45">
-        <v>-2209.701932590232</v>
+        <v>-2296.886267994562</v>
       </c>
       <c r="O45">
-        <v>-276.2127415737791</v>
+        <v>-287.1107834993202</v>
       </c>
       <c r="P45">
-        <v>-1933.489191016453</v>
+        <v>-2009.775484495242</v>
       </c>
       <c r="Q45">
-        <v>-911.4891910164533</v>
+        <v>-987.7754844952417</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1001056635191403</v>
+        <v>0.1010754075105535</v>
       </c>
       <c r="T45">
-        <v>1.058518461066398</v>
+        <v>1.077420576442583</v>
       </c>
       <c r="U45">
         <v>0.2067366166625341</v>
       </c>
       <c r="V45">
-        <v>0.05132217588363</v>
+        <v>0.05015576279536568</v>
       </c>
       <c r="W45">
-        <v>0.1961264436605929</v>
+        <v>0.1963675839560916</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.41057740706904</v>
+        <v>0.4012461023629255</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1430039651465903</v>
+        <v>0.1446133313132156</v>
       </c>
       <c r="C46">
-        <v>-3319.184653823531</v>
+        <v>-3973.5663321374</v>
       </c>
       <c r="D46">
-        <v>14285.36114023551</v>
+        <v>14052.69641178662</v>
       </c>
       <c r="E46">
-        <v>4289.750807561224</v>
+        <v>4711.467757426202</v>
       </c>
       <c r="F46">
-        <v>18555.54579405904</v>
+        <v>18977.26274392402</v>
       </c>
       <c r="G46">
         <v>951</v>
@@ -5047,37 +5047,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M46">
-        <v>3836.11075779048</v>
+        <v>3923.295093194809</v>
       </c>
       <c r="N46">
-        <v>-2296.886267994562</v>
+        <v>-2384.070603398891</v>
       </c>
       <c r="O46">
-        <v>-287.1107834993202</v>
+        <v>-298.0088254248614</v>
       </c>
       <c r="P46">
-        <v>-2009.775484495242</v>
+        <v>-2086.06177797403</v>
       </c>
       <c r="Q46">
-        <v>-987.7754844952417</v>
+        <v>-1064.06177797403</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1010754075105535</v>
+        <v>0.1020804149198363</v>
       </c>
       <c r="T46">
-        <v>1.077420576442583</v>
+        <v>1.097010041468812</v>
       </c>
       <c r="U46">
         <v>0.2067366166625341</v>
       </c>
       <c r="V46">
-        <v>0.05015576279536568</v>
+        <v>0.049041190288802</v>
       </c>
       <c r="W46">
-        <v>0.1963675839560916</v>
+        <v>0.1965980069051236</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4012461023629255</v>
+        <v>0.392329522310416</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1446133313132156</v>
+        <v>0.146222697479841</v>
       </c>
       <c r="C47">
-        <v>-3973.5663321374</v>
+        <v>-4620.490677566782</v>
       </c>
       <c r="D47">
-        <v>14052.69641178662</v>
+        <v>13827.48901622221</v>
       </c>
       <c r="E47">
-        <v>4711.467757426202</v>
+        <v>5133.184707291181</v>
       </c>
       <c r="F47">
-        <v>18977.26274392402</v>
+        <v>19398.979693789</v>
       </c>
       <c r="G47">
         <v>951</v>
@@ -5129,37 +5129,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M47">
-        <v>3923.295093194809</v>
+        <v>4010.479428599138</v>
       </c>
       <c r="N47">
-        <v>-2384.070603398891</v>
+        <v>-2471.25493880322</v>
       </c>
       <c r="O47">
-        <v>-298.0088254248614</v>
+        <v>-308.9068673504025</v>
       </c>
       <c r="P47">
-        <v>-2086.06177797403</v>
+        <v>-2162.348071452817</v>
       </c>
       <c r="Q47">
-        <v>-1064.06177797403</v>
+        <v>-1140.348071452817</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1020804149198363</v>
+        <v>0.1031226448257592</v>
       </c>
       <c r="T47">
-        <v>1.097010041468812</v>
+        <v>1.117325042236753</v>
       </c>
       <c r="U47">
         <v>0.2067366166625341</v>
       </c>
       <c r="V47">
-        <v>0.049041190288802</v>
+        <v>0.04797507745643674</v>
       </c>
       <c r="W47">
-        <v>0.1965980069051236</v>
+        <v>0.1968184114650674</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.392329522310416</v>
+        <v>0.3838006196514939</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.146222697479841</v>
+        <v>0.1478320636464663</v>
       </c>
       <c r="C48">
-        <v>-4620.490677566782</v>
+        <v>-5260.310566809705</v>
       </c>
       <c r="D48">
-        <v>13827.48901622221</v>
+        <v>13609.38607684427</v>
       </c>
       <c r="E48">
-        <v>5133.184707291181</v>
+        <v>5554.901657156159</v>
       </c>
       <c r="F48">
-        <v>19398.979693789</v>
+        <v>19820.69664365397</v>
       </c>
       <c r="G48">
         <v>951</v>
@@ -5211,37 +5211,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M48">
-        <v>4010.479428599138</v>
+        <v>4097.663764003468</v>
       </c>
       <c r="N48">
-        <v>-2471.25493880322</v>
+        <v>-2558.439274207549</v>
       </c>
       <c r="O48">
-        <v>-308.9068673504025</v>
+        <v>-319.8049092759437</v>
       </c>
       <c r="P48">
-        <v>-2162.348071452817</v>
+        <v>-2238.634364931605</v>
       </c>
       <c r="Q48">
-        <v>-1140.348071452817</v>
+        <v>-1216.634364931605</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1031226448257592</v>
+        <v>0.1042042041620943</v>
       </c>
       <c r="T48">
-        <v>1.117325042236753</v>
+        <v>1.138406646807258</v>
       </c>
       <c r="U48">
         <v>0.2067366166625341</v>
       </c>
       <c r="V48">
-        <v>0.04797507745643674</v>
+        <v>0.04695433112757638</v>
       </c>
       <c r="W48">
-        <v>0.1968184114650674</v>
+        <v>0.1970294371075667</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3838006196514939</v>
+        <v>0.3756346490206111</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1478320636464663</v>
+        <v>0.1494414298130917</v>
       </c>
       <c r="C49">
-        <v>-5260.310566809705</v>
+        <v>-5893.356958386499</v>
       </c>
       <c r="D49">
-        <v>13609.38607684427</v>
+        <v>13398.05663513245</v>
       </c>
       <c r="E49">
-        <v>5554.901657156159</v>
+        <v>5976.618607021137</v>
       </c>
       <c r="F49">
-        <v>19820.69664365397</v>
+        <v>20242.41359351895</v>
       </c>
       <c r="G49">
         <v>951</v>
@@ -5293,37 +5293,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M49">
-        <v>4097.663764003468</v>
+        <v>4184.848099407796</v>
       </c>
       <c r="N49">
-        <v>-2558.439274207549</v>
+        <v>-2645.623609611878</v>
       </c>
       <c r="O49">
-        <v>-319.8049092759437</v>
+        <v>-330.7029512014847</v>
       </c>
       <c r="P49">
-        <v>-2238.634364931605</v>
+        <v>-2314.920658410393</v>
       </c>
       <c r="Q49">
-        <v>-1216.634364931605</v>
+        <v>-1292.920658410393</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1042042041620943</v>
+        <v>0.1053273619344423</v>
       </c>
       <c r="T49">
-        <v>1.138406646807258</v>
+        <v>1.160299082322782</v>
       </c>
       <c r="U49">
         <v>0.2067366166625341</v>
       </c>
       <c r="V49">
-        <v>0.04695433112757638</v>
+        <v>0.04597611589575188</v>
       </c>
       <c r="W49">
-        <v>0.1970294371075667</v>
+        <v>0.1972316700149618</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3756346490206111</v>
+        <v>0.367808927166015</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1494414298130916</v>
+        <v>0.151050795979717</v>
       </c>
       <c r="C50">
-        <v>-5893.356958386494</v>
+        <v>-6519.940568369344</v>
       </c>
       <c r="D50">
-        <v>13398.05663513246</v>
+        <v>13193.18997501459</v>
       </c>
       <c r="E50">
-        <v>5976.618607021137</v>
+        <v>6398.335556886115</v>
       </c>
       <c r="F50">
-        <v>20242.41359351895</v>
+        <v>20664.13054338393</v>
       </c>
       <c r="G50">
         <v>951</v>
@@ -5375,37 +5375,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M50">
-        <v>4184.848099407796</v>
+        <v>4272.032434812126</v>
       </c>
       <c r="N50">
-        <v>-2645.623609611878</v>
+        <v>-2732.807945016207</v>
       </c>
       <c r="O50">
-        <v>-330.7029512014847</v>
+        <v>-341.6009931270259</v>
       </c>
       <c r="P50">
-        <v>-2314.920658410393</v>
+        <v>-2391.206951889181</v>
       </c>
       <c r="Q50">
-        <v>-1292.920658410393</v>
+        <v>-1369.206951889181</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1053273619344423</v>
+        <v>0.1064945651096274</v>
       </c>
       <c r="T50">
-        <v>1.160299082322782</v>
+        <v>1.183050044721268</v>
       </c>
       <c r="U50">
         <v>0.2067366166625341</v>
       </c>
       <c r="V50">
-        <v>0.04597611589575188</v>
+        <v>0.04503782781624673</v>
       </c>
       <c r="W50">
-        <v>0.1972316700149618</v>
+        <v>0.1974256485179735</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.367808927166015</v>
+        <v>0.3603026225299739</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.151050795979717</v>
+        <v>0.1526601621463423</v>
       </c>
       <c r="C51">
-        <v>-6519.940568369344</v>
+        <v>-7140.353394687998</v>
       </c>
       <c r="D51">
-        <v>13193.18997501459</v>
+        <v>12994.49409856091</v>
       </c>
       <c r="E51">
-        <v>6398.335556886115</v>
+        <v>6820.052506751093</v>
       </c>
       <c r="F51">
-        <v>20664.13054338393</v>
+        <v>21085.84749324891</v>
       </c>
       <c r="G51">
         <v>951</v>
@@ -5457,37 +5457,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M51">
-        <v>4272.032434812126</v>
+        <v>4359.216770216455</v>
       </c>
       <c r="N51">
-        <v>-2732.807945016207</v>
+        <v>-2819.992280420537</v>
       </c>
       <c r="O51">
-        <v>-341.6009931270259</v>
+        <v>-352.4990350525671</v>
       </c>
       <c r="P51">
-        <v>-2391.206951889181</v>
+        <v>-2467.493245367969</v>
       </c>
       <c r="Q51">
-        <v>-1369.206951889181</v>
+        <v>-1445.493245367969</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1064945651096274</v>
+        <v>0.1077084564118199</v>
       </c>
       <c r="T51">
-        <v>1.183050044721268</v>
+        <v>1.206711045615694</v>
       </c>
       <c r="U51">
         <v>0.2067366166625341</v>
       </c>
       <c r="V51">
-        <v>0.04503782781624673</v>
+        <v>0.04413707125992179</v>
       </c>
       <c r="W51">
-        <v>0.1974256485179735</v>
+        <v>0.1976118678808647</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3603026225299739</v>
+        <v>0.3530965700793743</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1526601621463423</v>
+        <v>0.1542695283129676</v>
       </c>
       <c r="C52">
-        <v>-7140.353394687998</v>
+        <v>-7754.87010573841</v>
       </c>
       <c r="D52">
-        <v>12994.49409856091</v>
+        <v>12801.69433737548</v>
       </c>
       <c r="E52">
-        <v>6820.052506751093</v>
+        <v>7241.769456616072</v>
       </c>
       <c r="F52">
-        <v>21085.84749324891</v>
+        <v>21507.56444311389</v>
       </c>
       <c r="G52">
         <v>951</v>
@@ -5539,37 +5539,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M52">
-        <v>4359.216770216455</v>
+        <v>4446.401105620784</v>
       </c>
       <c r="N52">
-        <v>-2819.992280420537</v>
+        <v>-2907.176615824865</v>
       </c>
       <c r="O52">
-        <v>-352.4990350525671</v>
+        <v>-363.3970769781081</v>
       </c>
       <c r="P52">
-        <v>-2467.493245367969</v>
+        <v>-2543.779538846757</v>
       </c>
       <c r="Q52">
-        <v>-1445.493245367969</v>
+        <v>-1521.779538846757</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1077084564118199</v>
+        <v>0.1089718942977755</v>
       </c>
       <c r="T52">
-        <v>1.206711045615694</v>
+        <v>1.231337801648667</v>
       </c>
       <c r="U52">
         <v>0.2067366166625341</v>
       </c>
       <c r="V52">
-        <v>0.04413707125992179</v>
+        <v>0.04327163849011941</v>
       </c>
       <c r="W52">
-        <v>0.1976118678808647</v>
+        <v>0.1977907845236425</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3530965700793743</v>
+        <v>0.3461731079209553</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1542695283129676</v>
+        <v>0.155878894479593</v>
       </c>
       <c r="C53">
-        <v>-7754.87010573841</v>
+        <v>-8363.749307181697</v>
       </c>
       <c r="D53">
-        <v>12801.69433737548</v>
+        <v>12614.53208579717</v>
       </c>
       <c r="E53">
-        <v>7241.769456616072</v>
+        <v>7663.48640648105</v>
       </c>
       <c r="F53">
-        <v>21507.56444311389</v>
+        <v>21929.28139297886</v>
       </c>
       <c r="G53">
         <v>951</v>
@@ -5621,37 +5621,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M53">
-        <v>4446.401105620784</v>
+        <v>4533.585441025113</v>
       </c>
       <c r="N53">
-        <v>-2907.176615824865</v>
+        <v>-2994.360951229195</v>
       </c>
       <c r="O53">
-        <v>-363.3970769781081</v>
+        <v>-374.2951189036493</v>
       </c>
       <c r="P53">
-        <v>-2543.779538846757</v>
+        <v>-2620.065832325545</v>
       </c>
       <c r="Q53">
-        <v>-1521.779538846757</v>
+        <v>-1598.065832325545</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1089718942977755</v>
+        <v>0.1102879754289791</v>
       </c>
       <c r="T53">
-        <v>1.231337801648667</v>
+        <v>1.256990672516348</v>
       </c>
       <c r="U53">
         <v>0.2067366166625341</v>
       </c>
       <c r="V53">
-        <v>0.04327163849011941</v>
+        <v>0.04243949159607865</v>
       </c>
       <c r="W53">
-        <v>0.1977907845236425</v>
+        <v>0.1979628197570827</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3461731079209553</v>
+        <v>0.3395159327686292</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.155878894479593</v>
+        <v>0.1574882606462183</v>
       </c>
       <c r="C54">
-        <v>-8363.749307181697</v>
+        <v>-8967.234699219818</v>
       </c>
       <c r="D54">
-        <v>12614.53208579717</v>
+        <v>12432.76364362402</v>
       </c>
       <c r="E54">
-        <v>7663.48640648105</v>
+        <v>8085.203356346028</v>
       </c>
       <c r="F54">
-        <v>21929.28139297886</v>
+        <v>22350.99834284384</v>
       </c>
       <c r="G54">
         <v>951</v>
@@ -5703,37 +5703,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M54">
-        <v>4533.585441025113</v>
+        <v>4620.769776429443</v>
       </c>
       <c r="N54">
-        <v>-2994.360951229195</v>
+        <v>-3081.545286633524</v>
       </c>
       <c r="O54">
-        <v>-374.2951189036493</v>
+        <v>-385.1931608291905</v>
       </c>
       <c r="P54">
-        <v>-2620.065832325545</v>
+        <v>-2696.352125804333</v>
       </c>
       <c r="Q54">
-        <v>-1598.065832325545</v>
+        <v>-1674.352125804333</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1102879754289791</v>
+        <v>0.1116600600125744</v>
       </c>
       <c r="T54">
-        <v>1.256990672516348</v>
+        <v>1.283735154910312</v>
       </c>
       <c r="U54">
         <v>0.2067366166625341</v>
       </c>
       <c r="V54">
-        <v>0.04243949159607865</v>
+        <v>0.04163874647162433</v>
       </c>
       <c r="W54">
-        <v>0.1979628197570827</v>
+        <v>0.1981283630949214</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3395159327686292</v>
+        <v>0.3331099717729947</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1574882606462183</v>
+        <v>0.1590976268128437</v>
       </c>
       <c r="C55">
-        <v>-8967.234699219818</v>
+        <v>-9565.556135238341</v>
       </c>
       <c r="D55">
-        <v>12432.76364362402</v>
+        <v>12256.15915747048</v>
       </c>
       <c r="E55">
-        <v>8085.203356346028</v>
+        <v>8506.920306211006</v>
       </c>
       <c r="F55">
-        <v>22350.99834284384</v>
+        <v>22772.71529270882</v>
       </c>
       <c r="G55">
         <v>951</v>
@@ -5785,37 +5785,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M55">
-        <v>4620.769776429443</v>
+        <v>4707.954111833771</v>
       </c>
       <c r="N55">
-        <v>-3081.545286633524</v>
+        <v>-3168.729622037853</v>
       </c>
       <c r="O55">
-        <v>-385.1931608291905</v>
+        <v>-396.0912027547316</v>
       </c>
       <c r="P55">
-        <v>-2696.352125804333</v>
+        <v>-2772.638419283121</v>
       </c>
       <c r="Q55">
-        <v>-1674.352125804333</v>
+        <v>-1750.638419283121</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1116600600125744</v>
+        <v>0.1130918004476304</v>
       </c>
       <c r="T55">
-        <v>1.283735154910312</v>
+        <v>1.311642440886624</v>
       </c>
       <c r="U55">
         <v>0.2067366166625341</v>
       </c>
       <c r="V55">
-        <v>0.04163874647162433</v>
+        <v>0.04086765857400167</v>
       </c>
       <c r="W55">
-        <v>0.1981283630949214</v>
+        <v>0.1982877751980254</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3331099717729947</v>
+        <v>0.3269412685920133</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1590976268128437</v>
+        <v>0.1607069929794691</v>
       </c>
       <c r="C56">
-        <v>-9565.556135238341</v>
+        <v>-10158.93059148618</v>
       </c>
       <c r="D56">
-        <v>12256.15915747048</v>
+        <v>12084.50165108762</v>
       </c>
       <c r="E56">
-        <v>8506.920306211006</v>
+        <v>8928.637256075985</v>
       </c>
       <c r="F56">
-        <v>22772.71529270882</v>
+        <v>23194.4322425738</v>
       </c>
       <c r="G56">
         <v>951</v>
@@ -5867,37 +5867,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M56">
-        <v>4707.954111833771</v>
+        <v>4795.138447238101</v>
       </c>
       <c r="N56">
-        <v>-3168.729622037853</v>
+        <v>-3255.913957442182</v>
       </c>
       <c r="O56">
-        <v>-396.0912027547316</v>
+        <v>-406.9892446802727</v>
       </c>
       <c r="P56">
-        <v>-2772.638419283121</v>
+        <v>-2848.924712761909</v>
       </c>
       <c r="Q56">
-        <v>-1750.638419283121</v>
+        <v>-1826.924712761909</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1130918004476304</v>
+        <v>0.1145871737909111</v>
       </c>
       <c r="T56">
-        <v>1.311642440886624</v>
+        <v>1.340790050684104</v>
       </c>
       <c r="U56">
         <v>0.2067366166625341</v>
       </c>
       <c r="V56">
-        <v>0.04086765857400167</v>
+        <v>0.04012461023629255</v>
       </c>
       <c r="W56">
-        <v>0.1982877751980254</v>
+        <v>0.1984413904973801</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3269412685920133</v>
+        <v>0.3209968818903404</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1607069929794691</v>
+        <v>0.1623163591460944</v>
       </c>
       <c r="C57">
-        <v>-10158.93059148618</v>
+        <v>-10747.56305639401</v>
       </c>
       <c r="D57">
-        <v>12084.50165108762</v>
+        <v>11917.58613604476</v>
       </c>
       <c r="E57">
-        <v>8928.637256075985</v>
+        <v>9350.354205940963</v>
       </c>
       <c r="F57">
-        <v>23194.4322425738</v>
+        <v>23616.14919243878</v>
       </c>
       <c r="G57">
         <v>951</v>
@@ -5949,37 +5949,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M57">
-        <v>4795.138447238101</v>
+        <v>4882.32278264243</v>
       </c>
       <c r="N57">
-        <v>-3255.913957442182</v>
+        <v>-3343.098292846511</v>
       </c>
       <c r="O57">
-        <v>-406.9892446802727</v>
+        <v>-417.8872866058139</v>
       </c>
       <c r="P57">
-        <v>-2848.924712761909</v>
+        <v>-2925.211006240697</v>
       </c>
       <c r="Q57">
-        <v>-1826.924712761909</v>
+        <v>-1903.211006240697</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1145871737909111</v>
+        <v>0.1161505186497954</v>
       </c>
       <c r="T57">
-        <v>1.340790050684104</v>
+        <v>1.371262551836016</v>
       </c>
       <c r="U57">
         <v>0.2067366166625341</v>
       </c>
       <c r="V57">
-        <v>0.04012461023629255</v>
+        <v>0.03940809933921589</v>
       </c>
       <c r="W57">
-        <v>0.1984413904973801</v>
+        <v>0.1985895195360436</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3209968818903404</v>
+        <v>0.3152647947137271</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1623163591460944</v>
+        <v>0.1639257253127197</v>
       </c>
       <c r="C58">
-        <v>-10747.56305639401</v>
+        <v>-11331.64734719525</v>
       </c>
       <c r="D58">
-        <v>11917.58613604476</v>
+        <v>11755.21879510851</v>
       </c>
       <c r="E58">
-        <v>9350.354205940963</v>
+        <v>9772.071155805945</v>
       </c>
       <c r="F58">
-        <v>23616.14919243878</v>
+        <v>24037.86614230376</v>
       </c>
       <c r="G58">
         <v>951</v>
@@ -6031,37 +6031,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M58">
-        <v>4882.32278264243</v>
+        <v>4969.507118046759</v>
       </c>
       <c r="N58">
-        <v>-3343.098292846511</v>
+        <v>-3430.282628250841</v>
       </c>
       <c r="O58">
-        <v>-417.8872866058139</v>
+        <v>-428.7853285313551</v>
       </c>
       <c r="P58">
-        <v>-2925.211006240697</v>
+        <v>-3001.497299719486</v>
       </c>
       <c r="Q58">
-        <v>-1903.211006240697</v>
+        <v>-1979.497299719486</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1161505186497954</v>
+        <v>0.1177865772230464</v>
       </c>
       <c r="T58">
-        <v>1.371262551836016</v>
+        <v>1.4031523786229</v>
       </c>
       <c r="U58">
         <v>0.2067366166625341</v>
       </c>
       <c r="V58">
-        <v>0.03940809933921589</v>
+        <v>0.03871672917536999</v>
       </c>
       <c r="W58">
-        <v>0.1985895195360436</v>
+        <v>0.1987324510645785</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3152647947137271</v>
+        <v>0.3097338334029599</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1639257253127197</v>
+        <v>0.1655350914793451</v>
       </c>
       <c r="C59">
-        <v>-11331.64734719525</v>
+        <v>-11911.36686068954</v>
       </c>
       <c r="D59">
-        <v>11755.21879510851</v>
+        <v>11597.21623147919</v>
       </c>
       <c r="E59">
-        <v>9772.071155805945</v>
+        <v>10193.78810567092</v>
       </c>
       <c r="F59">
-        <v>24037.86614230376</v>
+        <v>24459.58309216874</v>
       </c>
       <c r="G59">
         <v>951</v>
@@ -6113,37 +6113,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M59">
-        <v>4969.507118046759</v>
+        <v>5056.691453451089</v>
       </c>
       <c r="N59">
-        <v>-3430.282628250841</v>
+        <v>-3517.46696365517</v>
       </c>
       <c r="O59">
-        <v>-428.7853285313551</v>
+        <v>-439.6833704568963</v>
       </c>
       <c r="P59">
-        <v>-3001.497299719486</v>
+        <v>-3077.783593198274</v>
       </c>
       <c r="Q59">
-        <v>-1979.497299719486</v>
+        <v>-2055.783593198274</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1177865772230464</v>
+        <v>0.1195005433474047</v>
       </c>
       <c r="T59">
-        <v>1.4031523786229</v>
+        <v>1.436560768590112</v>
       </c>
       <c r="U59">
         <v>0.2067366166625341</v>
       </c>
       <c r="V59">
-        <v>0.03871672917536999</v>
+        <v>0.03804919936200154</v>
       </c>
       <c r="W59">
-        <v>0.1987324510645785</v>
+        <v>0.1988704539197156</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3097338334029599</v>
+        <v>0.3043935948960124</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.165535091479345</v>
+        <v>0.1671444576459704</v>
       </c>
       <c r="C60">
-        <v>-11911.36686068953</v>
+        <v>-12486.89526426288</v>
       </c>
       <c r="D60">
-        <v>11597.2162314792</v>
+        <v>11443.40477777083</v>
       </c>
       <c r="E60">
-        <v>10193.78810567092</v>
+        <v>10615.50505553589</v>
       </c>
       <c r="F60">
-        <v>24459.58309216873</v>
+        <v>24881.30004203371</v>
       </c>
       <c r="G60">
         <v>951</v>
@@ -6195,37 +6195,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M60">
-        <v>5056.691453451087</v>
+        <v>5143.875788855416</v>
       </c>
       <c r="N60">
-        <v>-3517.466963655168</v>
+        <v>-3604.651299059498</v>
       </c>
       <c r="O60">
-        <v>-439.6833704568961</v>
+        <v>-450.5814123824372</v>
       </c>
       <c r="P60">
-        <v>-3077.783593198272</v>
+        <v>-3154.069886677061</v>
       </c>
       <c r="Q60">
-        <v>-2055.783593198272</v>
+        <v>-2132.069886677061</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1195005433474047</v>
+        <v>0.1212981175753902</v>
       </c>
       <c r="T60">
-        <v>1.436560768590111</v>
+        <v>1.471598836116699</v>
       </c>
       <c r="U60">
         <v>0.2067366166625341</v>
       </c>
       <c r="V60">
-        <v>0.03804919936200155</v>
+        <v>0.03740429767789983</v>
       </c>
       <c r="W60">
-        <v>0.1988704539197156</v>
+        <v>0.1990037787119668</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3043935948960125</v>
+        <v>0.2992343814231987</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1671444576459704</v>
+        <v>0.1687538238125957</v>
       </c>
       <c r="C61">
-        <v>-12486.89526426288</v>
+        <v>-13058.39713263852</v>
       </c>
       <c r="D61">
-        <v>11443.40477777083</v>
+        <v>11293.61985926017</v>
       </c>
       <c r="E61">
-        <v>10615.50505553589</v>
+        <v>11037.22200540088</v>
       </c>
       <c r="F61">
-        <v>24881.30004203371</v>
+        <v>25303.01699189869</v>
       </c>
       <c r="G61">
         <v>951</v>
@@ -6277,37 +6277,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M61">
-        <v>5143.875788855416</v>
+        <v>5231.060124259746</v>
       </c>
       <c r="N61">
-        <v>-3604.651299059498</v>
+        <v>-3691.835634463827</v>
       </c>
       <c r="O61">
-        <v>-450.5814123824372</v>
+        <v>-461.4794543079784</v>
       </c>
       <c r="P61">
-        <v>-3154.069886677061</v>
+        <v>-3230.356180155849</v>
       </c>
       <c r="Q61">
-        <v>-2132.069886677061</v>
+        <v>-2208.356180155849</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1212981175753902</v>
+        <v>0.1231855705147749</v>
       </c>
       <c r="T61">
-        <v>1.471598836116699</v>
+        <v>1.508388807019617</v>
       </c>
       <c r="U61">
         <v>0.2067366166625341</v>
       </c>
       <c r="V61">
-        <v>0.03740429767789983</v>
+        <v>0.0367808927166015</v>
       </c>
       <c r="W61">
-        <v>0.1990037787119668</v>
+        <v>0.1991326593444763</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2992343814231987</v>
+        <v>0.294247141732812</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1687538238125957</v>
+        <v>0.1703631899792211</v>
       </c>
       <c r="C62">
-        <v>-13058.39713263852</v>
+        <v>-13626.02853526642</v>
       </c>
       <c r="D62">
-        <v>11293.61985926017</v>
+        <v>11147.70540649725</v>
       </c>
       <c r="E62">
-        <v>11037.22200540088</v>
+        <v>11458.93895526585</v>
       </c>
       <c r="F62">
-        <v>25303.01699189869</v>
+        <v>25724.73394176367</v>
       </c>
       <c r="G62">
         <v>951</v>
@@ -6359,37 +6359,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M62">
-        <v>5231.060124259746</v>
+        <v>5318.244459664075</v>
       </c>
       <c r="N62">
-        <v>-3691.835634463827</v>
+        <v>-3779.019969868157</v>
       </c>
       <c r="O62">
-        <v>-461.4794543079784</v>
+        <v>-472.3774962335196</v>
       </c>
       <c r="P62">
-        <v>-3230.356180155849</v>
+        <v>-3306.642473634637</v>
       </c>
       <c r="Q62">
-        <v>-2208.356180155849</v>
+        <v>-2284.642473634637</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1231855705147749</v>
+        <v>0.1251698159125897</v>
       </c>
       <c r="T62">
-        <v>1.508388807019617</v>
+        <v>1.547065443097043</v>
       </c>
       <c r="U62">
         <v>0.2067366166625341</v>
       </c>
       <c r="V62">
-        <v>0.0367808927166015</v>
+        <v>0.03617792726223098</v>
       </c>
       <c r="W62">
-        <v>0.1991326593444763</v>
+        <v>0.1992573143824772</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.294247141732812</v>
+        <v>0.2894234180978479</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1703631899792211</v>
+        <v>0.1719725561458464</v>
       </c>
       <c r="C63">
-        <v>-13626.02853526642</v>
+        <v>-14189.93757875899</v>
       </c>
       <c r="D63">
-        <v>11147.70540649725</v>
+        <v>11005.51331286966</v>
       </c>
       <c r="E63">
-        <v>11458.93895526585</v>
+        <v>11880.65590513083</v>
       </c>
       <c r="F63">
-        <v>25724.73394176367</v>
+        <v>26146.45089162865</v>
       </c>
       <c r="G63">
         <v>951</v>
@@ -6441,37 +6441,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M63">
-        <v>5318.244459664075</v>
+        <v>5405.428795068405</v>
       </c>
       <c r="N63">
-        <v>-3779.019969868157</v>
+        <v>-3866.204305272486</v>
       </c>
       <c r="O63">
-        <v>-472.3774962335196</v>
+        <v>-483.2755381590608</v>
       </c>
       <c r="P63">
-        <v>-3306.642473634637</v>
+        <v>-3382.928767113425</v>
       </c>
       <c r="Q63">
-        <v>-2284.642473634637</v>
+        <v>-2360.928767113425</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1251698159125897</v>
+        <v>0.1272584952787104</v>
       </c>
       <c r="T63">
-        <v>1.547065443097043</v>
+        <v>1.587777691599597</v>
       </c>
       <c r="U63">
         <v>0.2067366166625341</v>
       </c>
       <c r="V63">
-        <v>0.03617792726223098</v>
+        <v>0.03559441230638855</v>
       </c>
       <c r="W63">
-        <v>0.1992573143824772</v>
+        <v>0.1993779482902201</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2894234180978479</v>
+        <v>0.2847552984511084</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1719725561458464</v>
+        <v>0.1735819223124718</v>
       </c>
       <c r="C64">
-        <v>-14189.93757875899</v>
+        <v>-14750.2649083361</v>
       </c>
       <c r="D64">
-        <v>11005.51331286966</v>
+        <v>10866.90293315753</v>
       </c>
       <c r="E64">
-        <v>11880.65590513083</v>
+        <v>12302.37285499581</v>
       </c>
       <c r="F64">
-        <v>26146.45089162865</v>
+        <v>26568.16784149363</v>
       </c>
       <c r="G64">
         <v>951</v>
@@ -6523,37 +6523,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M64">
-        <v>5405.428795068405</v>
+        <v>5492.613130472733</v>
       </c>
       <c r="N64">
-        <v>-3866.204305272486</v>
+        <v>-3953.388640676815</v>
       </c>
       <c r="O64">
-        <v>-483.2755381590608</v>
+        <v>-494.1735800846018</v>
       </c>
       <c r="P64">
-        <v>-3382.928767113425</v>
+        <v>-3459.215060592213</v>
       </c>
       <c r="Q64">
-        <v>-2360.928767113425</v>
+        <v>-2437.215060592213</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1272584952787104</v>
+        <v>0.1294600762321891</v>
       </c>
       <c r="T64">
-        <v>1.587777691599597</v>
+        <v>1.63069060218337</v>
       </c>
       <c r="U64">
         <v>0.2067366166625341</v>
       </c>
       <c r="V64">
-        <v>0.03559441230638855</v>
+        <v>0.03502942163485857</v>
       </c>
       <c r="W64">
-        <v>0.1993779482902201</v>
+        <v>0.1994947525500981</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2847552984511084</v>
+        <v>0.2802353730788686</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1735819223124718</v>
+        <v>0.1751912884790971</v>
       </c>
       <c r="C65">
-        <v>-14750.2649083361</v>
+        <v>-15307.14417184826</v>
       </c>
       <c r="D65">
-        <v>10866.90293315753</v>
+        <v>10731.74061951034</v>
       </c>
       <c r="E65">
-        <v>12302.37285499581</v>
+        <v>12724.08980486079</v>
       </c>
       <c r="F65">
-        <v>26568.16784149363</v>
+        <v>26989.8847913586</v>
       </c>
       <c r="G65">
         <v>951</v>
@@ -6605,37 +6605,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M65">
-        <v>5492.613130472733</v>
+        <v>5579.797465877063</v>
       </c>
       <c r="N65">
-        <v>-3953.388640676815</v>
+        <v>-4040.572976081144</v>
       </c>
       <c r="O65">
-        <v>-494.1735800846018</v>
+        <v>-505.071622010143</v>
       </c>
       <c r="P65">
-        <v>-3459.215060592213</v>
+        <v>-3535.501354071001</v>
       </c>
       <c r="Q65">
-        <v>-2437.215060592213</v>
+        <v>-2513.501354071001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1294600762321891</v>
+        <v>0.1317839672386388</v>
       </c>
       <c r="T65">
-        <v>1.63069060218337</v>
+        <v>1.67598756335513</v>
       </c>
       <c r="U65">
         <v>0.2067366166625341</v>
       </c>
       <c r="V65">
-        <v>0.03502942163485857</v>
+        <v>0.03448208692181391</v>
       </c>
       <c r="W65">
-        <v>0.1994947525500981</v>
+        <v>0.1996079066768549</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2802353730788686</v>
+        <v>0.2758566953745112</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1751912884790971</v>
+        <v>0.1768006546457224</v>
       </c>
       <c r="C66">
-        <v>-15307.14417184826</v>
+        <v>-15860.70244959627</v>
       </c>
       <c r="D66">
-        <v>10731.74061951034</v>
+        <v>10599.89929162731</v>
       </c>
       <c r="E66">
-        <v>12724.08980486079</v>
+        <v>13145.80675472577</v>
       </c>
       <c r="F66">
-        <v>26989.8847913586</v>
+        <v>27411.60174122358</v>
       </c>
       <c r="G66">
         <v>951</v>
@@ -6687,37 +6687,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M66">
-        <v>5579.797465877063</v>
+        <v>5666.981801281392</v>
       </c>
       <c r="N66">
-        <v>-4040.572976081144</v>
+        <v>-4127.757311485473</v>
       </c>
       <c r="O66">
-        <v>-505.071622010143</v>
+        <v>-515.9696639356841</v>
       </c>
       <c r="P66">
-        <v>-3535.501354071001</v>
+        <v>-3611.787647549789</v>
       </c>
       <c r="Q66">
-        <v>-2513.501354071001</v>
+        <v>-2589.787647549789</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1317839672386388</v>
+        <v>0.1342406520168856</v>
       </c>
       <c r="T66">
-        <v>1.67598756335513</v>
+        <v>1.723872922308134</v>
       </c>
       <c r="U66">
         <v>0.2067366166625341</v>
       </c>
       <c r="V66">
-        <v>0.03448208692181391</v>
+        <v>0.03395159327686292</v>
       </c>
       <c r="W66">
-        <v>0.1996079066768549</v>
+        <v>0.199717579138173</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2758566953745112</v>
+        <v>0.2716127462149034</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1768006546457224</v>
+        <v>0.1784100208123477</v>
       </c>
       <c r="C67">
-        <v>-15860.70244959627</v>
+        <v>-16411.06065285281</v>
       </c>
       <c r="D67">
-        <v>10599.89929162731</v>
+        <v>10471.25803823575</v>
       </c>
       <c r="E67">
-        <v>13145.80675472577</v>
+        <v>13567.52370459075</v>
       </c>
       <c r="F67">
-        <v>27411.60174122358</v>
+        <v>27833.31869108856</v>
       </c>
       <c r="G67">
         <v>951</v>
@@ -6769,37 +6769,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M67">
-        <v>5666.981801281392</v>
+        <v>5754.166136685721</v>
       </c>
       <c r="N67">
-        <v>-4127.757311485473</v>
+        <v>-4214.941646889802</v>
       </c>
       <c r="O67">
-        <v>-515.9696639356841</v>
+        <v>-526.8677058612252</v>
       </c>
       <c r="P67">
-        <v>-3611.787647549789</v>
+        <v>-3688.073941028576</v>
       </c>
       <c r="Q67">
-        <v>-2589.787647549789</v>
+        <v>-2666.073941028576</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1342406520168856</v>
+        <v>0.1368418476644411</v>
       </c>
       <c r="T67">
-        <v>1.723872922308134</v>
+        <v>1.774575067081902</v>
       </c>
       <c r="U67">
         <v>0.2067366166625341</v>
       </c>
       <c r="V67">
-        <v>0.03395159327686292</v>
+        <v>0.03343717519691045</v>
       </c>
       <c r="W67">
-        <v>0.199717579138173</v>
+        <v>0.1998239281915724</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2716127462149034</v>
+        <v>0.2674974015752837</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1784100208123477</v>
+        <v>0.1800193869789731</v>
       </c>
       <c r="C68">
-        <v>-16411.06065285281</v>
+        <v>-16958.33389371307</v>
       </c>
       <c r="D68">
-        <v>10471.25803823575</v>
+        <v>10345.70174724047</v>
       </c>
       <c r="E68">
-        <v>13567.52370459075</v>
+        <v>13989.24065445572</v>
       </c>
       <c r="F68">
-        <v>27833.31869108856</v>
+        <v>28255.03564095354</v>
       </c>
       <c r="G68">
         <v>951</v>
@@ -6851,37 +6851,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M68">
-        <v>5754.166136685721</v>
+        <v>5841.35047209005</v>
       </c>
       <c r="N68">
-        <v>-4214.941646889802</v>
+        <v>-4302.125982294132</v>
       </c>
       <c r="O68">
-        <v>-526.8677058612252</v>
+        <v>-537.7657477867665</v>
       </c>
       <c r="P68">
-        <v>-3688.073941028576</v>
+        <v>-3764.360234507365</v>
       </c>
       <c r="Q68">
-        <v>-2666.073941028576</v>
+        <v>-2742.360234507365</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1368418476644411</v>
+        <v>0.1396006915330605</v>
       </c>
       <c r="T68">
-        <v>1.774575067081902</v>
+        <v>1.828350069114688</v>
       </c>
       <c r="U68">
         <v>0.2067366166625341</v>
       </c>
       <c r="V68">
-        <v>0.03343717519691045</v>
+        <v>0.03293811288053865</v>
       </c>
       <c r="W68">
-        <v>0.1998239281915724</v>
+        <v>0.1999271026463629</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2674974015752837</v>
+        <v>0.2635049030443092</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1800193869789731</v>
+        <v>0.1816287531455985</v>
       </c>
       <c r="C69">
-        <v>-16958.33389371307</v>
+        <v>-17502.63182865237</v>
       </c>
       <c r="D69">
-        <v>10345.70174724047</v>
+        <v>10223.12076216614</v>
       </c>
       <c r="E69">
-        <v>13989.24065445572</v>
+        <v>14410.9576043207</v>
       </c>
       <c r="F69">
-        <v>28255.03564095354</v>
+        <v>28676.75259081852</v>
       </c>
       <c r="G69">
         <v>951</v>
@@ -6933,37 +6933,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M69">
-        <v>5841.35047209005</v>
+        <v>5928.534807494379</v>
       </c>
       <c r="N69">
-        <v>-4302.125982294132</v>
+        <v>-4389.31031769846</v>
       </c>
       <c r="O69">
-        <v>-537.7657477867665</v>
+        <v>-548.6637897123076</v>
       </c>
       <c r="P69">
-        <v>-3764.360234507365</v>
+        <v>-3840.646527986153</v>
       </c>
       <c r="Q69">
-        <v>-2742.360234507365</v>
+        <v>-2818.646527986153</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1396006915330605</v>
+        <v>0.1425319631434687</v>
       </c>
       <c r="T69">
-        <v>1.828350069114688</v>
+        <v>1.885486008774522</v>
       </c>
       <c r="U69">
         <v>0.2067366166625341</v>
       </c>
       <c r="V69">
-        <v>0.03293811288053865</v>
+        <v>0.03245372886758956</v>
       </c>
       <c r="W69">
-        <v>0.1999271026463629</v>
+        <v>0.2000272425583654</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2635049030443092</v>
+        <v>0.2596298309407163</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1816287531455985</v>
+        <v>0.1832381193122238</v>
       </c>
       <c r="C70">
-        <v>-17502.63182865237</v>
+        <v>-18044.05897794593</v>
       </c>
       <c r="D70">
-        <v>10223.12076216614</v>
+        <v>10103.41056273756</v>
       </c>
       <c r="E70">
-        <v>14410.9576043207</v>
+        <v>14832.67455418568</v>
       </c>
       <c r="F70">
-        <v>28676.75259081852</v>
+        <v>29098.46954068349</v>
       </c>
       <c r="G70">
         <v>951</v>
@@ -7015,37 +7015,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M70">
-        <v>5928.534807494379</v>
+        <v>6015.719142898708</v>
       </c>
       <c r="N70">
-        <v>-4389.31031769846</v>
+        <v>-4476.494653102789</v>
       </c>
       <c r="O70">
-        <v>-548.6637897123076</v>
+        <v>-559.5618316378486</v>
       </c>
       <c r="P70">
-        <v>-3840.646527986153</v>
+        <v>-3916.93282146494</v>
       </c>
       <c r="Q70">
-        <v>-2818.646527986153</v>
+        <v>-2894.93282146494</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1425319631434687</v>
+        <v>0.1456523490513225</v>
       </c>
       <c r="T70">
-        <v>1.885486008774522</v>
+        <v>1.946308138089829</v>
       </c>
       <c r="U70">
         <v>0.2067366166625341</v>
       </c>
       <c r="V70">
-        <v>0.03245372886758956</v>
+        <v>0.03198338497095782</v>
       </c>
       <c r="W70">
-        <v>0.2000272425583654</v>
+        <v>0.2001244798642229</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2596298309407163</v>
+        <v>0.2558670797676627</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1832381193122238</v>
+        <v>0.1848474854788492</v>
       </c>
       <c r="C71">
-        <v>-18044.05897794593</v>
+        <v>-18582.71502290637</v>
       </c>
       <c r="D71">
-        <v>10103.41056273756</v>
+        <v>9986.471467642106</v>
       </c>
       <c r="E71">
-        <v>14832.67455418568</v>
+        <v>15254.39150405066</v>
       </c>
       <c r="F71">
-        <v>29098.46954068349</v>
+        <v>29520.18649054847</v>
       </c>
       <c r="G71">
         <v>951</v>
@@ -7097,37 +7097,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M71">
-        <v>6015.719142898708</v>
+        <v>6102.903478303037</v>
       </c>
       <c r="N71">
-        <v>-4476.494653102789</v>
+        <v>-4563.678988507119</v>
       </c>
       <c r="O71">
-        <v>-559.5618316378486</v>
+        <v>-570.4598735633899</v>
       </c>
       <c r="P71">
-        <v>-3916.93282146494</v>
+        <v>-3993.219114943729</v>
       </c>
       <c r="Q71">
-        <v>-2894.93282146494</v>
+        <v>-2971.219114943729</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1456523490513225</v>
+        <v>0.1489807606863666</v>
       </c>
       <c r="T71">
-        <v>1.946308138089829</v>
+        <v>2.011185076026157</v>
       </c>
       <c r="U71">
         <v>0.2067366166625341</v>
       </c>
       <c r="V71">
-        <v>0.03198338497095782</v>
+        <v>0.03152647947137271</v>
       </c>
       <c r="W71">
-        <v>0.2001244798642229</v>
+        <v>0.2002189389613417</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2558670797676627</v>
+        <v>0.2522118357709816</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1848474854788492</v>
+        <v>0.1864568516454745</v>
       </c>
       <c r="C72">
-        <v>-18582.71502290637</v>
+        <v>-19118.69508271569</v>
       </c>
       <c r="D72">
-        <v>9986.471467642106</v>
+        <v>9872.208357697758</v>
       </c>
       <c r="E72">
-        <v>15254.39150405066</v>
+        <v>15676.10845391564</v>
       </c>
       <c r="F72">
-        <v>29520.18649054847</v>
+        <v>29941.90344041345</v>
       </c>
       <c r="G72">
         <v>951</v>
@@ -7179,37 +7179,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M72">
-        <v>6102.903478303037</v>
+        <v>6190.087813707366</v>
       </c>
       <c r="N72">
-        <v>-4563.678988507119</v>
+        <v>-4650.863323911448</v>
       </c>
       <c r="O72">
-        <v>-570.4598735633899</v>
+        <v>-581.357915488931</v>
       </c>
       <c r="P72">
-        <v>-3993.219114943729</v>
+        <v>-4069.505408422517</v>
       </c>
       <c r="Q72">
-        <v>-2971.219114943729</v>
+        <v>-3047.505408422517</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1489807606863666</v>
+        <v>0.1525387179514137</v>
       </c>
       <c r="T72">
-        <v>2.011185076026157</v>
+        <v>2.0805362855443</v>
       </c>
       <c r="U72">
         <v>0.2067366166625341</v>
       </c>
       <c r="V72">
-        <v>0.03152647947137271</v>
+        <v>0.0310824445492407</v>
       </c>
       <c r="W72">
-        <v>0.2002189389613417</v>
+        <v>0.2003107372388233</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2522118357709816</v>
+        <v>0.2486595563939256</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1864568516454745</v>
+        <v>0.1880662178120998</v>
       </c>
       <c r="C73">
-        <v>-19118.69508271569</v>
+        <v>-19652.08997246755</v>
       </c>
       <c r="D73">
-        <v>9872.208357697758</v>
+        <v>9760.530417810874</v>
       </c>
       <c r="E73">
-        <v>15676.10845391563</v>
+        <v>16097.82540378061</v>
       </c>
       <c r="F73">
-        <v>29941.90344041345</v>
+        <v>30363.62039027843</v>
       </c>
       <c r="G73">
         <v>951</v>
@@ -7261,37 +7261,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M73">
-        <v>6190.087813707366</v>
+        <v>6277.272149111694</v>
       </c>
       <c r="N73">
-        <v>-4650.863323911448</v>
+        <v>-4738.047659315776</v>
       </c>
       <c r="O73">
-        <v>-581.357915488931</v>
+        <v>-592.2559574144721</v>
       </c>
       <c r="P73">
-        <v>-4069.505408422517</v>
+        <v>-4145.791701901304</v>
       </c>
       <c r="Q73">
-        <v>-3047.505408422517</v>
+        <v>-3123.791701901304</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1525387179514137</v>
+        <v>0.156350815021107</v>
       </c>
       <c r="T73">
-        <v>2.080536285544299</v>
+        <v>2.154841152885167</v>
       </c>
       <c r="U73">
         <v>0.2067366166625341</v>
       </c>
       <c r="V73">
-        <v>0.0310824445492407</v>
+        <v>0.03065074393050125</v>
       </c>
       <c r="W73">
-        <v>0.2003107372388233</v>
+        <v>0.2003999855641526</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2486595563939256</v>
+        <v>0.2452059514440099</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1880662178120998</v>
+        <v>0.1896755839787252</v>
       </c>
       <c r="C74">
-        <v>-19652.08997246755</v>
+        <v>-20182.986443891</v>
       </c>
       <c r="D74">
-        <v>9760.530417810874</v>
+        <v>9651.350896252403</v>
       </c>
       <c r="E74">
-        <v>16097.82540378061</v>
+        <v>16519.54235364559</v>
       </c>
       <c r="F74">
-        <v>30363.62039027843</v>
+        <v>30785.3373401434</v>
       </c>
       <c r="G74">
         <v>951</v>
@@ -7343,37 +7343,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M74">
-        <v>6277.272149111694</v>
+        <v>6364.456484516024</v>
       </c>
       <c r="N74">
-        <v>-4738.047659315776</v>
+        <v>-4825.231994720105</v>
       </c>
       <c r="O74">
-        <v>-592.2559574144721</v>
+        <v>-603.1539993400131</v>
       </c>
       <c r="P74">
-        <v>-4145.791701901304</v>
+        <v>-4222.077995380092</v>
       </c>
       <c r="Q74">
-        <v>-3123.791701901304</v>
+        <v>-3200.077995380092</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.156350815021107</v>
+        <v>0.1604452896515184</v>
       </c>
       <c r="T74">
-        <v>2.154841152885167</v>
+        <v>2.234650084473506</v>
       </c>
       <c r="U74">
         <v>0.2067366166625341</v>
       </c>
       <c r="V74">
-        <v>0.03065074393050125</v>
+        <v>0.03023087072597384</v>
       </c>
       <c r="W74">
-        <v>0.2003999855641526</v>
+        <v>0.2004867887298838</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2452059514440099</v>
+        <v>0.2418469658077907</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1896755839787252</v>
+        <v>0.1912849501453505</v>
       </c>
       <c r="C75">
-        <v>-20182.986443891</v>
+        <v>-20711.46741009677</v>
       </c>
       <c r="D75">
-        <v>9651.350896252403</v>
+        <v>9544.586879911611</v>
       </c>
       <c r="E75">
-        <v>16519.54235364559</v>
+        <v>16941.25930351057</v>
       </c>
       <c r="F75">
-        <v>30785.3373401434</v>
+        <v>31207.05429000838</v>
       </c>
       <c r="G75">
         <v>951</v>
@@ -7425,37 +7425,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M75">
-        <v>6364.456484516024</v>
+        <v>6451.640819920353</v>
       </c>
       <c r="N75">
-        <v>-4825.231994720105</v>
+        <v>-4912.416330124435</v>
       </c>
       <c r="O75">
-        <v>-603.1539993400131</v>
+        <v>-614.0520412655544</v>
       </c>
       <c r="P75">
-        <v>-4222.077995380092</v>
+        <v>-4298.364288858881</v>
       </c>
       <c r="Q75">
-        <v>-3200.077995380092</v>
+        <v>-3276.364288858881</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1604452896515184</v>
+        <v>0.1648547238688845</v>
       </c>
       <c r="T75">
-        <v>2.234650084473506</v>
+        <v>2.320598164645564</v>
       </c>
       <c r="U75">
         <v>0.2067366166625341</v>
       </c>
       <c r="V75">
-        <v>0.03023087072597384</v>
+        <v>0.02982234544589311</v>
       </c>
       <c r="W75">
-        <v>0.2004867887298838</v>
+        <v>0.2005712458641088</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2418469658077907</v>
+        <v>0.2385787635671448</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1912849501453505</v>
+        <v>0.1928943163119758</v>
       </c>
       <c r="C76">
-        <v>-20711.46741009677</v>
+        <v>-21237.6121555699</v>
       </c>
       <c r="D76">
-        <v>9544.586879911611</v>
+        <v>9440.159084303468</v>
       </c>
       <c r="E76">
-        <v>16941.25930351057</v>
+        <v>17362.97625337555</v>
       </c>
       <c r="F76">
-        <v>31207.05429000838</v>
+        <v>31628.77123987336</v>
       </c>
       <c r="G76">
         <v>951</v>
@@ -7507,37 +7507,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M76">
-        <v>6451.640819920353</v>
+        <v>6538.825155324683</v>
       </c>
       <c r="N76">
-        <v>-4912.416330124435</v>
+        <v>-4999.600665528764</v>
       </c>
       <c r="O76">
-        <v>-614.0520412655544</v>
+        <v>-624.9500831910955</v>
       </c>
       <c r="P76">
-        <v>-4298.364288858881</v>
+        <v>-4374.650582337668</v>
       </c>
       <c r="Q76">
-        <v>-3276.364288858881</v>
+        <v>-3352.650582337668</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1648547238688845</v>
+        <v>0.1696169128236399</v>
       </c>
       <c r="T76">
-        <v>2.320598164645564</v>
+        <v>2.413422091231387</v>
       </c>
       <c r="U76">
         <v>0.2067366166625341</v>
       </c>
       <c r="V76">
-        <v>0.02982234544589311</v>
+        <v>0.0294247141732812</v>
       </c>
       <c r="W76">
-        <v>0.2005712458641088</v>
+        <v>0.2006534508080878</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2385787635671448</v>
+        <v>0.2353977133862496</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1928943163119758</v>
+        <v>0.1945036824786012</v>
       </c>
       <c r="C77">
-        <v>-21237.6121555699</v>
+        <v>-21761.49653252616</v>
       </c>
       <c r="D77">
-        <v>9440.159084303468</v>
+        <v>9337.99165721218</v>
       </c>
       <c r="E77">
-        <v>17362.97625337555</v>
+        <v>17784.69320324053</v>
       </c>
       <c r="F77">
-        <v>31628.77123987336</v>
+        <v>32050.48818973834</v>
       </c>
       <c r="G77">
         <v>951</v>
@@ -7589,37 +7589,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M77">
-        <v>6538.825155324683</v>
+        <v>6626.009490729012</v>
       </c>
       <c r="N77">
-        <v>-4999.600665528764</v>
+        <v>-5086.785000933094</v>
       </c>
       <c r="O77">
-        <v>-624.9500831910955</v>
+        <v>-635.8481251166368</v>
       </c>
       <c r="P77">
-        <v>-4374.650582337668</v>
+        <v>-4450.936875816457</v>
       </c>
       <c r="Q77">
-        <v>-3352.650582337668</v>
+        <v>-3428.936875816457</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1696169128236399</v>
+        <v>0.1747759508579582</v>
       </c>
       <c r="T77">
-        <v>2.413422091231387</v>
+        <v>2.513981345032696</v>
       </c>
       <c r="U77">
         <v>0.2067366166625341</v>
       </c>
       <c r="V77">
-        <v>0.0294247141732812</v>
+        <v>0.02903754688152749</v>
       </c>
       <c r="W77">
-        <v>0.2006534508080878</v>
+        <v>0.2007334924640674</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2353977133862496</v>
+        <v>0.2323003750522199</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1945036824786012</v>
+        <v>0.1961130486452265</v>
       </c>
       <c r="C78">
-        <v>-21761.49653252616</v>
+        <v>-22283.19314465464</v>
       </c>
       <c r="D78">
-        <v>9337.99165721218</v>
+        <v>9238.011994948678</v>
       </c>
       <c r="E78">
-        <v>17784.69320324053</v>
+        <v>18206.41015310551</v>
       </c>
       <c r="F78">
-        <v>32050.48818973834</v>
+        <v>32472.20513960332</v>
       </c>
       <c r="G78">
         <v>951</v>
@@ -7671,37 +7671,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M78">
-        <v>6626.009490729012</v>
+        <v>6713.193826133341</v>
       </c>
       <c r="N78">
-        <v>-5086.785000933094</v>
+        <v>-5173.969336337423</v>
       </c>
       <c r="O78">
-        <v>-635.8481251166368</v>
+        <v>-646.7461670421778</v>
       </c>
       <c r="P78">
-        <v>-4450.936875816457</v>
+        <v>-4527.223169295245</v>
       </c>
       <c r="Q78">
-        <v>-3428.936875816457</v>
+        <v>-3505.223169295245</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1747759508579582</v>
+        <v>0.1803836008952608</v>
       </c>
       <c r="T78">
-        <v>2.513981345032696</v>
+        <v>2.623284881773247</v>
       </c>
       <c r="U78">
         <v>0.2067366166625341</v>
       </c>
       <c r="V78">
-        <v>0.02903754688152749</v>
+        <v>0.0286604358830661</v>
       </c>
       <c r="W78">
-        <v>0.2007334924640674</v>
+        <v>0.2008114551159955</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2323003750522199</v>
+        <v>0.2292834870645287</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1961130486452265</v>
+        <v>0.1977224148118518</v>
       </c>
       <c r="C79">
-        <v>-22283.19314465464</v>
+        <v>-22802.77151918142</v>
       </c>
       <c r="D79">
-        <v>9238.011994948678</v>
+        <v>9140.150570286874</v>
       </c>
       <c r="E79">
-        <v>18206.41015310551</v>
+        <v>18628.12710297048</v>
       </c>
       <c r="F79">
-        <v>32472.20513960332</v>
+        <v>32893.92208946829</v>
       </c>
       <c r="G79">
         <v>951</v>
@@ -7753,37 +7753,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M79">
-        <v>6713.193826133341</v>
+        <v>6800.378161537669</v>
       </c>
       <c r="N79">
-        <v>-5173.969336337423</v>
+        <v>-5261.153671741751</v>
       </c>
       <c r="O79">
-        <v>-646.7461670421778</v>
+        <v>-657.6442089677189</v>
       </c>
       <c r="P79">
-        <v>-4527.223169295245</v>
+        <v>-4603.509462774033</v>
       </c>
       <c r="Q79">
-        <v>-3505.223169295245</v>
+        <v>-3581.509462774033</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1803836008952608</v>
+        <v>0.1865010372995908</v>
       </c>
       <c r="T79">
-        <v>2.623284881773247</v>
+        <v>2.742525103672031</v>
       </c>
       <c r="U79">
         <v>0.2067366166625341</v>
       </c>
       <c r="V79">
-        <v>0.0286604358830661</v>
+        <v>0.02829299439738577</v>
       </c>
       <c r="W79">
-        <v>0.2008114551159955</v>
+        <v>0.2008874187255665</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2292834870645287</v>
+        <v>0.2263439551790861</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1977224148118518</v>
+        <v>0.1993317809784772</v>
       </c>
       <c r="C80">
-        <v>-22802.77151918142</v>
+        <v>-23320.29826811168</v>
       </c>
       <c r="D80">
-        <v>9140.150570286874</v>
+        <v>9044.340771221601</v>
       </c>
       <c r="E80">
-        <v>18628.12710297048</v>
+        <v>19049.84405283546</v>
       </c>
       <c r="F80">
-        <v>32893.92208946829</v>
+        <v>33315.63903933328</v>
       </c>
       <c r="G80">
         <v>951</v>
@@ -7835,37 +7835,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M80">
-        <v>6800.378161537669</v>
+        <v>6887.562496942</v>
       </c>
       <c r="N80">
-        <v>-5261.153671741751</v>
+        <v>-5348.338007146082</v>
       </c>
       <c r="O80">
-        <v>-657.6442089677189</v>
+        <v>-668.5422508932602</v>
       </c>
       <c r="P80">
-        <v>-4603.509462774033</v>
+        <v>-4679.795756252821</v>
       </c>
       <c r="Q80">
-        <v>-3581.509462774033</v>
+        <v>-3657.795756252821</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1865010372995908</v>
+        <v>0.1932010866948094</v>
       </c>
       <c r="T80">
-        <v>2.742525103672031</v>
+        <v>2.873121537180223</v>
       </c>
       <c r="U80">
         <v>0.2067366166625341</v>
       </c>
       <c r="V80">
-        <v>0.02829299439738577</v>
+        <v>0.0279348552277986</v>
       </c>
       <c r="W80">
-        <v>0.2008874187255665</v>
+        <v>0.2009614592057813</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2263439551790861</v>
+        <v>0.2234788418223888</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1993317809784772</v>
+        <v>0.2009411471451025</v>
       </c>
       <c r="C81">
-        <v>-23320.29826811168</v>
+        <v>-23835.83723943573</v>
       </c>
       <c r="D81">
-        <v>9044.340771221601</v>
+        <v>8950.518749762525</v>
       </c>
       <c r="E81">
-        <v>19049.84405283546</v>
+        <v>19471.56100270044</v>
       </c>
       <c r="F81">
-        <v>33315.63903933328</v>
+        <v>33737.35598919825</v>
       </c>
       <c r="G81">
         <v>951</v>
@@ -7917,37 +7917,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M81">
-        <v>6887.562496942</v>
+        <v>6974.746832346327</v>
       </c>
       <c r="N81">
-        <v>-5348.338007146082</v>
+        <v>-5435.522342550408</v>
       </c>
       <c r="O81">
-        <v>-668.5422508932602</v>
+        <v>-679.440292818801</v>
       </c>
       <c r="P81">
-        <v>-4679.795756252821</v>
+        <v>-4756.082049731607</v>
       </c>
       <c r="Q81">
-        <v>-3657.795756252821</v>
+        <v>-3734.082049731607</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1932010866948094</v>
+        <v>0.2005711410295499</v>
       </c>
       <c r="T81">
-        <v>2.873121537180223</v>
+        <v>3.016777614039234</v>
       </c>
       <c r="U81">
         <v>0.2067366166625341</v>
       </c>
       <c r="V81">
-        <v>0.0279348552277986</v>
+        <v>0.02758566953745113</v>
       </c>
       <c r="W81">
-        <v>0.2009614592057813</v>
+        <v>0.2010336486739907</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2234788418223888</v>
+        <v>0.2206853562996091</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2009411471451025</v>
+        <v>0.2025505133117279</v>
       </c>
       <c r="C82">
-        <v>-23835.83723943573</v>
+        <v>-24349.44965902059</v>
       </c>
       <c r="D82">
-        <v>8950.518749762525</v>
+        <v>8858.623280042644</v>
       </c>
       <c r="E82">
-        <v>19471.56100270044</v>
+        <v>19893.27795256542</v>
       </c>
       <c r="F82">
-        <v>33737.35598919825</v>
+        <v>34159.07293906323</v>
       </c>
       <c r="G82">
         <v>951</v>
@@ -7999,37 +7999,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M82">
-        <v>6974.746832346327</v>
+        <v>7061.931167750658</v>
       </c>
       <c r="N82">
-        <v>-5435.522342550408</v>
+        <v>-5522.706677954739</v>
       </c>
       <c r="O82">
-        <v>-679.440292818801</v>
+        <v>-690.3383347443423</v>
       </c>
       <c r="P82">
-        <v>-4756.082049731607</v>
+        <v>-4832.368343210396</v>
       </c>
       <c r="Q82">
-        <v>-3734.082049731607</v>
+        <v>-3810.368343210396</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2005711410295499</v>
+        <v>0.2087169905574209</v>
       </c>
       <c r="T82">
-        <v>3.016777614039234</v>
+        <v>3.175555383199194</v>
       </c>
       <c r="U82">
         <v>0.2067366166625341</v>
       </c>
       <c r="V82">
-        <v>0.02758566953745113</v>
+        <v>0.02724510571600111</v>
       </c>
       <c r="W82">
-        <v>0.2010336486739907</v>
+        <v>0.2011040556861949</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2206853562996091</v>
+        <v>0.2179608457280089</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2025505133117279</v>
+        <v>0.2041598794783532</v>
       </c>
       <c r="C83">
-        <v>-24349.44965902059</v>
+        <v>-24861.19426384933</v>
       </c>
       <c r="D83">
-        <v>8858.623280042644</v>
+        <v>8768.59562507888</v>
       </c>
       <c r="E83">
-        <v>19893.27795256542</v>
+        <v>20314.9949024304</v>
       </c>
       <c r="F83">
-        <v>34159.07293906323</v>
+        <v>34580.78988892822</v>
       </c>
       <c r="G83">
         <v>951</v>
@@ -8081,37 +8081,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M83">
-        <v>7061.931167750658</v>
+        <v>7149.115503154987</v>
       </c>
       <c r="N83">
-        <v>-5522.706677954739</v>
+        <v>-5609.891013359069</v>
       </c>
       <c r="O83">
-        <v>-690.3383347443423</v>
+        <v>-701.2363766698836</v>
       </c>
       <c r="P83">
-        <v>-4832.368343210396</v>
+        <v>-4908.654636689185</v>
       </c>
       <c r="Q83">
-        <v>-3810.368343210396</v>
+        <v>-3886.654636689185</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2087169905574209</v>
+        <v>0.2177679344772777</v>
       </c>
       <c r="T83">
-        <v>3.175555383199194</v>
+        <v>3.351975126710261</v>
       </c>
       <c r="U83">
         <v>0.2067366166625341</v>
       </c>
       <c r="V83">
-        <v>0.02724510571600111</v>
+        <v>0.02691284832922061</v>
       </c>
       <c r="W83">
-        <v>0.2011040556861949</v>
+        <v>0.2011727454541991</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2179608457280089</v>
+        <v>0.2153027866337648</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2041598794783532</v>
+        <v>0.2057692456449786</v>
       </c>
       <c r="C84">
-        <v>-24861.19426384933</v>
+        <v>-25371.12742721786</v>
       </c>
       <c r="D84">
-        <v>8768.59562507888</v>
+        <v>8680.379411575324</v>
       </c>
       <c r="E84">
-        <v>20314.9949024304</v>
+        <v>20736.71185229538</v>
       </c>
       <c r="F84">
-        <v>34580.78988892822</v>
+        <v>35002.50683879319</v>
       </c>
       <c r="G84">
         <v>951</v>
@@ -8163,37 +8163,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M84">
-        <v>7149.115503154987</v>
+        <v>7236.299838559316</v>
       </c>
       <c r="N84">
-        <v>-5609.891013359069</v>
+        <v>-5697.075348763397</v>
       </c>
       <c r="O84">
-        <v>-701.2363766698836</v>
+        <v>-712.1344185954247</v>
       </c>
       <c r="P84">
-        <v>-4908.654636689185</v>
+        <v>-4984.940930167973</v>
       </c>
       <c r="Q84">
-        <v>-3886.654636689185</v>
+        <v>-3962.940930167973</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2177679344772777</v>
+        <v>0.2278836953288822</v>
       </c>
       <c r="T84">
-        <v>3.351975126710261</v>
+        <v>3.549150134163805</v>
       </c>
       <c r="U84">
         <v>0.2067366166625341</v>
       </c>
       <c r="V84">
-        <v>0.02691284832922061</v>
+        <v>0.0265885971445312</v>
       </c>
       <c r="W84">
-        <v>0.2011727454541991</v>
+        <v>0.2012397800470706</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2153027866337648</v>
+        <v>0.2127087771562496</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2057692456449786</v>
+        <v>0.2073786118116039</v>
       </c>
       <c r="C85">
-        <v>-25371.12742721786</v>
+        <v>-25879.30327644973</v>
       </c>
       <c r="D85">
-        <v>8680.379411575324</v>
+        <v>8593.92051220844</v>
       </c>
       <c r="E85">
-        <v>20736.71185229538</v>
+        <v>21158.42880216036</v>
       </c>
       <c r="F85">
-        <v>35002.50683879319</v>
+        <v>35424.22378865817</v>
       </c>
       <c r="G85">
         <v>951</v>
@@ -8245,37 +8245,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M85">
-        <v>7236.299838559316</v>
+        <v>7323.484173963646</v>
       </c>
       <c r="N85">
-        <v>-5697.075348763397</v>
+        <v>-5784.259684167728</v>
       </c>
       <c r="O85">
-        <v>-712.1344185954247</v>
+        <v>-723.032460520966</v>
       </c>
       <c r="P85">
-        <v>-4984.940930167973</v>
+        <v>-5061.227223646762</v>
       </c>
       <c r="Q85">
-        <v>-3962.940930167973</v>
+        <v>-4039.227223646762</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2278836953288822</v>
+        <v>0.2392639262869374</v>
       </c>
       <c r="T85">
-        <v>3.549150134163805</v>
+        <v>3.770972017549044</v>
       </c>
       <c r="U85">
         <v>0.2067366166625341</v>
       </c>
       <c r="V85">
-        <v>0.0265885971445312</v>
+        <v>0.02627206622614392</v>
       </c>
       <c r="W85">
-        <v>0.2012397800470706</v>
+        <v>0.201305218578207</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2127087771562496</v>
+        <v>0.2101765298091514</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2073786118116039</v>
+        <v>0.2089879779782292</v>
       </c>
       <c r="C86">
-        <v>-25879.30327644973</v>
+        <v>-26385.7738036454</v>
       </c>
       <c r="D86">
-        <v>8593.92051220844</v>
+        <v>8509.166934877747</v>
       </c>
       <c r="E86">
-        <v>21158.42880216035</v>
+        <v>21580.14575202533</v>
       </c>
       <c r="F86">
-        <v>35424.22378865816</v>
+        <v>35845.94073852315</v>
       </c>
       <c r="G86">
         <v>951</v>
@@ -8327,37 +8327,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M86">
-        <v>7323.484173963644</v>
+        <v>7410.668509367974</v>
       </c>
       <c r="N86">
-        <v>-5784.259684167726</v>
+        <v>-5871.444019572056</v>
       </c>
       <c r="O86">
-        <v>-723.0324605209657</v>
+        <v>-733.930502446507</v>
       </c>
       <c r="P86">
-        <v>-5061.22722364676</v>
+        <v>-5137.51351712555</v>
       </c>
       <c r="Q86">
-        <v>-4039.22722364676</v>
+        <v>-4115.51351712555</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2392639262869373</v>
+        <v>0.2521615213727331</v>
       </c>
       <c r="T86">
-        <v>3.770972017549042</v>
+        <v>4.022370152052312</v>
       </c>
       <c r="U86">
         <v>0.2067366166625341</v>
       </c>
       <c r="V86">
-        <v>0.02627206622614393</v>
+        <v>0.02596298309407164</v>
       </c>
       <c r="W86">
-        <v>0.201305218578207</v>
+        <v>0.2013691173791992</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2101765298091514</v>
+        <v>0.2077038647525731</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2089879779782292</v>
+        <v>0.2105973441448546</v>
       </c>
       <c r="C87">
-        <v>-26385.7738036454</v>
+        <v>-26890.58896994232</v>
       </c>
       <c r="D87">
-        <v>8509.166934877747</v>
+        <v>8426.068718445804</v>
       </c>
       <c r="E87">
-        <v>21580.14575202533</v>
+        <v>22001.86270189031</v>
       </c>
       <c r="F87">
-        <v>35845.94073852315</v>
+        <v>36267.65768838812</v>
       </c>
       <c r="G87">
         <v>951</v>
@@ -8409,37 +8409,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M87">
-        <v>7410.668509367974</v>
+        <v>7497.852844772302</v>
       </c>
       <c r="N87">
-        <v>-5871.444019572056</v>
+        <v>-5958.628354976383</v>
       </c>
       <c r="O87">
-        <v>-733.930502446507</v>
+        <v>-744.8285443720479</v>
       </c>
       <c r="P87">
-        <v>-5137.51351712555</v>
+        <v>-5213.799810604335</v>
       </c>
       <c r="Q87">
-        <v>-4115.51351712555</v>
+        <v>-4191.799810604335</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2521615213727331</v>
+        <v>0.266901630042214</v>
       </c>
       <c r="T87">
-        <v>4.022370152052312</v>
+        <v>4.309682305770334</v>
       </c>
       <c r="U87">
         <v>0.2067366166625341</v>
       </c>
       <c r="V87">
-        <v>0.02596298309407164</v>
+        <v>0.025661087941815</v>
       </c>
       <c r="W87">
-        <v>0.2013691173791992</v>
+        <v>0.2014315301615635</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2077038647525731</v>
+        <v>0.2052887035345201</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2105973441448546</v>
+        <v>0.2122067103114799</v>
       </c>
       <c r="C88">
-        <v>-26890.58896994232</v>
+        <v>-27393.79680372504</v>
       </c>
       <c r="D88">
-        <v>8426.068718445804</v>
+        <v>8344.57783452806</v>
       </c>
       <c r="E88">
-        <v>22001.86270189031</v>
+        <v>22423.57965175529</v>
       </c>
       <c r="F88">
-        <v>36267.65768838812</v>
+        <v>36689.3746382531</v>
       </c>
       <c r="G88">
         <v>951</v>
@@ -8491,37 +8491,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M88">
-        <v>7497.852844772302</v>
+        <v>7585.037180176632</v>
       </c>
       <c r="N88">
-        <v>-5958.628354976383</v>
+        <v>-6045.812690380713</v>
       </c>
       <c r="O88">
-        <v>-744.8285443720479</v>
+        <v>-755.7265862975892</v>
       </c>
       <c r="P88">
-        <v>-5213.799810604335</v>
+        <v>-5290.086104083124</v>
       </c>
       <c r="Q88">
-        <v>-4191.799810604335</v>
+        <v>-4268.086104083124</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.266901630042214</v>
+        <v>0.2839094477377689</v>
       </c>
       <c r="T88">
-        <v>4.309682305770334</v>
+        <v>4.641196329291128</v>
       </c>
       <c r="U88">
         <v>0.2067366166625341</v>
       </c>
       <c r="V88">
-        <v>0.025661087941815</v>
+        <v>0.02536613290800103</v>
       </c>
       <c r="W88">
-        <v>0.2014315301615635</v>
+        <v>0.2014925081673218</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2052887035345201</v>
+        <v>0.2029290632640083</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2122067103114799</v>
+        <v>0.2138160764781053</v>
       </c>
       <c r="C89">
-        <v>-27393.79680372504</v>
+        <v>-27895.44349319093</v>
       </c>
       <c r="D89">
-        <v>8344.57783452806</v>
+        <v>8264.648094927146</v>
       </c>
       <c r="E89">
-        <v>22423.57965175529</v>
+        <v>22845.29660162026</v>
       </c>
       <c r="F89">
-        <v>36689.3746382531</v>
+        <v>37111.09158811808</v>
       </c>
       <c r="G89">
         <v>951</v>
@@ -8573,37 +8573,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M89">
-        <v>7585.037180176632</v>
+        <v>7672.221515580961</v>
       </c>
       <c r="N89">
-        <v>-6045.812690380713</v>
+        <v>-6132.997025785042</v>
       </c>
       <c r="O89">
-        <v>-755.7265862975892</v>
+        <v>-766.6246282231302</v>
       </c>
       <c r="P89">
-        <v>-5290.086104083124</v>
+        <v>-5366.372397561911</v>
       </c>
       <c r="Q89">
-        <v>-4268.086104083124</v>
+        <v>-4344.372397561911</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2839094477377689</v>
+        <v>0.3037519017159165</v>
       </c>
       <c r="T89">
-        <v>4.641196329291128</v>
+        <v>5.027962690065391</v>
       </c>
       <c r="U89">
         <v>0.2067366166625341</v>
       </c>
       <c r="V89">
-        <v>0.02536613290800103</v>
+        <v>0.02507788139768284</v>
       </c>
       <c r="W89">
-        <v>0.2014925081673218</v>
+        <v>0.2015521003093128</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2029290632640083</v>
+        <v>0.2006230511814627</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2138160764781053</v>
+        <v>0.2466765797878494</v>
       </c>
       <c r="C90">
-        <v>-27895.44349319093</v>
+        <v>-29669.13734531125</v>
       </c>
       <c r="D90">
-        <v>8264.648094927146</v>
+        <v>6912.671192671814</v>
       </c>
       <c r="E90">
-        <v>22845.29660162026</v>
+        <v>23267.01355148524</v>
       </c>
       <c r="F90">
-        <v>37111.09158811808</v>
+        <v>37532.80853798306</v>
       </c>
       <c r="G90">
         <v>951</v>
@@ -8655,45 +8655,45 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M90">
-        <v>7672.221515580961</v>
+        <v>9073.054149814698</v>
       </c>
       <c r="N90">
-        <v>-6132.997025785042</v>
+        <v>-7533.829660018779</v>
       </c>
       <c r="O90">
-        <v>-766.6246282231302</v>
+        <v>-941.7287075023473</v>
       </c>
       <c r="P90">
-        <v>-5366.372397561911</v>
+        <v>-6592.100952516432</v>
       </c>
       <c r="Q90">
-        <v>-4344.372397561911</v>
+        <v>-5570.100952516432</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3037519017159165</v>
+        <v>0.3281215031729889</v>
       </c>
       <c r="T90">
-        <v>5.027962690065391</v>
+        <v>5.502971581579072</v>
       </c>
       <c r="U90">
-        <v>0.2067366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V90">
-        <v>0.02507788139768284</v>
+        <v>0.02120598621451183</v>
       </c>
       <c r="W90">
-        <v>0.2015521003093128</v>
+        <v>0.2366103533020457</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.2006230511814627</v>
+        <v>0.1696478897160947</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2466765797878494</v>
+        <v>0.2486359459544747</v>
       </c>
       <c r="C91">
-        <v>-29669.13734531125</v>
+        <v>-30157.62970814453</v>
       </c>
       <c r="D91">
-        <v>6912.671192671814</v>
+        <v>6845.895779703506</v>
       </c>
       <c r="E91">
-        <v>23267.01355148524</v>
+        <v>23688.73050135022</v>
       </c>
       <c r="F91">
-        <v>37532.80853798306</v>
+        <v>37954.52548784803</v>
       </c>
       <c r="G91">
         <v>951</v>
@@ -8737,37 +8737,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M91">
-        <v>9073.054149814698</v>
+        <v>9174.998578464299</v>
       </c>
       <c r="N91">
-        <v>-7533.829660018779</v>
+        <v>-7635.774088668381</v>
       </c>
       <c r="O91">
-        <v>-941.7287075023473</v>
+        <v>-954.4717610835476</v>
       </c>
       <c r="P91">
-        <v>-6592.100952516432</v>
+        <v>-6681.302327584833</v>
       </c>
       <c r="Q91">
-        <v>-5570.100952516432</v>
+        <v>-5659.302327584833</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3281215031729889</v>
+        <v>0.3563536534902877</v>
       </c>
       <c r="T91">
-        <v>5.502971581579072</v>
+        <v>6.053268739736978</v>
       </c>
       <c r="U91">
         <v>0.2417366166625341</v>
       </c>
       <c r="V91">
-        <v>0.02120598621451183</v>
+        <v>0.0209703641454617</v>
       </c>
       <c r="W91">
-        <v>0.2366103533020457</v>
+        <v>0.2366673117838289</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1696478897160947</v>
+        <v>0.1677629131636936</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2486359459544747</v>
+        <v>0.2505953121211001</v>
       </c>
       <c r="C92">
-        <v>-30157.62970814453</v>
+        <v>-30644.84433191653</v>
       </c>
       <c r="D92">
-        <v>6845.895779703506</v>
+        <v>6780.398105796486</v>
       </c>
       <c r="E92">
-        <v>23688.73050135022</v>
+        <v>24110.4474512152</v>
       </c>
       <c r="F92">
-        <v>37954.52548784803</v>
+        <v>38376.24243771302</v>
       </c>
       <c r="G92">
         <v>951</v>
@@ -8819,37 +8819,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M92">
-        <v>9174.998578464299</v>
+        <v>9276.943007113905</v>
       </c>
       <c r="N92">
-        <v>-7635.774088668381</v>
+        <v>-7737.718517317986</v>
       </c>
       <c r="O92">
-        <v>-954.4717610835476</v>
+        <v>-967.2148146647482</v>
       </c>
       <c r="P92">
-        <v>-6681.302327584833</v>
+        <v>-6770.503702653237</v>
       </c>
       <c r="Q92">
-        <v>-5659.302327584833</v>
+        <v>-5748.503702653237</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3563536534902877</v>
+        <v>0.3908596149892087</v>
       </c>
       <c r="T92">
-        <v>6.053268739736978</v>
+        <v>6.725854155263312</v>
       </c>
       <c r="U92">
         <v>0.2417366166625341</v>
       </c>
       <c r="V92">
-        <v>0.0209703641454617</v>
+        <v>0.02073992058342366</v>
       </c>
       <c r="W92">
-        <v>0.2366673117838289</v>
+        <v>0.2367230184308476</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1677629131636936</v>
+        <v>0.1659193646673893</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2505953121211001</v>
+        <v>0.2525546782877254</v>
       </c>
       <c r="C93">
-        <v>-30644.84433191653</v>
+        <v>-31130.81754313806</v>
       </c>
       <c r="D93">
-        <v>6780.398105796486</v>
+        <v>6716.141844439927</v>
       </c>
       <c r="E93">
-        <v>24110.4474512152</v>
+        <v>24532.16440108018</v>
       </c>
       <c r="F93">
-        <v>38376.24243771302</v>
+        <v>38797.95938757799</v>
       </c>
       <c r="G93">
         <v>951</v>
@@ -8901,37 +8901,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M93">
-        <v>9276.943007113905</v>
+        <v>9378.887435763507</v>
       </c>
       <c r="N93">
-        <v>-7737.718517317986</v>
+        <v>-7839.662945967588</v>
       </c>
       <c r="O93">
-        <v>-967.2148146647482</v>
+        <v>-979.9578682459485</v>
       </c>
       <c r="P93">
-        <v>-6770.503702653237</v>
+        <v>-6859.705077721639</v>
       </c>
       <c r="Q93">
-        <v>-5748.503702653237</v>
+        <v>-5837.705077721639</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3908596149892087</v>
+        <v>0.4339920668628599</v>
       </c>
       <c r="T93">
-        <v>6.725854155263312</v>
+        <v>7.566585924671227</v>
       </c>
       <c r="U93">
         <v>0.2417366166625341</v>
       </c>
       <c r="V93">
-        <v>0.02073992058342366</v>
+        <v>0.02051448666403862</v>
       </c>
       <c r="W93">
-        <v>0.2367230184308476</v>
+        <v>0.2367775140638007</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1659193646673893</v>
+        <v>0.164115893312309</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2525546782877254</v>
+        <v>0.2545140444543508</v>
       </c>
       <c r="C94">
-        <v>-31130.81754313806</v>
+        <v>-31615.58430421559</v>
       </c>
       <c r="D94">
-        <v>6716.141844439927</v>
+        <v>6653.092033227383</v>
       </c>
       <c r="E94">
-        <v>24532.16440108018</v>
+        <v>24953.88135094516</v>
       </c>
       <c r="F94">
-        <v>38797.95938757799</v>
+        <v>39219.67633744297</v>
       </c>
       <c r="G94">
         <v>951</v>
@@ -8983,37 +8983,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M94">
-        <v>9378.887435763507</v>
+        <v>9480.83186441311</v>
       </c>
       <c r="N94">
-        <v>-7839.662945967588</v>
+        <v>-7941.607374617191</v>
       </c>
       <c r="O94">
-        <v>-979.9578682459485</v>
+        <v>-992.7009218271489</v>
       </c>
       <c r="P94">
-        <v>-6859.705077721639</v>
+        <v>-6948.906452790043</v>
       </c>
       <c r="Q94">
-        <v>-5837.705077721639</v>
+        <v>-5926.906452790043</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4339920668628599</v>
+        <v>0.4894480764146971</v>
       </c>
       <c r="T94">
-        <v>7.566585924671227</v>
+        <v>8.647526771052831</v>
       </c>
       <c r="U94">
         <v>0.2417366166625341</v>
       </c>
       <c r="V94">
-        <v>0.02051448666403862</v>
+        <v>0.02029390078593067</v>
       </c>
       <c r="W94">
-        <v>0.2367775140638007</v>
+        <v>0.2368308377476581</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.164115893312309</v>
+        <v>0.1623512062874455</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2545140444543508</v>
+        <v>0.2564734106209761</v>
       </c>
       <c r="C95">
-        <v>-31615.58430421559</v>
+        <v>-32099.17827688532</v>
       </c>
       <c r="D95">
-        <v>6653.092033227383</v>
+        <v>6591.215010422628</v>
       </c>
       <c r="E95">
-        <v>24953.88135094516</v>
+        <v>25375.59830081013</v>
       </c>
       <c r="F95">
-        <v>39219.67633744297</v>
+        <v>39641.39328730795</v>
       </c>
       <c r="G95">
         <v>951</v>
@@ -9065,37 +9065,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M95">
-        <v>9480.83186441311</v>
+        <v>9582.776293062714</v>
       </c>
       <c r="N95">
-        <v>-7941.607374617191</v>
+        <v>-8043.551803266795</v>
       </c>
       <c r="O95">
-        <v>-992.7009218271489</v>
+        <v>-1005.443975408349</v>
       </c>
       <c r="P95">
-        <v>-6948.906452790043</v>
+        <v>-7038.107827858445</v>
       </c>
       <c r="Q95">
-        <v>-5926.906452790043</v>
+        <v>-6016.107827858445</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4894480764146971</v>
+        <v>0.5633894224838134</v>
       </c>
       <c r="T95">
-        <v>8.647526771052831</v>
+        <v>10.08878123289497</v>
       </c>
       <c r="U95">
         <v>0.2417366166625341</v>
       </c>
       <c r="V95">
-        <v>0.02029390078593067</v>
+        <v>0.02007800822437822</v>
       </c>
       <c r="W95">
-        <v>0.2368308377476581</v>
+        <v>0.2368830268850504</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1623512062874455</v>
+        <v>0.1606240657950259</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2564734106209761</v>
+        <v>0.2584327767876015</v>
       </c>
       <c r="C96">
-        <v>-32099.17827688532</v>
+        <v>-32581.63188214034</v>
       </c>
       <c r="D96">
-        <v>6591.215010422628</v>
+        <v>6530.478355032589</v>
       </c>
       <c r="E96">
-        <v>25375.59830081013</v>
+        <v>25797.31525067511</v>
       </c>
       <c r="F96">
-        <v>39641.39328730795</v>
+        <v>40063.11023717293</v>
       </c>
       <c r="G96">
         <v>951</v>
@@ -9147,37 +9147,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M96">
-        <v>9582.776293062714</v>
+        <v>9684.720721712318</v>
       </c>
       <c r="N96">
-        <v>-8043.551803266795</v>
+        <v>-8145.496231916399</v>
       </c>
       <c r="O96">
-        <v>-1005.443975408349</v>
+        <v>-1018.18702898955</v>
       </c>
       <c r="P96">
-        <v>-7038.107827858445</v>
+        <v>-7127.309202926849</v>
       </c>
       <c r="Q96">
-        <v>-6016.107827858445</v>
+        <v>-6105.309202926849</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5633894224838134</v>
+        <v>0.6669073069805763</v>
       </c>
       <c r="T96">
-        <v>10.08878123289497</v>
+        <v>12.10653747947397</v>
       </c>
       <c r="U96">
         <v>0.2417366166625341</v>
       </c>
       <c r="V96">
-        <v>0.02007800822437822</v>
+        <v>0.01986666076938477</v>
       </c>
       <c r="W96">
-        <v>0.2368830268850504</v>
+        <v>0.2369341173037607</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1606240657950259</v>
+        <v>0.1589332861550782</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2584327767876015</v>
+        <v>0.2603921429542268</v>
       </c>
       <c r="C97">
-        <v>-32581.63188214034</v>
+        <v>-33062.97635687447</v>
       </c>
       <c r="D97">
-        <v>6530.478355032589</v>
+        <v>6470.85083016343</v>
       </c>
       <c r="E97">
-        <v>25797.31525067511</v>
+        <v>26219.03220054009</v>
       </c>
       <c r="F97">
-        <v>40063.11023717293</v>
+        <v>40484.8271870379</v>
       </c>
       <c r="G97">
         <v>951</v>
@@ -9229,37 +9229,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M97">
-        <v>9684.720721712318</v>
+        <v>9786.66515036192</v>
       </c>
       <c r="N97">
-        <v>-8145.496231916399</v>
+        <v>-8247.440660566001</v>
       </c>
       <c r="O97">
-        <v>-1018.18702898955</v>
+        <v>-1030.93008257075</v>
       </c>
       <c r="P97">
-        <v>-7127.309202926849</v>
+        <v>-7216.51057799525</v>
       </c>
       <c r="Q97">
-        <v>-6105.309202926849</v>
+        <v>-6194.51057799525</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6669073069805763</v>
+        <v>0.8221841337257207</v>
       </c>
       <c r="T97">
-        <v>12.10653747947397</v>
+        <v>15.13317184934247</v>
       </c>
       <c r="U97">
         <v>0.2417366166625341</v>
       </c>
       <c r="V97">
-        <v>0.01986666076938477</v>
+        <v>0.01965971638637034</v>
       </c>
       <c r="W97">
-        <v>0.2369341173037607</v>
+        <v>0.236984143338748</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1589332861550782</v>
+        <v>0.1572777310909628</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2603921429542268</v>
+        <v>0.2623515091208521</v>
       </c>
       <c r="C98">
-        <v>-33062.97635687447</v>
+        <v>-33543.24180745124</v>
       </c>
       <c r="D98">
-        <v>6470.85083016343</v>
+        <v>6412.302329451637</v>
       </c>
       <c r="E98">
-        <v>26219.03220054009</v>
+        <v>26640.74915040506</v>
       </c>
       <c r="F98">
-        <v>40484.8271870379</v>
+        <v>40906.54413690288</v>
       </c>
       <c r="G98">
         <v>951</v>
@@ -9311,37 +9311,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M98">
-        <v>9786.66515036192</v>
+        <v>9888.609579011523</v>
       </c>
       <c r="N98">
-        <v>-8247.440660566001</v>
+        <v>-8349.385089215604</v>
       </c>
       <c r="O98">
-        <v>-1030.93008257075</v>
+        <v>-1043.673136151951</v>
       </c>
       <c r="P98">
-        <v>-7216.51057799525</v>
+        <v>-7305.711953063654</v>
       </c>
       <c r="Q98">
-        <v>-6194.51057799525</v>
+        <v>-6283.711953063654</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8221841337257186</v>
+        <v>1.080978844967625</v>
       </c>
       <c r="T98">
-        <v>15.13317184934243</v>
+        <v>20.17756246578991</v>
       </c>
       <c r="U98">
         <v>0.2417366166625341</v>
       </c>
       <c r="V98">
-        <v>0.01965971638637034</v>
+        <v>0.01945703889785106</v>
       </c>
       <c r="W98">
-        <v>0.236984143338748</v>
+        <v>0.2370331379090962</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1572777310909628</v>
+        <v>0.1556563111828085</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2623515091208521</v>
+        <v>0.2643108752874775</v>
       </c>
       <c r="C99">
-        <v>-33543.24180745124</v>
+        <v>-34022.4572603906</v>
       </c>
       <c r="D99">
-        <v>6412.302329451637</v>
+        <v>6354.803826377265</v>
       </c>
       <c r="E99">
-        <v>26640.74915040506</v>
+        <v>27062.46610027004</v>
       </c>
       <c r="F99">
-        <v>40906.54413690288</v>
+        <v>41328.26108676786</v>
       </c>
       <c r="G99">
         <v>951</v>
@@ -9393,37 +9393,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M99">
-        <v>9888.609579011523</v>
+        <v>9990.554007661127</v>
       </c>
       <c r="N99">
-        <v>-8349.385089215604</v>
+        <v>-8451.329517865208</v>
       </c>
       <c r="O99">
-        <v>-1043.673136151951</v>
+        <v>-1056.416189733151</v>
       </c>
       <c r="P99">
-        <v>-7305.711953063654</v>
+        <v>-7394.913328132057</v>
       </c>
       <c r="Q99">
-        <v>-6283.711953063654</v>
+        <v>-6372.913328132057</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.080978844967625</v>
+        <v>1.598568267451437</v>
       </c>
       <c r="T99">
-        <v>20.17756246578991</v>
+        <v>30.26634369868487</v>
       </c>
       <c r="U99">
         <v>0.2417366166625341</v>
       </c>
       <c r="V99">
-        <v>0.01945703889785106</v>
+        <v>0.01925849768460768</v>
       </c>
       <c r="W99">
-        <v>0.2370331379090962</v>
+        <v>0.2370811325902538</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1556563111828085</v>
+        <v>0.1540679814768615</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2643108752874775</v>
+        <v>0.2662702414541028</v>
       </c>
       <c r="C100">
-        <v>-34022.4572603906</v>
+        <v>-34500.65071035291</v>
       </c>
       <c r="D100">
-        <v>6354.803826377265</v>
+        <v>6298.327326279919</v>
       </c>
       <c r="E100">
-        <v>27062.46610027004</v>
+        <v>27484.18305013502</v>
       </c>
       <c r="F100">
-        <v>41328.26108676786</v>
+        <v>41749.97803663283</v>
       </c>
       <c r="G100">
         <v>951</v>
@@ -9475,37 +9475,37 @@
         <v>1539.224489795919</v>
       </c>
       <c r="M100">
-        <v>9990.554007661127</v>
+        <v>10092.49843631073</v>
       </c>
       <c r="N100">
-        <v>-8451.329517865208</v>
+        <v>-8553.27394651481</v>
       </c>
       <c r="O100">
-        <v>-1056.416189733151</v>
+        <v>-1069.159243314351</v>
       </c>
       <c r="P100">
-        <v>-7394.913328132057</v>
+        <v>-7484.114703200458</v>
       </c>
       <c r="Q100">
-        <v>-6372.913328132057</v>
+        <v>-6462.114703200458</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.598568267451437</v>
+        <v>3.151336534902875</v>
       </c>
       <c r="T100">
-        <v>30.26634369868487</v>
+        <v>60.53268739736973</v>
       </c>
       <c r="U100">
         <v>0.2417366166625341</v>
       </c>
       <c r="V100">
-        <v>0.01925849768460768</v>
+        <v>0.01906396740496518</v>
       </c>
       <c r="W100">
-        <v>0.2370811325902538</v>
+        <v>0.237128157681893</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1540679814768615</v>
+        <v>0.1525117392397215</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2662702414541028</v>
-      </c>
-      <c r="C101">
-        <v>-34500.65071035291</v>
-      </c>
-      <c r="D101">
-        <v>6298.327326279919</v>
-      </c>
-      <c r="E101">
-        <v>27484.18305013502</v>
-      </c>
-      <c r="F101">
-        <v>41749.97803663283</v>
-      </c>
-      <c r="G101">
-        <v>951</v>
-      </c>
-      <c r="H101">
-        <v>27905.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2561.224489795919</v>
-      </c>
-      <c r="K101">
-        <v>1022</v>
-      </c>
-      <c r="L101">
-        <v>1539.224489795919</v>
-      </c>
-      <c r="M101">
-        <v>10092.49843631073</v>
-      </c>
-      <c r="N101">
-        <v>-8553.27394651481</v>
-      </c>
-      <c r="O101">
-        <v>-1069.159243314351</v>
-      </c>
-      <c r="P101">
-        <v>-7484.114703200458</v>
-      </c>
-      <c r="Q101">
-        <v>-6462.114703200458</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.151336534902875</v>
-      </c>
-      <c r="T101">
-        <v>60.53268739736973</v>
-      </c>
-      <c r="U101">
-        <v>0.2417366166625341</v>
-      </c>
-      <c r="V101">
-        <v>0.01906396740496518</v>
-      </c>
-      <c r="W101">
-        <v>0.237128157681893</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1525117392397215</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
